--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1136,16 +1136,16 @@
         <v>3.71</v>
       </c>
       <c r="R5">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="S5">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="U5">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="V5">
         <v>1.23</v>
@@ -1157,13 +1157,13 @@
         <v>1.07</v>
       </c>
       <c r="Y5">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z5">
         <v>2.43</v>
       </c>
       <c r="AA5">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="AB5">
         <v>1.51</v>
@@ -1178,10 +1178,10 @@
         <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G7">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G23">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O30">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="Q30">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="R30">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T30">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="U30">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="V30">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>5.45</v>
+        <v>4.33</v>
       </c>
       <c r="AA30">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="AB30">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="AC30">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="AD30">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AE30">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AG30">
-        <v>2.81</v>
+        <v>2.42</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
         <v>1.44</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="O31">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P31">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q31">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="R31">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S31">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T31">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="U31">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V31">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="W31">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z31">
-        <v>5.85</v>
+        <v>6.7</v>
       </c>
       <c r="AA31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB31">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AC31">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD31">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE31">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AF31">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AG31">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK31">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="Q33">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T33">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="V33">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z33">
-        <v>4.33</v>
+        <v>5.45</v>
       </c>
       <c r="AA33">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AB33">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="AC33">
-        <v>2.43</v>
+        <v>2.06</v>
       </c>
       <c r="AD33">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AE33">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF33">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AG33">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
         <v>1.44</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G44">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G59">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU63"/>
+  <dimension ref="A1:AU64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G8">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-16 12:30:00</t>
+          <t>2026-09-16 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.17</v>
+        <v>1.33</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P10">
-        <v>2.29</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>3.85</v>
+        <v>1.85</v>
       </c>
       <c r="R10">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="S10">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T10">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U10">
-        <v>3.14</v>
+        <v>2.81</v>
       </c>
       <c r="V10">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z10">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA10">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AB10">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AC10">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="AD10">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="AG10">
-        <v>1.89</v>
+        <v>1.54</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>1.38</v>
+        <v>3.34</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.88</v>
+        <v>3.17</v>
       </c>
       <c r="O11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-16 12:45:00</t>
+          <t>2026-09-16 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G12">
@@ -2261,68 +2261,68 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N12">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="O12">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="Q12">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-16 13:00:00</t>
+          <t>2026-09-16 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,68 +2424,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.61</v>
+        <v>5.45</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>4.53</v>
+        <v>1.94</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G14">
@@ -2587,68 +2587,68 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="O14">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>8.5</v>
+        <v>4.53</v>
       </c>
       <c r="Q14">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.6</v>
+        <v>1.24</v>
       </c>
       <c r="O15">
-        <v>3.9</v>
+        <v>5.75</v>
       </c>
       <c r="P15">
-        <v>1.55</v>
+        <v>7.5</v>
       </c>
       <c r="Q15">
-        <v>5.07</v>
+        <v>1.62</v>
       </c>
       <c r="R15">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="V15">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="W15">
+        <v>1.17</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
         <v>1.08</v>
       </c>
-      <c r="X15">
-        <v>1.04</v>
-      </c>
-      <c r="Y15">
-        <v>1.24</v>
-      </c>
       <c r="Z15">
-        <v>3.72</v>
+        <v>5.75</v>
       </c>
       <c r="AA15">
+        <v>1.43</v>
+      </c>
+      <c r="AB15">
+        <v>2.75</v>
+      </c>
+      <c r="AC15">
+        <v>1.98</v>
+      </c>
+      <c r="AD15">
+        <v>1.61</v>
+      </c>
+      <c r="AE15">
+        <v>1.27</v>
+      </c>
+      <c r="AF15">
         <v>1.75</v>
       </c>
-      <c r="AB15">
-        <v>2.05</v>
-      </c>
-      <c r="AC15">
-        <v>2.75</v>
-      </c>
-      <c r="AD15">
-        <v>1.4</v>
-      </c>
-      <c r="AE15">
-        <v>1.15</v>
-      </c>
-      <c r="AF15">
-        <v>1.74</v>
-      </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK15">
-        <v>1.17</v>
+        <v>3.52</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G16">
@@ -2913,68 +2913,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G18">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-16 13:30:00</t>
+          <t>2026-09-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-16 14:00:00</t>
+          <t>2026-09-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>7.95</v>
+        <v>5.39</v>
       </c>
       <c r="O26">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="P26">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Q26">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="S26">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="T26">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="U26">
         <v>3.3</v>
       </c>
       <c r="V26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z26">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AA26">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB26">
         <v>1.57</v>
       </c>
       <c r="AC26">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AG26">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AK26">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G27">
@@ -4706,68 +4706,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.01</v>
+        <v>7.95</v>
       </c>
       <c r="O27">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="P27">
-        <v>3.52</v>
+        <v>1.44</v>
       </c>
       <c r="Q27">
-        <v>2.47</v>
+        <v>7</v>
       </c>
       <c r="R27">
+        <v>2.2</v>
+      </c>
+      <c r="S27">
+        <v>1.49</v>
+      </c>
+      <c r="T27">
+        <v>2.37</v>
+      </c>
+      <c r="U27">
+        <v>3.3</v>
+      </c>
+      <c r="V27">
+        <v>1.29</v>
+      </c>
+      <c r="W27">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>1.03</v>
+      </c>
+      <c r="Y27">
+        <v>1.37</v>
+      </c>
+      <c r="Z27">
+        <v>2.66</v>
+      </c>
+      <c r="AA27">
+        <v>2.25</v>
+      </c>
+      <c r="AB27">
+        <v>1.57</v>
+      </c>
+      <c r="AC27">
+        <v>4.1</v>
+      </c>
+      <c r="AD27">
+        <v>1.18</v>
+      </c>
+      <c r="AE27">
+        <v>1.01</v>
+      </c>
+      <c r="AF27">
         <v>2.4</v>
       </c>
-      <c r="S27">
-        <v>1.23</v>
-      </c>
-      <c r="T27">
-        <v>3.8</v>
-      </c>
-      <c r="U27">
-        <v>2.16</v>
-      </c>
-      <c r="V27">
-        <v>1.65</v>
-      </c>
-      <c r="W27">
-        <v>1.17</v>
-      </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
-      <c r="Y27">
-        <v>1.11</v>
-      </c>
-      <c r="Z27">
-        <v>4.8</v>
-      </c>
-      <c r="AA27">
-        <v>1.46</v>
-      </c>
-      <c r="AB27">
-        <v>2.39</v>
-      </c>
-      <c r="AC27">
-        <v>2.26</v>
-      </c>
-      <c r="AD27">
-        <v>1.62</v>
-      </c>
-      <c r="AE27">
-        <v>1.21</v>
-      </c>
-      <c r="AF27">
-        <v>1.44</v>
-      </c>
       <c r="AG27">
-        <v>2.55</v>
+        <v>1.48</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.74</v>
+        <v>1.08</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.72</v>
+        <v>2.01</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P28">
-        <v>2.2</v>
+        <v>3.52</v>
       </c>
       <c r="Q28">
-        <v>3.05</v>
+        <v>2.47</v>
       </c>
       <c r="R28">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T28">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U28">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V28">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="W28">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X28">
         <v>1.02</v>
@@ -4909,28 +4909,28 @@
         <v>1.11</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA28">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB28">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="AC28">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AD28">
         <v>1.62</v>
       </c>
       <c r="AE28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF28">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG28">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AK28">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,68 +5032,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29">
-        <v>1.74</v>
+        <v>2.72</v>
       </c>
       <c r="O29">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q29">
+        <v>3.05</v>
+      </c>
+      <c r="R29">
+        <v>2.29</v>
+      </c>
+      <c r="S29">
+        <v>1.24</v>
+      </c>
+      <c r="T29">
+        <v>3.5</v>
+      </c>
+      <c r="U29">
         <v>2.1</v>
       </c>
-      <c r="R29">
-        <v>2.63</v>
-      </c>
-      <c r="S29">
-        <v>1.17</v>
-      </c>
-      <c r="T29">
-        <v>4.5</v>
-      </c>
-      <c r="U29">
-        <v>1.92</v>
-      </c>
       <c r="V29">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="W29">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z29">
-        <v>5.85</v>
+        <v>5</v>
       </c>
       <c r="AA29">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AB29">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="AC29">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD29">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE29">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AG29">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AK29">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.55</v>
+        <v>1.74</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P30">
-        <v>2.46</v>
+        <v>3.8</v>
       </c>
       <c r="Q30">
-        <v>2.93</v>
+        <v>2.1</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S30">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="T30">
-        <v>3.48</v>
+        <v>4.5</v>
       </c>
       <c r="U30">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="V30">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z30">
-        <v>4.33</v>
+        <v>5.85</v>
       </c>
       <c r="AA30">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AB30">
-        <v>2.21</v>
+        <v>2.83</v>
       </c>
       <c r="AC30">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AD30">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AE30">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AF30">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AG30">
-        <v>2.42</v>
+        <v>2.73</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK30">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="T34">
-        <v>2.65</v>
+        <v>3.48</v>
       </c>
       <c r="U34">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>2.65</v>
+        <v>4.33</v>
       </c>
       <c r="AA34">
-        <v>2.28</v>
+        <v>1.59</v>
       </c>
       <c r="AB34">
-        <v>1.6</v>
+        <v>2.21</v>
       </c>
       <c r="AC34">
-        <v>3.7</v>
+        <v>2.43</v>
       </c>
       <c r="AD34">
+        <v>1.44</v>
+      </c>
+      <c r="AE34">
+        <v>1.15</v>
+      </c>
+      <c r="AF34">
+        <v>1.49</v>
+      </c>
+      <c r="AG34">
+        <v>2.42</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
         <v>1.22</v>
       </c>
-      <c r="AE34">
-        <v>1.06</v>
-      </c>
-      <c r="AF34">
-        <v>1.9</v>
-      </c>
-      <c r="AG34">
-        <v>1.83</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.4</v>
-      </c>
       <c r="AK34">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="R35">
-        <v>2.57</v>
+        <v>1.95</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="U35">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y35">
+        <v>1.38</v>
+      </c>
+      <c r="Z35">
+        <v>2.76</v>
+      </c>
+      <c r="AA35">
+        <v>2.28</v>
+      </c>
+      <c r="AB35">
+        <v>1.6</v>
+      </c>
+      <c r="AC35">
+        <v>3.7</v>
+      </c>
+      <c r="AD35">
         <v>1.22</v>
       </c>
-      <c r="Z35">
-        <v>4</v>
-      </c>
-      <c r="AA35">
-        <v>1.72</v>
-      </c>
-      <c r="AB35">
-        <v>2.1</v>
-      </c>
-      <c r="AC35">
-        <v>2.8</v>
-      </c>
-      <c r="AD35">
-        <v>1.38</v>
-      </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG35">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK35">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.32</v>
+        <v>1.53</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>4.24</v>
       </c>
       <c r="P36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>2.7</v>
+        <v>2.01</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U36">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="V36">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA36">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB36">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD36">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AG36">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>4.28</v>
+        <v>3</v>
       </c>
       <c r="Q37">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="R37">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="V37">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.44</v>
+        <v>3.95</v>
       </c>
       <c r="AA37">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="AB37">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC37">
-        <v>3.24</v>
+        <v>2.85</v>
       </c>
       <c r="AD37">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AG37">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-16 14:45:00</t>
+          <t>2026-09-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.6</v>
+        <v>1.77</v>
       </c>
       <c r="O38">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>1.75</v>
+        <v>4.28</v>
       </c>
       <c r="Q38">
-        <v>5.1</v>
+        <v>2.31</v>
       </c>
       <c r="R38">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S38">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T38">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="V38">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W38">
         <v>1.05</v>
@@ -6536,31 +6536,31 @@
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.05</v>
+        <v>3.44</v>
       </c>
       <c r="AA38">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AB38">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AC38">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="AD38">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE38">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>2.09</v>
+        <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.22</v>
+        <v>2.08</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6619,27 +6619,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>1.79</v>
+        <v>4.6</v>
       </c>
       <c r="O39">
-        <v>2.47</v>
+        <v>3.72</v>
       </c>
       <c r="P39">
-        <v>4.6</v>
+        <v>1.75</v>
       </c>
       <c r="Q39">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="R39">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="S39">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="T39">
-        <v>2.04</v>
+        <v>2.77</v>
       </c>
       <c r="U39">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="V39">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="W39">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="Z39">
-        <v>2.14</v>
+        <v>3.05</v>
       </c>
       <c r="AA39">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AC39">
-        <v>6.5</v>
+        <v>3.44</v>
       </c>
       <c r="AD39">
+        <v>1.25</v>
+      </c>
+      <c r="AE39">
         <v>1.05</v>
       </c>
-      <c r="AE39">
-        <v>1.01</v>
-      </c>
       <c r="AF39">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AG39">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>2.09</v>
       </c>
       <c r="AK39">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:00</t>
+          <t>2026-09-16 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G40">
@@ -6825,68 +6825,68 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-16 16:00:00</t>
+          <t>2026-09-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,22 +7602,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G45">
@@ -7760,27 +7760,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U46">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="V46">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="W46">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z46">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA46">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD46">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AE46">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF46">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG46">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK46">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-16 16:30:00</t>
+          <t>2026-09-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,61 +7970,61 @@
         </is>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>1.11</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>12</v>
       </c>
       <c r="P47">
-        <v>2.24</v>
+        <v>20</v>
       </c>
       <c r="Q47">
-        <v>3.32</v>
+        <v>1.29</v>
       </c>
       <c r="R47">
-        <v>2.09</v>
+        <v>4</v>
       </c>
       <c r="S47">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="T47">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="U47">
-        <v>2.59</v>
+        <v>1.54</v>
       </c>
       <c r="V47">
+        <v>2.38</v>
+      </c>
+      <c r="W47">
         <v>1.43</v>
       </c>
-      <c r="W47">
-        <v>1.06</v>
-      </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="Z47">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="AA47">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="AB47">
-        <v>1.85</v>
+        <v>5.5</v>
       </c>
       <c r="AC47">
-        <v>2.95</v>
+        <v>1.33</v>
       </c>
       <c r="AD47">
-        <v>1.33</v>
+        <v>3.04</v>
       </c>
       <c r="AE47">
-        <v>1.08</v>
+        <v>1.97</v>
       </c>
       <c r="AF47">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG47">
         <v>2.1</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.62</v>
+        <v>1.05</v>
       </c>
       <c r="AK47">
-        <v>1.33</v>
+        <v>8</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.54</v>
+        <v>3</v>
       </c>
       <c r="O48">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>6.54</v>
+        <v>2.24</v>
       </c>
       <c r="Q48">
+        <v>3.32</v>
+      </c>
+      <c r="R48">
+        <v>2.09</v>
+      </c>
+      <c r="S48">
+        <v>1.36</v>
+      </c>
+      <c r="T48">
+        <v>2.88</v>
+      </c>
+      <c r="U48">
+        <v>2.59</v>
+      </c>
+      <c r="V48">
+        <v>1.43</v>
+      </c>
+      <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.26</v>
+      </c>
+      <c r="Z48">
+        <v>3.4</v>
+      </c>
+      <c r="AA48">
         <v>1.9</v>
       </c>
-      <c r="R48">
-        <v>2.4</v>
-      </c>
-      <c r="S48">
-        <v>1.3</v>
-      </c>
-      <c r="T48">
-        <v>3.2</v>
-      </c>
-      <c r="U48">
-        <v>2.4</v>
-      </c>
-      <c r="V48">
-        <v>1.5</v>
-      </c>
-      <c r="W48">
-        <v>1.11</v>
-      </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.2</v>
-      </c>
-      <c r="Z48">
-        <v>4.1</v>
-      </c>
-      <c r="AA48">
-        <v>1.75</v>
-      </c>
       <c r="AB48">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AC48">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE48">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG48">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="AK48">
-        <v>2.61</v>
+        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-16 18:00:00</t>
+          <t>2026-09-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-16 19:00:00</t>
+          <t>2026-09-16 18:00:00</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G50">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC51">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-09-16 19:30:00</t>
+          <t>2026-09-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G52">
@@ -8781,68 +8781,68 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 19:30:00</t>
         </is>
       </c>
     </row>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G59">
@@ -10042,27 +10042,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE60">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF60">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK60">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-09-16 21:30:00</t>
+          <t>2026-09-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G61">
@@ -10248,68 +10248,68 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-09-16 22:30:00</t>
+          <t>2026-09-16 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10531,156 +10531,319 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Denver Summit W</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>0</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>0</v>
+      </c>
+      <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63">
+        <v>0</v>
+      </c>
+      <c r="AM63">
+        <v>-1</v>
+      </c>
+      <c r="AN63">
+        <v>-1</v>
+      </c>
+      <c r="AO63">
+        <v>-1</v>
+      </c>
+      <c r="AP63">
+        <v>-1</v>
+      </c>
+      <c r="AQ63">
+        <v>0</v>
+      </c>
+      <c r="AR63">
+        <v>0</v>
+      </c>
+      <c r="AS63">
+        <v>0</v>
+      </c>
+      <c r="AT63">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63" t="inlineStr">
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>0</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>0</v>
-      </c>
-      <c r="Z63">
-        <v>0</v>
-      </c>
-      <c r="AA63">
-        <v>0</v>
-      </c>
-      <c r="AB63">
-        <v>0</v>
-      </c>
-      <c r="AC63">
-        <v>0</v>
-      </c>
-      <c r="AD63">
-        <v>0</v>
-      </c>
-      <c r="AE63">
-        <v>0</v>
-      </c>
-      <c r="AF63">
-        <v>0</v>
-      </c>
-      <c r="AG63">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>0</v>
-      </c>
-      <c r="AK63">
-        <v>0</v>
-      </c>
-      <c r="AL63">
-        <v>0</v>
-      </c>
-      <c r="AM63">
-        <v>-1</v>
-      </c>
-      <c r="AN63">
-        <v>-1</v>
-      </c>
-      <c r="AO63">
-        <v>-1</v>
-      </c>
-      <c r="AP63">
-        <v>-1</v>
-      </c>
-      <c r="AQ63">
-        <v>0</v>
-      </c>
-      <c r="AR63">
-        <v>0</v>
-      </c>
-      <c r="AS63">
-        <v>0</v>
-      </c>
-      <c r="AT63">
-        <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>0</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>-1</v>
+      </c>
+      <c r="AN64">
+        <v>-1</v>
+      </c>
+      <c r="AO64">
+        <v>-1</v>
+      </c>
+      <c r="AP64">
+        <v>-1</v>
+      </c>
+      <c r="AQ64">
+        <v>0</v>
+      </c>
+      <c r="AR64">
+        <v>0</v>
+      </c>
+      <c r="AS64">
+        <v>0</v>
+      </c>
+      <c r="AT64">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
         <is>
           <t>2026-09-16 23:00:00</t>
         </is>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="Q34">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="V34">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z34">
-        <v>4.33</v>
+        <v>5.45</v>
       </c>
       <c r="AA34">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AB34">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="AC34">
-        <v>2.43</v>
+        <v>2.06</v>
       </c>
       <c r="AD34">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF34">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AG34">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
         <v>1.44</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
         <v>3</v>
@@ -6355,10 +6355,10 @@
         <v>2.28</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U37">
         <v>2.48</v>
@@ -6367,10 +6367,10 @@
         <v>1.46</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
         <v>1.2</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G60">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O40">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P40">
         <v>4.81</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G45">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.54</v>
+        <v>7</v>
       </c>
       <c r="O49">
         <v>4.2</v>
       </c>
       <c r="P49">
-        <v>6.54</v>
+        <v>6</v>
       </c>
       <c r="Q49">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z49">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB49">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AC49">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD49">
         <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF49">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG49">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AK49">
-        <v>2.61</v>
+        <v>2.78</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8785,43 +8785,43 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q52">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="R52">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S52">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T52">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U52">
-        <v>2.71</v>
+        <v>2.99</v>
       </c>
       <c r="V52">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
         <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AA52">
         <v>2</v>
@@ -8833,16 +8833,16 @@
         <v>3.05</v>
       </c>
       <c r="AD52">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF52">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG52">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.29</v>
       </c>
       <c r="AK52">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G60">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -644,31 +644,31 @@
         <v>3.65</v>
       </c>
       <c r="Q2">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R2">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U2">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z2">
         <v>4.1</v>
@@ -677,22 +677,22 @@
         <v>1.65</v>
       </c>
       <c r="AB2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC2">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AD2">
         <v>1.45</v>
       </c>
       <c r="AE2">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
         <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1148,13 +1148,13 @@
         <v>3.3</v>
       </c>
       <c r="V5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y5">
         <v>1.47</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O10">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Q10">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R10">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="S10">
         <v>1.4</v>
@@ -1972,16 +1972,16 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z10">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AA10">
         <v>1.91</v>
       </c>
       <c r="AB10">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AC10">
         <v>3.05</v>
@@ -1993,10 +1993,10 @@
         <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AG10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.17</v>
+        <v>2.95</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="Q11">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="R11">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="S11">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="U11">
         <v>3.14</v>
@@ -2144,22 +2144,22 @@
         <v>2.12</v>
       </c>
       <c r="AB11">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AC11">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE11">
         <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG11">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AK11">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2470,7 +2470,7 @@
         <v>2.05</v>
       </c>
       <c r="AB13">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC13">
         <v>3.84</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>3.83</v>
@@ -2935,16 +2935,16 @@
         <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U16">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V16">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -2959,22 +2959,22 @@
         <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC16">
         <v>2.95</v>
       </c>
       <c r="AD16">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
         <v>1.74</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>5.39</v>
+        <v>5.45</v>
       </c>
       <c r="O26">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="P26">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q26">
         <v>6.1</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
         <v>1.15</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>7.95</v>
+        <v>7.5</v>
       </c>
       <c r="O27">
         <v>3.58</v>
@@ -4728,7 +4728,7 @@
         <v>1.49</v>
       </c>
       <c r="T27">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="U27">
         <v>3.3</v>
@@ -4737,16 +4737,16 @@
         <v>1.29</v>
       </c>
       <c r="W27">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z27">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="AA27">
         <v>2.25</v>
@@ -4755,7 +4755,7 @@
         <v>1.57</v>
       </c>
       <c r="AC27">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD27">
         <v>1.18</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O28">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="Q28">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="R28">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="S28">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U28">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="V28">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="W28">
         <v>1.17</v>
@@ -4906,31 +4906,31 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z28">
-        <v>4.8</v>
+        <v>6.14</v>
       </c>
       <c r="AA28">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB28">
-        <v>2.39</v>
+        <v>2.83</v>
       </c>
       <c r="AC28">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AD28">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AE28">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AF28">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG28">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK28">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="O29">
         <v>3.5</v>
@@ -5045,10 +5045,10 @@
         <v>2.2</v>
       </c>
       <c r="Q29">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R29">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="S29">
         <v>1.24</v>
@@ -5057,13 +5057,13 @@
         <v>3.5</v>
       </c>
       <c r="U29">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V29">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W29">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
         <v>1.02</v>
@@ -5075,22 +5075,22 @@
         <v>5</v>
       </c>
       <c r="AA29">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB29">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AC29">
         <v>2.25</v>
       </c>
       <c r="AD29">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE29">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF29">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG29">
         <v>2.6</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="AK29">
         <v>1.41</v>
@@ -5217,7 +5217,7 @@
         <v>1.17</v>
       </c>
       <c r="T30">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U30">
         <v>1.92</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
         <v>2</v>
@@ -5377,16 +5377,16 @@
         <v>2.7</v>
       </c>
       <c r="S31">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T31">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="U31">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V31">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W31">
         <v>1.2</v>
@@ -5398,7 +5398,7 @@
         <v>1.05</v>
       </c>
       <c r="Z31">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="AA31">
         <v>1.3</v>
@@ -5419,7 +5419,7 @@
         <v>1.38</v>
       </c>
       <c r="AG31">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>1.55</v>
       </c>
       <c r="W32">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X32">
         <v>1.01</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O34">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q34">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="R34">
         <v>2.38</v>
@@ -5908,7 +5908,7 @@
         <v>1.37</v>
       </c>
       <c r="AG34">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>1.42</v>
       </c>
       <c r="T35">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="U35">
         <v>2.88</v>
@@ -6059,7 +6059,7 @@
         <v>1.6</v>
       </c>
       <c r="AC35">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="AD35">
         <v>1.22</v>
@@ -6071,7 +6071,7 @@
         <v>1.9</v>
       </c>
       <c r="AG35">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.4</v>
       </c>
       <c r="AK35">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O36">
         <v>4.24</v>
@@ -6186,10 +6186,10 @@
         <v>6</v>
       </c>
       <c r="Q36">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="R36">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
         <v>1.3</v>
@@ -6198,10 +6198,10 @@
         <v>3.2</v>
       </c>
       <c r="U36">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W36">
         <v>1.11</v>
@@ -6231,10 +6231,10 @@
         <v>1.15</v>
       </c>
       <c r="AF36">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
+        <v>1.84</v>
+      </c>
+      <c r="O38">
+        <v>3.76</v>
+      </c>
+      <c r="P38">
+        <v>4</v>
+      </c>
+      <c r="Q38">
+        <v>2.38</v>
+      </c>
+      <c r="R38">
+        <v>2.24</v>
+      </c>
+      <c r="S38">
+        <v>1.34</v>
+      </c>
+      <c r="T38">
+        <v>3.14</v>
+      </c>
+      <c r="U38">
+        <v>2.6</v>
+      </c>
+      <c r="V38">
+        <v>1.47</v>
+      </c>
+      <c r="W38">
+        <v>1.07</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.2</v>
+      </c>
+      <c r="Z38">
+        <v>3.92</v>
+      </c>
+      <c r="AA38">
         <v>1.77</v>
       </c>
-      <c r="O38">
-        <v>3.9</v>
-      </c>
-      <c r="P38">
-        <v>4.28</v>
-      </c>
-      <c r="Q38">
-        <v>2.31</v>
-      </c>
-      <c r="R38">
-        <v>2.26</v>
-      </c>
-      <c r="S38">
-        <v>1.35</v>
-      </c>
-      <c r="T38">
-        <v>3.08</v>
-      </c>
-      <c r="U38">
+      <c r="AB38">
+        <v>2.06</v>
+      </c>
+      <c r="AC38">
         <v>2.81</v>
       </c>
-      <c r="V38">
-        <v>1.41</v>
-      </c>
-      <c r="W38">
-        <v>1.05</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.25</v>
-      </c>
-      <c r="Z38">
-        <v>3.44</v>
-      </c>
-      <c r="AA38">
-        <v>1.97</v>
-      </c>
-      <c r="AB38">
-        <v>1.97</v>
-      </c>
-      <c r="AC38">
-        <v>3.24</v>
-      </c>
       <c r="AD38">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG38">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O39">
-        <v>3.72</v>
+        <v>3.48</v>
       </c>
       <c r="P39">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Q39">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="R39">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="S39">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="T39">
-        <v>2.77</v>
+        <v>2.54</v>
       </c>
       <c r="U39">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="V39">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="Z39">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="AA39">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="AB39">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AC39">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF39">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AG39">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>2.09</v>
+        <v>1.34</v>
       </c>
       <c r="AK39">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7973,16 +7973,16 @@
         <v>1.11</v>
       </c>
       <c r="O47">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P47">
         <v>20</v>
       </c>
       <c r="Q47">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="R47">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="S47">
         <v>1.09</v>
@@ -7991,13 +7991,13 @@
         <v>6</v>
       </c>
       <c r="U47">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V47">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="W47">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X47">
         <v>1</v>
@@ -8009,25 +8009,25 @@
         <v>11</v>
       </c>
       <c r="AA47">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB47">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AC47">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD47">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="AE47">
         <v>1.97</v>
       </c>
       <c r="AF47">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.05</v>
       </c>
       <c r="AK47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8139,13 +8139,13 @@
         <v>3.4</v>
       </c>
       <c r="P48">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q48">
-        <v>3.32</v>
+        <v>3.88</v>
       </c>
       <c r="R48">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="S48">
         <v>1.36</v>
@@ -8154,16 +8154,16 @@
         <v>2.88</v>
       </c>
       <c r="U48">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
         <v>1.26</v>
@@ -8172,25 +8172,25 @@
         <v>3.4</v>
       </c>
       <c r="AA48">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC48">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AD48">
         <v>1.33</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF48">
         <v>1.7</v>
       </c>
       <c r="AG48">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="O50">
-        <v>4.15</v>
+        <v>4.32</v>
       </c>
       <c r="P50">
-        <v>4.7</v>
+        <v>4.89</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -10261,7 +10261,7 @@
         <v>2.85</v>
       </c>
       <c r="Q61">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="R61">
         <v>2.25</v>
@@ -10270,34 +10270,34 @@
         <v>1.3</v>
       </c>
       <c r="T61">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U61">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V61">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W61">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z61">
-        <v>4.24</v>
+        <v>3.9</v>
       </c>
       <c r="AA61">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB61">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC61">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD61">
         <v>1.39</v>
@@ -10306,7 +10306,7 @@
         <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
         <v>2.3</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL61">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P2">
         <v>3.65</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>2.9</v>
+        <v>1.99</v>
       </c>
       <c r="R35">
+        <v>2.5</v>
+      </c>
+      <c r="S35">
+        <v>1.3</v>
+      </c>
+      <c r="T35">
+        <v>3.2</v>
+      </c>
+      <c r="U35">
+        <v>2.59</v>
+      </c>
+      <c r="V35">
+        <v>1.48</v>
+      </c>
+      <c r="W35">
+        <v>1.11</v>
+      </c>
+      <c r="X35">
+        <v>1</v>
+      </c>
+      <c r="Y35">
+        <v>1.22</v>
+      </c>
+      <c r="Z35">
+        <v>4</v>
+      </c>
+      <c r="AA35">
+        <v>1.72</v>
+      </c>
+      <c r="AB35">
+        <v>2.1</v>
+      </c>
+      <c r="AC35">
+        <v>2.8</v>
+      </c>
+      <c r="AD35">
+        <v>1.38</v>
+      </c>
+      <c r="AE35">
+        <v>1.15</v>
+      </c>
+      <c r="AF35">
+        <v>1.85</v>
+      </c>
+      <c r="AG35">
         <v>1.95</v>
       </c>
-      <c r="S35">
-        <v>1.42</v>
-      </c>
-      <c r="T35">
-        <v>2.65</v>
-      </c>
-      <c r="U35">
-        <v>2.88</v>
-      </c>
-      <c r="V35">
-        <v>1.36</v>
-      </c>
-      <c r="W35">
-        <v>1.07</v>
-      </c>
-      <c r="X35">
-        <v>1.08</v>
-      </c>
-      <c r="Y35">
-        <v>1.38</v>
-      </c>
-      <c r="Z35">
-        <v>2.76</v>
-      </c>
-      <c r="AA35">
-        <v>2.28</v>
-      </c>
-      <c r="AB35">
-        <v>1.6</v>
-      </c>
-      <c r="AC35">
-        <v>3.84</v>
-      </c>
-      <c r="AD35">
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.22</v>
       </c>
-      <c r="AE35">
-        <v>1.06</v>
-      </c>
-      <c r="AF35">
-        <v>1.9</v>
-      </c>
-      <c r="AG35">
-        <v>1.83</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.4</v>
-      </c>
       <c r="AK35">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>1.99</v>
+        <v>2.9</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T36">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U36">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y36">
+        <v>1.38</v>
+      </c>
+      <c r="Z36">
+        <v>2.76</v>
+      </c>
+      <c r="AA36">
+        <v>2.28</v>
+      </c>
+      <c r="AB36">
+        <v>1.6</v>
+      </c>
+      <c r="AC36">
+        <v>3.84</v>
+      </c>
+      <c r="AD36">
         <v>1.22</v>
       </c>
-      <c r="Z36">
-        <v>4</v>
-      </c>
-      <c r="AA36">
-        <v>1.72</v>
-      </c>
-      <c r="AB36">
-        <v>2.1</v>
-      </c>
-      <c r="AC36">
-        <v>2.8</v>
-      </c>
-      <c r="AD36">
-        <v>1.38</v>
-      </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG36">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK36">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O37">
         <v>3.3</v>
@@ -6355,10 +6355,10 @@
         <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
         <v>2.48</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.84</v>
+        <v>4.5</v>
       </c>
       <c r="O38">
-        <v>3.76</v>
+        <v>3.48</v>
       </c>
       <c r="P38">
-        <v>4</v>
+        <v>1.81</v>
       </c>
       <c r="Q38">
-        <v>2.38</v>
+        <v>5.2</v>
       </c>
       <c r="R38">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="S38">
+        <v>1.49</v>
+      </c>
+      <c r="T38">
+        <v>2.54</v>
+      </c>
+      <c r="U38">
+        <v>3.32</v>
+      </c>
+      <c r="V38">
+        <v>1.31</v>
+      </c>
+      <c r="W38">
+        <v>1.03</v>
+      </c>
+      <c r="X38">
+        <v>1.04</v>
+      </c>
+      <c r="Y38">
+        <v>1.39</v>
+      </c>
+      <c r="Z38">
+        <v>2.69</v>
+      </c>
+      <c r="AA38">
+        <v>2.31</v>
+      </c>
+      <c r="AB38">
+        <v>1.68</v>
+      </c>
+      <c r="AC38">
+        <v>4.1</v>
+      </c>
+      <c r="AD38">
+        <v>1.18</v>
+      </c>
+      <c r="AE38">
+        <v>1.02</v>
+      </c>
+      <c r="AF38">
+        <v>2.04</v>
+      </c>
+      <c r="AG38">
+        <v>1.69</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.34</v>
       </c>
-      <c r="T38">
-        <v>3.14</v>
-      </c>
-      <c r="U38">
-        <v>2.6</v>
-      </c>
-      <c r="V38">
-        <v>1.47</v>
-      </c>
-      <c r="W38">
-        <v>1.07</v>
-      </c>
-      <c r="X38">
-        <v>1.03</v>
-      </c>
-      <c r="Y38">
-        <v>1.2</v>
-      </c>
-      <c r="Z38">
-        <v>3.92</v>
-      </c>
-      <c r="AA38">
-        <v>1.77</v>
-      </c>
-      <c r="AB38">
-        <v>2.06</v>
-      </c>
-      <c r="AC38">
-        <v>2.81</v>
-      </c>
-      <c r="AD38">
-        <v>1.36</v>
-      </c>
-      <c r="AE38">
-        <v>1.09</v>
-      </c>
-      <c r="AF38">
-        <v>1.66</v>
-      </c>
-      <c r="AG38">
-        <v>2.12</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.3</v>
-      </c>
       <c r="AK38">
-        <v>1.99</v>
+        <v>1.23</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.5</v>
+        <v>1.84</v>
       </c>
       <c r="O39">
-        <v>3.48</v>
+        <v>3.76</v>
       </c>
       <c r="P39">
-        <v>1.81</v>
+        <v>4</v>
       </c>
       <c r="Q39">
-        <v>5.2</v>
+        <v>2.38</v>
       </c>
       <c r="R39">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="S39">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="T39">
-        <v>2.54</v>
+        <v>3.14</v>
       </c>
       <c r="U39">
-        <v>3.32</v>
+        <v>2.6</v>
       </c>
       <c r="V39">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W39">
+        <v>1.07</v>
+      </c>
+      <c r="X39">
         <v>1.03</v>
       </c>
-      <c r="X39">
-        <v>1.04</v>
-      </c>
       <c r="Y39">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>2.69</v>
+        <v>3.92</v>
       </c>
       <c r="AA39">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AB39">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AC39">
-        <v>4.1</v>
+        <v>2.81</v>
       </c>
       <c r="AD39">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AF39">
-        <v>2.04</v>
+        <v>1.66</v>
       </c>
       <c r="AG39">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.23</v>
+        <v>1.99</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="O50">
-        <v>4.32</v>
+        <v>4.1</v>
       </c>
       <c r="P50">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8788,31 +8788,31 @@
         <v>1.82</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q52">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="R52">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T52">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="U52">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="V52">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W52">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -8821,7 +8821,7 @@
         <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="AA52">
         <v>2</v>
@@ -8833,10 +8833,10 @@
         <v>3.05</v>
       </c>
       <c r="AD52">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE52">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
         <v>1.9</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
         <v>2</v>
@@ -10261,34 +10261,34 @@
         <v>2.85</v>
       </c>
       <c r="Q61">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="R61">
         <v>2.25</v>
       </c>
       <c r="S61">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U61">
         <v>2.32</v>
       </c>
       <c r="V61">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="W61">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="AA61">
         <v>1.7</v>
@@ -10297,13 +10297,13 @@
         <v>2.05</v>
       </c>
       <c r="AC61">
-        <v>2.74</v>
+        <v>2.17</v>
       </c>
       <c r="AD61">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="AE61">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AF61">
         <v>1.57</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="O2">
         <v>3.55</v>
       </c>
       <c r="P2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q2">
         <v>2.43</v>
@@ -665,7 +665,7 @@
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.21</v>
@@ -680,7 +680,7 @@
         <v>2.08</v>
       </c>
       <c r="AC2">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="AD2">
         <v>1.45</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="P10">
         <v>9.4</v>
@@ -2757,10 +2757,10 @@
         <v>1.24</v>
       </c>
       <c r="O15">
+        <v>4.8</v>
+      </c>
+      <c r="P15">
         <v>5.75</v>
-      </c>
-      <c r="P15">
-        <v>7.5</v>
       </c>
       <c r="Q15">
         <v>1.62</v>
@@ -2772,22 +2772,22 @@
         <v>1.2</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U15">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V15">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z15">
         <v>5.75</v>
@@ -2799,16 +2799,16 @@
         <v>2.75</v>
       </c>
       <c r="AC15">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AD15">
         <v>1.61</v>
       </c>
       <c r="AE15">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF15">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AG15">
         <v>1.97</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK15">
-        <v>3.52</v>
+        <v>2.74</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK30">
         <v>2</v>
@@ -5419,7 +5419,7 @@
         <v>1.38</v>
       </c>
       <c r="AG31">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G32">
@@ -5528,61 +5528,61 @@
         <v>2.55</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="Q32">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="U32">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="V32">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="W32">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z32">
-        <v>4.33</v>
+        <v>5.45</v>
       </c>
       <c r="AA32">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AB32">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="AC32">
-        <v>2.43</v>
+        <v>2.06</v>
       </c>
       <c r="AD32">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AE32">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AG32">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
         <v>1.44</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
         <v>2.37</v>
       </c>
       <c r="Q34">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T34">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="U34">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="V34">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>5.45</v>
+        <v>4.33</v>
       </c>
       <c r="AA34">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="AB34">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="AC34">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="AD34">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AE34">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF34">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AG34">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
         <v>1.44</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O35">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="P35">
         <v>6</v>
@@ -6250,7 +6250,7 @@
         <v>1.4</v>
       </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>4.5</v>
       </c>
       <c r="O38">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
         <v>1.81</v>
@@ -6672,7 +6672,7 @@
         <v>3.76</v>
       </c>
       <c r="P39">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q39">
         <v>2.38</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
         <v>1.99</v>
@@ -7973,7 +7973,7 @@
         <v>1.11</v>
       </c>
       <c r="O47">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P47">
         <v>20</v>
@@ -7991,10 +7991,10 @@
         <v>6</v>
       </c>
       <c r="U47">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V47">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="W47">
         <v>1.41</v>
@@ -8009,22 +8009,22 @@
         <v>11</v>
       </c>
       <c r="AA47">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AB47">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AC47">
         <v>1.36</v>
       </c>
       <c r="AD47">
-        <v>3.01</v>
+        <v>2.84</v>
       </c>
       <c r="AE47">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AF47">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG47">
         <v>2</v>
@@ -8142,7 +8142,7 @@
         <v>2.3</v>
       </c>
       <c r="Q48">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="R48">
         <v>2.13</v>
@@ -8154,10 +8154,10 @@
         <v>2.88</v>
       </c>
       <c r="U48">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="V48">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
         <v>1.08</v>
@@ -8175,7 +8175,7 @@
         <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC48">
         <v>2.96</v>
@@ -8190,7 +8190,7 @@
         <v>1.7</v>
       </c>
       <c r="AG48">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -644,7 +644,7 @@
         <v>3.6</v>
       </c>
       <c r="Q2">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
         <v>2.17</v>
@@ -653,7 +653,7 @@
         <v>1.28</v>
       </c>
       <c r="T2">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U2">
         <v>2.5</v>
@@ -662,13 +662,13 @@
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z2">
         <v>4.1</v>
@@ -692,7 +692,7 @@
         <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
+        <v>1.31</v>
+      </c>
+      <c r="O10">
+        <v>5</v>
+      </c>
+      <c r="P10">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="Q10">
+        <v>1.75</v>
+      </c>
+      <c r="R10">
+        <v>2.63</v>
+      </c>
+      <c r="S10">
         <v>1.33</v>
       </c>
-      <c r="O10">
-        <v>4.84</v>
-      </c>
-      <c r="P10">
-        <v>9.4</v>
-      </c>
-      <c r="Q10">
-        <v>1.84</v>
-      </c>
-      <c r="R10">
-        <v>2.34</v>
-      </c>
-      <c r="S10">
-        <v>1.4</v>
-      </c>
       <c r="T10">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.81</v>
+        <v>2.51</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>3.36</v>
+        <v>3.98</v>
       </c>
       <c r="AA10">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AB10">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AC10">
-        <v>3.05</v>
+        <v>2.71</v>
       </c>
       <c r="AD10">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>2.29</v>
+        <v>2.02</v>
       </c>
       <c r="AG10">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q11">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="R11">
         <v>1.99</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="T11">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="U11">
         <v>3.14</v>
@@ -2144,7 +2144,7 @@
         <v>2.12</v>
       </c>
       <c r="AB11">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AC11">
         <v>3.66</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AK11">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2941,10 +2941,10 @@
         <v>2.63</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -2956,10 +2956,10 @@
         <v>3.7</v>
       </c>
       <c r="AA16">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AB16">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
         <v>2.95</v>
@@ -2971,10 +2971,10 @@
         <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
         <v>3.8</v>
@@ -4882,10 +4882,10 @@
         <v>3.3</v>
       </c>
       <c r="Q28">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R28">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="S28">
         <v>1.2</v>
@@ -4897,7 +4897,7 @@
         <v>2.04</v>
       </c>
       <c r="V28">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W28">
         <v>1.17</v>
@@ -4906,31 +4906,31 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z28">
-        <v>6.14</v>
+        <v>5.65</v>
       </c>
       <c r="AA28">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AB28">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="AC28">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD28">
         <v>1.76</v>
       </c>
       <c r="AE28">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AF28">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AG28">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.31</v>
       </c>
       <c r="AK28">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>1.6</v>
       </c>
       <c r="AB29">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC29">
         <v>2.25</v>
@@ -6343,10 +6343,10 @@
         <v>2.16</v>
       </c>
       <c r="O37">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P37">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q37">
         <v>2.7</v>
@@ -6355,10 +6355,10 @@
         <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
         <v>2.48</v>
@@ -6506,10 +6506,10 @@
         <v>4.5</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P38">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q38">
         <v>5.2</v>
@@ -6521,7 +6521,7 @@
         <v>1.49</v>
       </c>
       <c r="T38">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="U38">
         <v>3.32</v>
@@ -6542,7 +6542,7 @@
         <v>2.69</v>
       </c>
       <c r="AA38">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="AB38">
         <v>1.68</v>
@@ -6560,7 +6560,7 @@
         <v>2.04</v>
       </c>
       <c r="AG38">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6669,10 +6669,10 @@
         <v>1.84</v>
       </c>
       <c r="O39">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q39">
         <v>2.38</v>
@@ -6723,7 +6723,7 @@
         <v>1.66</v>
       </c>
       <c r="AG39">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>4.8</v>
       </c>
       <c r="Q50">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R50">
         <v>2.4</v>
@@ -8486,7 +8486,7 @@
         <v>1.55</v>
       </c>
       <c r="W50">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8495,13 +8495,13 @@
         <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="AA50">
         <v>1.57</v>
       </c>
       <c r="AB50">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AC50">
         <v>2.41</v>
@@ -8532,7 +8532,7 @@
         <v>1.15</v>
       </c>
       <c r="AK50">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -10261,10 +10261,10 @@
         <v>2.85</v>
       </c>
       <c r="Q61">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="R61">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S61">
         <v>1.2</v>
@@ -10288,19 +10288,19 @@
         <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA61">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AB61">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="AC61">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AD61">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE61">
         <v>1.24</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL61">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -807,55 +807,55 @@
         <v>3.3</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1130,7 +1130,7 @@
         <v>2.75</v>
       </c>
       <c r="P5">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="Q5">
         <v>3.71</v>
@@ -1142,13 +1142,13 @@
         <v>1.52</v>
       </c>
       <c r="T5">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="U5">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
         <v>1.01</v>
@@ -1172,13 +1172,13 @@
         <v>4.5</v>
       </c>
       <c r="AD5">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE5">
         <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG5">
         <v>1.69</v>
@@ -1197,7 +1197,7 @@
         <v>1.44</v>
       </c>
       <c r="AK5">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>1.45</v>
       </c>
       <c r="Q16">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2950,16 +2950,16 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="AA16">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC16">
         <v>2.95</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="O26">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="P26">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q26">
-        <v>6.1</v>
+        <v>6.37</v>
       </c>
       <c r="R26">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S26">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U26">
         <v>3.3</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
         <v>1.03</v>
@@ -4580,13 +4580,13 @@
         <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z26">
         <v>2.59</v>
       </c>
       <c r="AA26">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AB26">
         <v>1.57</v>
@@ -4601,7 +4601,7 @@
         <v>1.02</v>
       </c>
       <c r="AF26">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG26">
         <v>1.6</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4713,37 +4713,37 @@
         <v>7.5</v>
       </c>
       <c r="O27">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q27">
         <v>7</v>
       </c>
       <c r="R27">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="S27">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U27">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V27">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z27">
         <v>2.79</v>
@@ -4752,22 +4752,22 @@
         <v>2.25</v>
       </c>
       <c r="AB27">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC27">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD27">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE27">
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AG27">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O28">
         <v>3.8</v>
@@ -4891,7 +4891,7 @@
         <v>1.2</v>
       </c>
       <c r="T28">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U28">
         <v>2.04</v>
@@ -4924,7 +4924,7 @@
         <v>1.76</v>
       </c>
       <c r="AE28">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF28">
         <v>1.38</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="O31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P31">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q31">
         <v>1.91</v>
@@ -5377,16 +5377,16 @@
         <v>2.7</v>
       </c>
       <c r="S31">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T31">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U31">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V31">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W31">
         <v>1.2</v>
@@ -5398,28 +5398,28 @@
         <v>1.05</v>
       </c>
       <c r="Z31">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA31">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AB31">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AC31">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD31">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AE31">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AF31">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AG31">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK31">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P32">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="Q32">
-        <v>2.88</v>
+        <v>3.29</v>
       </c>
       <c r="R32">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T32">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U32">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="V32">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
+        <v>1.15</v>
+      </c>
+      <c r="Z32">
+        <v>4.8</v>
+      </c>
+      <c r="AA32">
+        <v>1.52</v>
+      </c>
+      <c r="AB32">
+        <v>2.41</v>
+      </c>
+      <c r="AC32">
+        <v>2.21</v>
+      </c>
+      <c r="AD32">
+        <v>1.59</v>
+      </c>
+      <c r="AE32">
+        <v>1.21</v>
+      </c>
+      <c r="AF32">
+        <v>1.33</v>
+      </c>
+      <c r="AG32">
+        <v>2.2</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.08</v>
       </c>
-      <c r="Z32">
-        <v>5.45</v>
-      </c>
-      <c r="AA32">
-        <v>1.39</v>
-      </c>
-      <c r="AB32">
-        <v>2.59</v>
-      </c>
-      <c r="AC32">
-        <v>2.06</v>
-      </c>
-      <c r="AD32">
-        <v>1.68</v>
-      </c>
-      <c r="AE32">
-        <v>1.25</v>
-      </c>
-      <c r="AF32">
-        <v>1.37</v>
-      </c>
-      <c r="AG32">
-        <v>2.75</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.2</v>
-      </c>
       <c r="AK32">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>1.99</v>
+        <v>2.9</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="U35">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y35">
+        <v>1.38</v>
+      </c>
+      <c r="Z35">
+        <v>2.76</v>
+      </c>
+      <c r="AA35">
+        <v>2.28</v>
+      </c>
+      <c r="AB35">
+        <v>1.6</v>
+      </c>
+      <c r="AC35">
+        <v>3.7</v>
+      </c>
+      <c r="AD35">
         <v>1.22</v>
       </c>
-      <c r="Z35">
-        <v>4</v>
-      </c>
-      <c r="AA35">
-        <v>1.72</v>
-      </c>
-      <c r="AB35">
-        <v>2.1</v>
-      </c>
-      <c r="AC35">
-        <v>2.8</v>
-      </c>
-      <c r="AD35">
-        <v>1.38</v>
-      </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK35">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q36">
-        <v>2.9</v>
+        <v>1.99</v>
       </c>
       <c r="R36">
+        <v>2.5</v>
+      </c>
+      <c r="S36">
+        <v>1.3</v>
+      </c>
+      <c r="T36">
+        <v>3.2</v>
+      </c>
+      <c r="U36">
+        <v>2.49</v>
+      </c>
+      <c r="V36">
+        <v>1.53</v>
+      </c>
+      <c r="W36">
+        <v>1.11</v>
+      </c>
+      <c r="X36">
+        <v>1</v>
+      </c>
+      <c r="Y36">
+        <v>1.22</v>
+      </c>
+      <c r="Z36">
+        <v>4</v>
+      </c>
+      <c r="AA36">
+        <v>1.72</v>
+      </c>
+      <c r="AB36">
+        <v>2.1</v>
+      </c>
+      <c r="AC36">
+        <v>2.8</v>
+      </c>
+      <c r="AD36">
+        <v>1.38</v>
+      </c>
+      <c r="AE36">
+        <v>1.15</v>
+      </c>
+      <c r="AF36">
+        <v>1.85</v>
+      </c>
+      <c r="AG36">
         <v>1.95</v>
       </c>
-      <c r="S36">
-        <v>1.42</v>
-      </c>
-      <c r="T36">
-        <v>2.65</v>
-      </c>
-      <c r="U36">
-        <v>2.88</v>
-      </c>
-      <c r="V36">
-        <v>1.36</v>
-      </c>
-      <c r="W36">
-        <v>1.07</v>
-      </c>
-      <c r="X36">
-        <v>1.08</v>
-      </c>
-      <c r="Y36">
-        <v>1.38</v>
-      </c>
-      <c r="Z36">
-        <v>2.76</v>
-      </c>
-      <c r="AA36">
-        <v>2.28</v>
-      </c>
-      <c r="AB36">
-        <v>1.6</v>
-      </c>
-      <c r="AC36">
-        <v>3.84</v>
-      </c>
-      <c r="AD36">
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.22</v>
       </c>
-      <c r="AE36">
-        <v>1.06</v>
-      </c>
-      <c r="AF36">
-        <v>1.9</v>
-      </c>
-      <c r="AG36">
-        <v>1.83</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.4</v>
-      </c>
       <c r="AK36">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6355,10 +6355,10 @@
         <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
         <v>2.48</v>
@@ -6367,7 +6367,7 @@
         <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6832,61 +6832,61 @@
         <v>1.85</v>
       </c>
       <c r="O40">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P40">
-        <v>4.81</v>
+        <v>4.33</v>
       </c>
       <c r="Q40">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="R40">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="S40">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="T40">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U40">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="V40">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W40">
         <v>1.03</v>
       </c>
       <c r="X40">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y40">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Z40">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AA40">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="AB40">
         <v>1.34</v>
       </c>
       <c r="AC40">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AD40">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AE40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AG40">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="O47">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="P47">
         <v>20</v>
@@ -7991,10 +7991,10 @@
         <v>6</v>
       </c>
       <c r="U47">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="V47">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="W47">
         <v>1.41</v>
@@ -8009,7 +8009,7 @@
         <v>11</v>
       </c>
       <c r="AA47">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AB47">
         <v>5.5</v>
@@ -8024,7 +8024,7 @@
         <v>1.98</v>
       </c>
       <c r="AF47">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG47">
         <v>2</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="Q48">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="R48">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S48">
         <v>1.36</v>
@@ -8154,10 +8154,10 @@
         <v>2.88</v>
       </c>
       <c r="U48">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W48">
         <v>1.08</v>
@@ -8172,13 +8172,13 @@
         <v>3.4</v>
       </c>
       <c r="AA48">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AB48">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC48">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AD48">
         <v>1.33</v>
@@ -8206,7 +8206,7 @@
         <v>1.62</v>
       </c>
       <c r="AK48">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>7</v>
+        <v>8.32</v>
       </c>
       <c r="O49">
         <v>4.2</v>
@@ -8465,13 +8465,13 @@
         <v>4.1</v>
       </c>
       <c r="P50">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="Q50">
         <v>2.02</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S50">
         <v>1.22</v>
@@ -8483,7 +8483,7 @@
         <v>2.28</v>
       </c>
       <c r="V50">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
         <v>1.14</v>
@@ -8504,10 +8504,10 @@
         <v>2.25</v>
       </c>
       <c r="AC50">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AD50">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AE50">
         <v>1.14</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
         <v>2.25</v>
@@ -10261,13 +10261,13 @@
         <v>2.85</v>
       </c>
       <c r="Q61">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="R61">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T61">
         <v>3.1</v>
@@ -10279,7 +10279,7 @@
         <v>1.7</v>
       </c>
       <c r="W61">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10288,22 +10288,22 @@
         <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA61">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB61">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AC61">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AD61">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE61">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF61">
         <v>1.57</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL61">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="O14">
         <v>4</v>
       </c>
       <c r="P14">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2766,19 +2766,19 @@
         <v>1.62</v>
       </c>
       <c r="R15">
-        <v>2.95</v>
+        <v>2.54</v>
       </c>
       <c r="S15">
         <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="U15">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W15">
         <v>1.14</v>
@@ -2787,13 +2787,13 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z15">
         <v>5.75</v>
       </c>
       <c r="AA15">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AB15">
         <v>2.75</v>
@@ -2827,7 +2827,7 @@
         <v>1.11</v>
       </c>
       <c r="AK15">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.74</v>
+        <v>2.85</v>
       </c>
       <c r="O30">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.8</v>
+        <v>2.14</v>
       </c>
       <c r="Q30">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="R30">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="S30">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="U30">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="V30">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="W30">
+        <v>1.15</v>
+      </c>
+      <c r="X30">
+        <v>1.02</v>
+      </c>
+      <c r="Y30">
+        <v>1.16</v>
+      </c>
+      <c r="Z30">
+        <v>4.92</v>
+      </c>
+      <c r="AA30">
+        <v>1.53</v>
+      </c>
+      <c r="AB30">
+        <v>2.55</v>
+      </c>
+      <c r="AC30">
+        <v>2.21</v>
+      </c>
+      <c r="AD30">
+        <v>1.59</v>
+      </c>
+      <c r="AE30">
         <v>1.21</v>
       </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.07</v>
-      </c>
-      <c r="Z30">
-        <v>5.85</v>
-      </c>
-      <c r="AA30">
+      <c r="AF30">
         <v>1.33</v>
       </c>
-      <c r="AB30">
-        <v>2.83</v>
-      </c>
-      <c r="AC30">
-        <v>1.9</v>
-      </c>
-      <c r="AD30">
-        <v>1.8</v>
-      </c>
-      <c r="AE30">
-        <v>1.31</v>
-      </c>
-      <c r="AF30">
-        <v>1.39</v>
-      </c>
       <c r="AG30">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
+        <v>2.55</v>
+      </c>
+      <c r="O31">
+        <v>3.5</v>
+      </c>
+      <c r="P31">
+        <v>2.5</v>
+      </c>
+      <c r="Q31">
+        <v>2.96</v>
+      </c>
+      <c r="R31">
+        <v>2.3</v>
+      </c>
+      <c r="S31">
+        <v>1.25</v>
+      </c>
+      <c r="T31">
+        <v>3.4</v>
+      </c>
+      <c r="U31">
+        <v>2.3</v>
+      </c>
+      <c r="V31">
         <v>1.53</v>
       </c>
-      <c r="O31">
-        <v>4.2</v>
-      </c>
-      <c r="P31">
-        <v>4.7</v>
-      </c>
-      <c r="Q31">
-        <v>1.91</v>
-      </c>
-      <c r="R31">
-        <v>2.7</v>
-      </c>
-      <c r="S31">
-        <v>1.2</v>
-      </c>
-      <c r="T31">
-        <v>4.4</v>
-      </c>
-      <c r="U31">
-        <v>1.91</v>
-      </c>
-      <c r="V31">
-        <v>1.75</v>
-      </c>
       <c r="W31">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA31">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="AC31">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="AD31">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AE31">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AG31">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P33">
-        <v>2.37</v>
+        <v>4.48</v>
       </c>
       <c r="Q33">
-        <v>2.93</v>
+        <v>1.91</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S33">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="T33">
-        <v>3.48</v>
+        <v>4.4</v>
       </c>
       <c r="U33">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="V33">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z33">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="AA33">
-        <v>1.59</v>
+        <v>1.31</v>
       </c>
       <c r="AB33">
-        <v>2.21</v>
+        <v>2.92</v>
       </c>
       <c r="AC33">
-        <v>2.43</v>
+        <v>1.88</v>
       </c>
       <c r="AD33">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AF33">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AG33">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>2.31</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="R35">
         <v>1.95</v>
@@ -6032,7 +6032,7 @@
         <v>1.42</v>
       </c>
       <c r="T35">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="U35">
         <v>2.88</v>
@@ -6059,10 +6059,10 @@
         <v>1.6</v>
       </c>
       <c r="AC35">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="AD35">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE35">
         <v>1.06</v>
@@ -6071,7 +6071,7 @@
         <v>1.9</v>
       </c>
       <c r="AG35">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="O36">
-        <v>4.26</v>
+        <v>4.5</v>
       </c>
       <c r="P36">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S36">
         <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
         <v>2.49</v>
@@ -6207,7 +6207,7 @@
         <v>1.11</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.22</v>
@@ -6225,7 +6225,7 @@
         <v>2.8</v>
       </c>
       <c r="AD36">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE36">
         <v>1.15</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK36">
         <v>2.5</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O37">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q37">
         <v>2.7</v>
@@ -6355,13 +6355,13 @@
         <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U37">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="V37">
         <v>1.46</v>
@@ -6379,25 +6379,25 @@
         <v>3.95</v>
       </c>
       <c r="AA37">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB37">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AD37">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE37">
         <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6868,7 +6868,7 @@
         <v>2.22</v>
       </c>
       <c r="AA40">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="AB40">
         <v>1.34</v>
@@ -6883,7 +6883,7 @@
         <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AG40">
         <v>1.5</v>
@@ -7973,13 +7973,13 @@
         <v>1.09</v>
       </c>
       <c r="O47">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="P47">
         <v>20</v>
       </c>
       <c r="Q47">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="R47">
         <v>3.82</v>
@@ -7991,13 +7991,13 @@
         <v>6</v>
       </c>
       <c r="U47">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V47">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="W47">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="X47">
         <v>1</v>
@@ -8009,25 +8009,25 @@
         <v>11</v>
       </c>
       <c r="AA47">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AB47">
         <v>5.5</v>
       </c>
       <c r="AC47">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AD47">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AE47">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AF47">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.05</v>
       </c>
       <c r="AK47">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8139,31 +8139,31 @@
         <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q48">
-        <v>3.88</v>
+        <v>3.97</v>
       </c>
       <c r="R48">
         <v>2.15</v>
       </c>
       <c r="S48">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T48">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U48">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W48">
         <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.26</v>
@@ -8172,13 +8172,13 @@
         <v>3.4</v>
       </c>
       <c r="AA48">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AB48">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC48">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AD48">
         <v>1.33</v>
@@ -8206,7 +8206,7 @@
         <v>1.62</v>
       </c>
       <c r="AK48">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="O50">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P50">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q50">
         <v>2.02</v>
@@ -8474,34 +8474,34 @@
         <v>2.45</v>
       </c>
       <c r="S50">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V50">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W50">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z50">
-        <v>4.54</v>
+        <v>4.65</v>
       </c>
       <c r="AA50">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB50">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC50">
         <v>2.49</v>
@@ -8510,13 +8510,13 @@
         <v>1.51</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK50">
         <v>2.25</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P52">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q52">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="R52">
         <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T52">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="U52">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="V52">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>3.44</v>
+        <v>3.66</v>
       </c>
       <c r="AA52">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB52">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AC52">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="AD52">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AG52">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK52">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10261,22 +10261,22 @@
         <v>2.85</v>
       </c>
       <c r="Q61">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R61">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="S61">
         <v>1.22</v>
       </c>
       <c r="T61">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="U61">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="V61">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W61">
         <v>1.18</v>
@@ -10288,22 +10288,22 @@
         <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AA61">
         <v>1.42</v>
       </c>
       <c r="AB61">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC61">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD61">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE61">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF61">
         <v>1.57</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK61">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,55 +10750,55 @@
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL64">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G22">
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="Q24">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>3.26</v>
+      </c>
+      <c r="R25">
+        <v>2.02</v>
+      </c>
+      <c r="S25">
+        <v>1.36</v>
+      </c>
+      <c r="T25">
+        <v>2.88</v>
+      </c>
+      <c r="U25">
         <v>2.75</v>
       </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O40">
         <v>2.9</v>
@@ -6844,7 +6844,7 @@
         <v>1.81</v>
       </c>
       <c r="S40">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="T40">
         <v>2.2</v>
@@ -6862,7 +6862,7 @@
         <v>1.08</v>
       </c>
       <c r="Y40">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z40">
         <v>2.22</v>
@@ -6883,7 +6883,7 @@
         <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AG40">
         <v>1.5</v>
@@ -6902,7 +6902,7 @@
         <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="O50">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P50">
         <v>4.8</v>
       </c>
       <c r="Q50">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R50">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S50">
         <v>1.25</v>
@@ -8480,43 +8480,43 @@
         <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="V50">
+        <v>1.61</v>
+      </c>
+      <c r="W50">
+        <v>1.11</v>
+      </c>
+      <c r="X50">
+        <v>1.02</v>
+      </c>
+      <c r="Y50">
+        <v>1.1</v>
+      </c>
+      <c r="Z50">
+        <v>5</v>
+      </c>
+      <c r="AA50">
+        <v>1.45</v>
+      </c>
+      <c r="AB50">
+        <v>2.41</v>
+      </c>
+      <c r="AC50">
+        <v>2.27</v>
+      </c>
+      <c r="AD50">
+        <v>1.57</v>
+      </c>
+      <c r="AE50">
+        <v>1.19</v>
+      </c>
+      <c r="AF50">
         <v>1.56</v>
       </c>
-      <c r="W50">
-        <v>1.1</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.12</v>
-      </c>
-      <c r="Z50">
-        <v>4.65</v>
-      </c>
-      <c r="AA50">
-        <v>1.61</v>
-      </c>
-      <c r="AB50">
-        <v>2.27</v>
-      </c>
-      <c r="AC50">
-        <v>2.49</v>
-      </c>
-      <c r="AD50">
-        <v>1.51</v>
-      </c>
-      <c r="AE50">
-        <v>1.15</v>
-      </c>
-      <c r="AF50">
-        <v>1.6</v>
-      </c>
       <c r="AG50">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.11</v>
       </c>
       <c r="AK50">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O52">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="P52">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q52">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="R52">
         <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="V52">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W52">
         <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
         <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="AA52">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB52">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC52">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AD52">
         <v>1.32</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF52">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG52">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="O61">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P61">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="Q61">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R61">
         <v>2.47</v>
@@ -10270,16 +10270,16 @@
         <v>1.22</v>
       </c>
       <c r="T61">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V61">
         <v>1.65</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10303,7 +10303,7 @@
         <v>1.64</v>
       </c>
       <c r="AE61">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF61">
         <v>1.57</v>
@@ -10590,7 +10590,7 @@
         <v>2.24</v>
       </c>
       <c r="R63">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S63">
         <v>1.24</v>
@@ -10762,10 +10762,10 @@
         <v>3.2</v>
       </c>
       <c r="U64">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="V64">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W64">
         <v>1.11</v>
@@ -10786,7 +10786,7 @@
         <v>2.17</v>
       </c>
       <c r="AC64">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="AD64">
         <v>1.41</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -635,46 +635,46 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="O2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
       </c>
       <c r="R2">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
         <v>1.28</v>
       </c>
       <c r="T2">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U2">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V2">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="AA2">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB2">
         <v>2.08</v>
@@ -683,10 +683,10 @@
         <v>2.59</v>
       </c>
       <c r="AD2">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AE2">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
         <v>1.57</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P5">
         <v>2.55</v>
       </c>
       <c r="Q5">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="R5">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S5">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
         <v>3.42</v>
       </c>
       <c r="V5">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>1.1</v>
       </c>
       <c r="Y5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z5">
         <v>2.43</v>
       </c>
       <c r="AA5">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="AB5">
         <v>1.51</v>
       </c>
       <c r="AC5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD5">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE5">
         <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AK5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -4550,28 +4550,28 @@
         <v>5.25</v>
       </c>
       <c r="O26">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="P26">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q26">
-        <v>6.37</v>
+        <v>6.16</v>
       </c>
       <c r="R26">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T26">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U26">
         <v>3.3</v>
       </c>
       <c r="V26">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W26">
         <v>1.03</v>
@@ -4580,31 +4580,31 @@
         <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z26">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AA26">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AB26">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC26">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD26">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF26">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="O27">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P27">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q27">
         <v>7</v>
       </c>
       <c r="R27">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="S27">
         <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="U27">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W27">
         <v>1.06</v>
       </c>
       <c r="X27">
+        <v>1.06</v>
+      </c>
+      <c r="Y27">
+        <v>1.45</v>
+      </c>
+      <c r="Z27">
+        <v>2.71</v>
+      </c>
+      <c r="AA27">
+        <v>2.37</v>
+      </c>
+      <c r="AB27">
+        <v>1.54</v>
+      </c>
+      <c r="AC27">
+        <v>4.75</v>
+      </c>
+      <c r="AD27">
+        <v>1.15</v>
+      </c>
+      <c r="AE27">
         <v>1.03</v>
-      </c>
-      <c r="Y27">
-        <v>1.37</v>
-      </c>
-      <c r="Z27">
-        <v>2.79</v>
-      </c>
-      <c r="AA27">
-        <v>2.25</v>
-      </c>
-      <c r="AB27">
-        <v>1.53</v>
-      </c>
-      <c r="AC27">
-        <v>4.5</v>
-      </c>
-      <c r="AD27">
-        <v>1.17</v>
-      </c>
-      <c r="AE27">
-        <v>1.01</v>
       </c>
       <c r="AF27">
         <v>2.55</v>
       </c>
       <c r="AG27">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>8.32</v>
+        <v>9</v>
       </c>
       <c r="O49">
         <v>4.2</v>
@@ -8468,7 +8468,7 @@
         <v>4.8</v>
       </c>
       <c r="Q50">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R50">
         <v>2.47</v>
@@ -8480,10 +8480,10 @@
         <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="V50">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W50">
         <v>1.11</v>
@@ -8498,25 +8498,25 @@
         <v>5</v>
       </c>
       <c r="AA50">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AB50">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AC50">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD50">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE50">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG50">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK50">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -10264,7 +10264,7 @@
         <v>2.95</v>
       </c>
       <c r="R61">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="S61">
         <v>1.22</v>
@@ -10273,7 +10273,7 @@
         <v>4</v>
       </c>
       <c r="U61">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V61">
         <v>1.65</v>
@@ -10325,7 +10325,7 @@
         <v>1.57</v>
       </c>
       <c r="AK61">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL61">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q3">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T3">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U3">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -831,47 +831,47 @@
         <v>1.03</v>
       </c>
       <c r="Y3">
+        <v>1.37</v>
+      </c>
+      <c r="Z3">
+        <v>2.94</v>
+      </c>
+      <c r="AA3">
+        <v>2.22</v>
+      </c>
+      <c r="AB3">
+        <v>1.64</v>
+      </c>
+      <c r="AC3">
+        <v>3.85</v>
+      </c>
+      <c r="AD3">
+        <v>1.18</v>
+      </c>
+      <c r="AE3">
+        <v>1.02</v>
+      </c>
+      <c r="AF3">
+        <v>1.87</v>
+      </c>
+      <c r="AG3">
+        <v>1.83</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.33</v>
       </c>
-      <c r="Z3">
-        <v>2.81</v>
-      </c>
-      <c r="AA3">
-        <v>2.19</v>
-      </c>
-      <c r="AB3">
-        <v>1.65</v>
-      </c>
-      <c r="AC3">
-        <v>3.8</v>
-      </c>
-      <c r="AD3">
-        <v>1.19</v>
-      </c>
-      <c r="AE3">
-        <v>1.03</v>
-      </c>
-      <c r="AF3">
-        <v>1.86</v>
-      </c>
-      <c r="AG3">
-        <v>1.84</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.32</v>
-      </c>
       <c r="AK3">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="P10">
-        <v>8.449999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Q10">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R10">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="S10">
         <v>1.33</v>
@@ -1975,22 +1975,22 @@
         <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AA10">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB10">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="AD10">
         <v>1.44</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF10">
         <v>2.02</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
         <v>2.41</v>
       </c>
       <c r="Q11">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="R11">
         <v>1.99</v>
@@ -2123,10 +2123,10 @@
         <v>2.6</v>
       </c>
       <c r="U11">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
         <v>1.03</v>
@@ -2135,19 +2135,19 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z11">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="AA11">
         <v>2.12</v>
       </c>
       <c r="AB11">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC11">
-        <v>3.66</v>
+        <v>3.77</v>
       </c>
       <c r="AD11">
         <v>1.26</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AK11">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>4.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK15">
         <v>2.77</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O16">
         <v>3.83</v>
@@ -2929,52 +2929,52 @@
         <v>5</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="U16">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>3.83</v>
+        <v>4.42</v>
       </c>
       <c r="AA16">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB16">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="AC16">
         <v>2.95</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O20">
         <v>2.9</v>
       </c>
       <c r="P20">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q20">
         <v>3.5</v>
@@ -3590,10 +3590,10 @@
         <v>2.36</v>
       </c>
       <c r="U20">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="V20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W20">
         <v>1.01</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P23">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q23">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="R23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
         <v>1.36</v>
@@ -4097,10 +4097,10 @@
         <v>3.14</v>
       </c>
       <c r="AA23">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB23">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC23">
         <v>3.2</v>
@@ -4112,10 +4112,10 @@
         <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG23">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4396,13 +4396,13 @@
         <v>3.26</v>
       </c>
       <c r="R25">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T25">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="U25">
         <v>2.75</v>
@@ -4423,13 +4423,13 @@
         <v>2.92</v>
       </c>
       <c r="AA25">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB25">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC25">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD25">
         <v>1.22</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK25">
         <v>1.4</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P28">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
         <v>2.4</v>
       </c>
       <c r="R28">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S28">
         <v>1.2</v>
@@ -4921,13 +4921,13 @@
         <v>2.08</v>
       </c>
       <c r="AD28">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE28">
         <v>1.29</v>
       </c>
       <c r="AF28">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG28">
         <v>2.81</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
         <v>1.8</v>
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="O29">
         <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q29">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R29">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S29">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T29">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="V29">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X29">
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z29">
         <v>5</v>
       </c>
       <c r="AA29">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB29">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AC29">
         <v>2.25</v>
       </c>
       <c r="AD29">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AE29">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF29">
+        <v>1.36</v>
+      </c>
+      <c r="AG29">
+        <v>2.75</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.26</v>
+      </c>
+      <c r="AK29">
         <v>1.44</v>
-      </c>
-      <c r="AG29">
-        <v>2.6</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.23</v>
-      </c>
-      <c r="AK29">
-        <v>1.41</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5223,25 +5223,25 @@
         <v>2.18</v>
       </c>
       <c r="V30">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z30">
-        <v>4.92</v>
+        <v>4.95</v>
       </c>
       <c r="AA30">
         <v>1.53</v>
       </c>
       <c r="AB30">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AC30">
         <v>2.21</v>
@@ -5253,10 +5253,10 @@
         <v>1.21</v>
       </c>
       <c r="AF30">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AG30">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5368,13 +5368,13 @@
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q31">
         <v>2.96</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
         <v>1.25</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
         <v>1.44</v>
@@ -5691,10 +5691,10 @@
         <v>1.55</v>
       </c>
       <c r="O33">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P33">
-        <v>4.48</v>
+        <v>4.7</v>
       </c>
       <c r="Q33">
         <v>1.91</v>
@@ -5706,16 +5706,16 @@
         <v>1.14</v>
       </c>
       <c r="T33">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U33">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="V33">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="W33">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X33">
         <v>1.01</v>
@@ -5730,19 +5730,19 @@
         <v>1.31</v>
       </c>
       <c r="AB33">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="AC33">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AD33">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AE33">
         <v>1.31</v>
       </c>
       <c r="AF33">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG33">
         <v>2.62</v>
@@ -5854,10 +5854,10 @@
         <v>1.87</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P34">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -5872,10 +5872,10 @@
         <v>3.9</v>
       </c>
       <c r="U34">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="V34">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W34">
         <v>1.17</v>
@@ -5887,28 +5887,28 @@
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>5.3</v>
+        <v>5.44</v>
       </c>
       <c r="AA34">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB34">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AC34">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AD34">
         <v>1.66</v>
       </c>
       <c r="AE34">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF34">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG34">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>1.42</v>
       </c>
       <c r="T35">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U35">
         <v>2.88</v>
@@ -6050,7 +6050,7 @@
         <v>1.38</v>
       </c>
       <c r="Z35">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AA35">
         <v>2.28</v>
@@ -6071,7 +6071,7 @@
         <v>1.9</v>
       </c>
       <c r="AG35">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AK35">
         <v>1.5</v>
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="O36">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="P36">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q36">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R36">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
         <v>2.49</v>
@@ -6210,7 +6210,7 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
         <v>4</v>
@@ -6231,7 +6231,7 @@
         <v>1.15</v>
       </c>
       <c r="AF36">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG36">
         <v>1.95</v>
@@ -6250,7 +6250,7 @@
         <v>1.17</v>
       </c>
       <c r="AK36">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P37">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q37">
         <v>2.7</v>
@@ -6355,19 +6355,19 @@
         <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="V37">
         <v>1.46</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6379,16 +6379,16 @@
         <v>3.95</v>
       </c>
       <c r="AA37">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB37">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC37">
         <v>2.75</v>
       </c>
       <c r="AD37">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE37">
         <v>1.11</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="O38">
         <v>3.48</v>
@@ -6515,7 +6515,7 @@
         <v>5.2</v>
       </c>
       <c r="R38">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="S38">
         <v>1.49</v>
@@ -6542,7 +6542,7 @@
         <v>2.69</v>
       </c>
       <c r="AA38">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AB38">
         <v>1.68</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P39">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q39">
         <v>2.38</v>
@@ -6696,7 +6696,7 @@
         <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.2</v>
@@ -6723,7 +6723,7 @@
         <v>1.66</v>
       </c>
       <c r="AG39">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7973,16 +7973,16 @@
         <v>1.09</v>
       </c>
       <c r="O47">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="P47">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q47">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="R47">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="S47">
         <v>1.09</v>
@@ -7991,10 +7991,10 @@
         <v>6</v>
       </c>
       <c r="U47">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V47">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="W47">
         <v>1.46</v>
@@ -8003,31 +8003,31 @@
         <v>1</v>
       </c>
       <c r="Y47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z47">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA47">
         <v>1.14</v>
       </c>
       <c r="AB47">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AC47">
         <v>1.35</v>
       </c>
       <c r="AD47">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AE47">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AF47">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG47">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK47">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,31 +8133,31 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O48">
         <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q48">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="R48">
         <v>2.15</v>
       </c>
       <c r="S48">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U48">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="V48">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
         <v>1.08</v>
@@ -8166,25 +8166,25 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z48">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA48">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB48">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC48">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="AD48">
         <v>1.33</v>
       </c>
       <c r="AE48">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
         <v>1.7</v>
@@ -8206,7 +8206,7 @@
         <v>1.62</v>
       </c>
       <c r="AK48">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -10590,7 +10590,7 @@
         <v>2.24</v>
       </c>
       <c r="R63">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S63">
         <v>1.24</v>
@@ -10750,22 +10750,22 @@
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R64">
         <v>2.25</v>
       </c>
       <c r="S64">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T64">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U64">
         <v>2.36</v>
       </c>
       <c r="V64">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
         <v>1.11</v>
@@ -10783,13 +10783,13 @@
         <v>1.66</v>
       </c>
       <c r="AB64">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC64">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="AD64">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE64">
         <v>1.12</v>
@@ -10798,7 +10798,7 @@
         <v>1.57</v>
       </c>
       <c r="AG64">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU64"/>
+  <dimension ref="A1:AU62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="O2">
+        <v>3.55</v>
+      </c>
+      <c r="P2">
         <v>3.6</v>
       </c>
-      <c r="P2">
-        <v>3.2</v>
-      </c>
       <c r="Q2">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S2">
         <v>1.28</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G6">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-16 11:00:00</t>
+          <t>2026-09-16 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G8">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-16 12:00:00</t>
+          <t>2026-09-16 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>8.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q10">
-        <v>1.78</v>
+        <v>3.73</v>
       </c>
       <c r="R10">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="U10">
-        <v>2.51</v>
+        <v>3.08</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="Z10">
-        <v>3.96</v>
+        <v>3.21</v>
       </c>
       <c r="AA10">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AB10">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AC10">
-        <v>2.76</v>
+        <v>3.77</v>
       </c>
       <c r="AD10">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AE10">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AG10">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AK10">
-        <v>3.28</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P11">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="Q11">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-16 12:30:00</t>
+          <t>2026-09-16 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G12">
@@ -2261,68 +2261,68 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.88</v>
+        <v>5.45</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-16 12:45:00</t>
+          <t>2026-09-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,68 +2424,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
-        <v>5.45</v>
+        <v>1.59</v>
       </c>
       <c r="O13">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="Q13">
-        <v>5.8</v>
+        <v>2.15</v>
       </c>
       <c r="R13">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>2.87</v>
+        <v>4.4</v>
       </c>
       <c r="AA13">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AB13">
+        <v>2.35</v>
+      </c>
+      <c r="AC13">
+        <v>2.25</v>
+      </c>
+      <c r="AD13">
+        <v>1.55</v>
+      </c>
+      <c r="AE13">
+        <v>1.23</v>
+      </c>
+      <c r="AF13">
         <v>1.57</v>
       </c>
-      <c r="AC13">
-        <v>3.84</v>
-      </c>
-      <c r="AD13">
-        <v>1.18</v>
-      </c>
-      <c r="AE13">
-        <v>1.03</v>
-      </c>
-      <c r="AF13">
-        <v>2.05</v>
-      </c>
       <c r="AG13">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK13">
-        <v>1.07</v>
+        <v>2.23</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G14">
@@ -2587,35 +2587,35 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="P14">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q14">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="R14">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="U14">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="V14">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="W14">
         <v>1.14</v>
@@ -2624,31 +2624,31 @@
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z14">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA14">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AB14">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AC14">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AD14">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AE14">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG14">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AK14">
-        <v>2.23</v>
+        <v>2.77</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.24</v>
+        <v>4.8</v>
       </c>
       <c r="O15">
-        <v>4.8</v>
+        <v>3.83</v>
       </c>
       <c r="P15">
-        <v>5.75</v>
+        <v>1.45</v>
       </c>
       <c r="Q15">
-        <v>1.62</v>
+        <v>4.7</v>
       </c>
       <c r="R15">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="U15">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>5.75</v>
+        <v>4.47</v>
       </c>
       <c r="AA15">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AB15">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="AC15">
-        <v>2.04</v>
+        <v>2.95</v>
       </c>
       <c r="AD15">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AE15">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF15">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AG15">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>2.77</v>
+        <v>1.13</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G16">
@@ -2913,68 +2913,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="O16">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="P16">
-        <v>1.45</v>
+        <v>4</v>
       </c>
       <c r="Q16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-16 13:00:00</t>
+          <t>2026-09-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="O23">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="Q23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>3.26</v>
+      </c>
+      <c r="R24">
+        <v>2.01</v>
+      </c>
+      <c r="S24">
+        <v>1.37</v>
+      </c>
+      <c r="T24">
+        <v>2.71</v>
+      </c>
+      <c r="U24">
         <v>2.75</v>
       </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q25">
-        <v>3.26</v>
+        <v>6.16</v>
       </c>
       <c r="R25">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="S25">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="T25">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="U25">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z25">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AA25">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB25">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC25">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD25">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-16 13:30:00</t>
+          <t>2026-09-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26">
-        <v>5.25</v>
+        <v>1.92</v>
       </c>
       <c r="O26">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="Q26">
-        <v>6.16</v>
+        <v>2.4</v>
       </c>
       <c r="R26">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="S26">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="U26">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="V26">
+        <v>1.73</v>
+      </c>
+      <c r="W26">
+        <v>1.17</v>
+      </c>
+      <c r="X26">
+        <v>1.02</v>
+      </c>
+      <c r="Y26">
+        <v>1.08</v>
+      </c>
+      <c r="Z26">
+        <v>5.65</v>
+      </c>
+      <c r="AA26">
+        <v>1.43</v>
+      </c>
+      <c r="AB26">
+        <v>2.68</v>
+      </c>
+      <c r="AC26">
+        <v>2.08</v>
+      </c>
+      <c r="AD26">
+        <v>1.71</v>
+      </c>
+      <c r="AE26">
         <v>1.29</v>
       </c>
-      <c r="W26">
-        <v>1.03</v>
-      </c>
-      <c r="X26">
-        <v>1.05</v>
-      </c>
-      <c r="Y26">
+      <c r="AF26">
         <v>1.4</v>
       </c>
-      <c r="Z26">
-        <v>2.7</v>
-      </c>
-      <c r="AA26">
-        <v>2.3</v>
-      </c>
-      <c r="AB26">
-        <v>1.6</v>
-      </c>
-      <c r="AC26">
-        <v>4.33</v>
-      </c>
-      <c r="AD26">
-        <v>1.18</v>
-      </c>
-      <c r="AE26">
-        <v>1.03</v>
-      </c>
-      <c r="AF26">
-        <v>2.05</v>
-      </c>
       <c r="AG26">
-        <v>1.7</v>
+        <v>2.81</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G27">
@@ -4706,84 +4706,84 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27">
-        <v>6.5</v>
+        <v>2.65</v>
       </c>
       <c r="O27">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
+        <v>2.25</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>2.5</v>
+      </c>
+      <c r="S27">
+        <v>1.22</v>
+      </c>
+      <c r="T27">
+        <v>4</v>
+      </c>
+      <c r="U27">
+        <v>2.11</v>
+      </c>
+      <c r="V27">
+        <v>1.67</v>
+      </c>
+      <c r="W27">
+        <v>1.17</v>
+      </c>
+      <c r="X27">
+        <v>1.02</v>
+      </c>
+      <c r="Y27">
+        <v>1.09</v>
+      </c>
+      <c r="Z27">
+        <v>5</v>
+      </c>
+      <c r="AA27">
+        <v>1.4</v>
+      </c>
+      <c r="AB27">
+        <v>2.88</v>
+      </c>
+      <c r="AC27">
+        <v>2.25</v>
+      </c>
+      <c r="AD27">
+        <v>1.68</v>
+      </c>
+      <c r="AE27">
+        <v>1.25</v>
+      </c>
+      <c r="AF27">
+        <v>1.36</v>
+      </c>
+      <c r="AG27">
+        <v>2.75</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.26</v>
+      </c>
+      <c r="AK27">
         <v>1.44</v>
-      </c>
-      <c r="Q27">
-        <v>7</v>
-      </c>
-      <c r="R27">
-        <v>2.17</v>
-      </c>
-      <c r="S27">
-        <v>1.44</v>
-      </c>
-      <c r="T27">
-        <v>2.33</v>
-      </c>
-      <c r="U27">
-        <v>3.3</v>
-      </c>
-      <c r="V27">
-        <v>1.29</v>
-      </c>
-      <c r="W27">
-        <v>1.06</v>
-      </c>
-      <c r="X27">
-        <v>1.06</v>
-      </c>
-      <c r="Y27">
-        <v>1.45</v>
-      </c>
-      <c r="Z27">
-        <v>2.71</v>
-      </c>
-      <c r="AA27">
-        <v>2.37</v>
-      </c>
-      <c r="AB27">
-        <v>1.54</v>
-      </c>
-      <c r="AC27">
-        <v>4.75</v>
-      </c>
-      <c r="AD27">
-        <v>1.15</v>
-      </c>
-      <c r="AE27">
-        <v>1.03</v>
-      </c>
-      <c r="AF27">
-        <v>2.55</v>
-      </c>
-      <c r="AG27">
-        <v>1.44</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.25</v>
-      </c>
-      <c r="AK27">
-        <v>1.07</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,84 +4869,84 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28">
-        <v>1.92</v>
+        <v>2.85</v>
       </c>
       <c r="O28">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>3.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q28">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S28">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U28">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="V28">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="W28">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z28">
-        <v>5.65</v>
+        <v>4.95</v>
       </c>
       <c r="AA28">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AB28">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="AC28">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="AD28">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AE28">
+        <v>1.21</v>
+      </c>
+      <c r="AF28">
+        <v>1.42</v>
+      </c>
+      <c r="AG28">
+        <v>2.5</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.29</v>
       </c>
-      <c r="AF28">
+      <c r="AK28">
         <v>1.4</v>
-      </c>
-      <c r="AG28">
-        <v>2.81</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.3</v>
-      </c>
-      <c r="AK28">
-        <v>1.8</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,68 +5032,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O29">
         <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q29">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R29">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="V29">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X29">
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AA29">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AB29">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC29">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AD29">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AE29">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AG29">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
         <v>1.44</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P31">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="Q31">
-        <v>2.96</v>
+        <v>1.91</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T31">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="U31">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z31">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="AB31">
-        <v>2.3</v>
+        <v>3.03</v>
       </c>
       <c r="AC31">
-        <v>2.41</v>
+        <v>1.99</v>
       </c>
       <c r="AD31">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AF31">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK31">
-        <v>1.44</v>
+        <v>2.31</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>1.91</v>
+        <v>3.18</v>
       </c>
       <c r="R33">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="S33">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="T33">
-        <v>4.5</v>
+        <v>2.67</v>
       </c>
       <c r="U33">
-        <v>1.96</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y33">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="Z33">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="AA33">
-        <v>1.31</v>
+        <v>2.28</v>
       </c>
       <c r="AB33">
-        <v>3.03</v>
+        <v>1.6</v>
       </c>
       <c r="AC33">
-        <v>1.99</v>
+        <v>3.84</v>
       </c>
       <c r="AD33">
-        <v>1.83</v>
+        <v>1.21</v>
       </c>
       <c r="AE33">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AG33">
-        <v>2.62</v>
+        <v>1.82</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>2.31</v>
+        <v>1.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="O34">
-        <v>3.85</v>
+        <v>4.46</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q34">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.04</v>
+        <v>2.49</v>
       </c>
       <c r="V34">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W34">
+        <v>1.11</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.19</v>
+      </c>
+      <c r="Z34">
+        <v>4</v>
+      </c>
+      <c r="AA34">
+        <v>1.72</v>
+      </c>
+      <c r="AB34">
+        <v>2.1</v>
+      </c>
+      <c r="AC34">
+        <v>2.8</v>
+      </c>
+      <c r="AD34">
+        <v>1.42</v>
+      </c>
+      <c r="AE34">
+        <v>1.15</v>
+      </c>
+      <c r="AF34">
+        <v>1.86</v>
+      </c>
+      <c r="AG34">
+        <v>1.95</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
         <v>1.17</v>
       </c>
-      <c r="X34">
-        <v>1.02</v>
-      </c>
-      <c r="Y34">
-        <v>1.13</v>
-      </c>
-      <c r="Z34">
-        <v>5.44</v>
-      </c>
-      <c r="AA34">
-        <v>1.46</v>
-      </c>
-      <c r="AB34">
-        <v>2.61</v>
-      </c>
-      <c r="AC34">
-        <v>2.09</v>
-      </c>
-      <c r="AD34">
-        <v>1.66</v>
-      </c>
-      <c r="AE34">
-        <v>1.24</v>
-      </c>
-      <c r="AF34">
-        <v>1.42</v>
-      </c>
-      <c r="AG34">
-        <v>2.62</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.25</v>
-      </c>
       <c r="AK34">
-        <v>1.83</v>
+        <v>2.77</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="R35">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>2.67</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="V35">
+        <v>1.46</v>
+      </c>
+      <c r="W35">
+        <v>1.08</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.2</v>
+      </c>
+      <c r="Z35">
+        <v>3.95</v>
+      </c>
+      <c r="AA35">
+        <v>1.71</v>
+      </c>
+      <c r="AB35">
+        <v>2.11</v>
+      </c>
+      <c r="AC35">
+        <v>2.75</v>
+      </c>
+      <c r="AD35">
         <v>1.36</v>
       </c>
-      <c r="W35">
-        <v>1.07</v>
-      </c>
-      <c r="X35">
-        <v>1.08</v>
-      </c>
-      <c r="Y35">
-        <v>1.38</v>
-      </c>
-      <c r="Z35">
-        <v>3</v>
-      </c>
-      <c r="AA35">
-        <v>2.28</v>
-      </c>
-      <c r="AB35">
-        <v>1.6</v>
-      </c>
-      <c r="AC35">
-        <v>3.84</v>
-      </c>
-      <c r="AD35">
-        <v>1.21</v>
-      </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.45</v>
+        <v>4.15</v>
       </c>
       <c r="O36">
-        <v>4.46</v>
+        <v>3.48</v>
       </c>
       <c r="P36">
-        <v>6.5</v>
+        <v>1.84</v>
       </c>
       <c r="Q36">
-        <v>1.93</v>
+        <v>5.2</v>
       </c>
       <c r="R36">
+        <v>2.11</v>
+      </c>
+      <c r="S36">
+        <v>1.49</v>
+      </c>
+      <c r="T36">
         <v>2.59</v>
       </c>
-      <c r="S36">
-        <v>1.33</v>
-      </c>
-      <c r="T36">
-        <v>3.3</v>
-      </c>
       <c r="U36">
-        <v>2.49</v>
+        <v>3.32</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="Z36">
-        <v>4</v>
+        <v>2.69</v>
       </c>
       <c r="AA36">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="AB36">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AC36">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD36">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AG36">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AK36">
-        <v>2.77</v>
+        <v>1.23</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-16 14:00:00</t>
+          <t>2026-09-16 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="O37">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="Q37">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="R37">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U37">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="AA37">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AB37">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AC37">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AD37">
         <v>1.36</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG37">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-16 14:00:00</t>
+          <t>2026-09-16 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
-        <v>4.15</v>
+        <v>1.87</v>
       </c>
       <c r="O38">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="P38">
-        <v>1.84</v>
+        <v>4.33</v>
       </c>
       <c r="Q38">
-        <v>5.2</v>
+        <v>2.61</v>
       </c>
       <c r="R38">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="S38">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="T38">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="U38">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="V38">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W38">
         <v>1.03</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y38">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="Z38">
-        <v>2.69</v>
+        <v>2.22</v>
       </c>
       <c r="AA38">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AB38">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="AC38">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AD38">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AE38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF38">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="AG38">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-16 14:45:00</t>
+          <t>2026-09-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="O39">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P39">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="Q39">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-16 14:45:00</t>
+          <t>2026-09-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G40">
@@ -6825,68 +6825,68 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N40">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="O40">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P40">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="Q40">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:00</t>
+          <t>2026-09-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:00</t>
+          <t>2026-09-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q45">
-        <v>4.23</v>
+        <v>1.22</v>
       </c>
       <c r="R45">
-        <v>2.1</v>
+        <v>4.33</v>
       </c>
       <c r="S45">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="T45">
-        <v>2.99</v>
+        <v>6</v>
       </c>
       <c r="U45">
-        <v>2.6</v>
+        <v>1.52</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>2.53</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.46</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="Z45">
-        <v>3.42</v>
+        <v>13</v>
       </c>
       <c r="AA45">
-        <v>1.84</v>
+        <v>1.14</v>
       </c>
       <c r="AB45">
-        <v>1.85</v>
+        <v>6</v>
       </c>
       <c r="AC45">
-        <v>3.08</v>
+        <v>1.35</v>
       </c>
       <c r="AD45">
-        <v>1.28</v>
+        <v>2.98</v>
       </c>
       <c r="AE45">
-        <v>1.06</v>
+        <v>2.01</v>
       </c>
       <c r="AF45">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG45">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK45">
-        <v>1.22</v>
+        <v>9.9</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-16 16:00:00</t>
+          <t>2026-09-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -7760,27 +7760,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-16 16:00:00</t>
+          <t>2026-09-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.09</v>
+        <v>9</v>
       </c>
       <c r="O47">
-        <v>19</v>
+        <v>4.2</v>
       </c>
       <c r="P47">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="Q47">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="R47">
+        <v>2.48</v>
+      </c>
+      <c r="S47">
+        <v>1.31</v>
+      </c>
+      <c r="T47">
+        <v>3.4</v>
+      </c>
+      <c r="U47">
+        <v>2.46</v>
+      </c>
+      <c r="V47">
+        <v>1.54</v>
+      </c>
+      <c r="W47">
+        <v>1.12</v>
+      </c>
+      <c r="X47">
+        <v>1.02</v>
+      </c>
+      <c r="Y47">
+        <v>1.21</v>
+      </c>
+      <c r="Z47">
         <v>4.33</v>
       </c>
-      <c r="S47">
-        <v>1.09</v>
-      </c>
-      <c r="T47">
-        <v>6</v>
-      </c>
-      <c r="U47">
-        <v>1.52</v>
-      </c>
-      <c r="V47">
-        <v>2.53</v>
-      </c>
-      <c r="W47">
-        <v>1.46</v>
-      </c>
-      <c r="X47">
-        <v>1</v>
-      </c>
-      <c r="Y47">
-        <v>1.02</v>
-      </c>
-      <c r="Z47">
-        <v>13</v>
-      </c>
       <c r="AA47">
-        <v>1.14</v>
+        <v>1.72</v>
       </c>
       <c r="AB47">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>1.35</v>
+        <v>2.74</v>
       </c>
       <c r="AD47">
-        <v>2.98</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>2.01</v>
+        <v>1.17</v>
       </c>
       <c r="AF47">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AG47">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
-        <v>9.9</v>
+        <v>2.78</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-16 16:30:00</t>
+          <t>2026-09-16 18:00:00</t>
         </is>
       </c>
     </row>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,65 +8133,65 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.3</v>
+        <v>1.56</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="P48">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q48">
-        <v>3.91</v>
+        <v>1.99</v>
       </c>
       <c r="R48">
+        <v>2.47</v>
+      </c>
+      <c r="S48">
+        <v>1.25</v>
+      </c>
+      <c r="T48">
+        <v>3.6</v>
+      </c>
+      <c r="U48">
+        <v>2.18</v>
+      </c>
+      <c r="V48">
+        <v>1.6</v>
+      </c>
+      <c r="W48">
+        <v>1.11</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.1</v>
+      </c>
+      <c r="Z48">
+        <v>5</v>
+      </c>
+      <c r="AA48">
+        <v>1.54</v>
+      </c>
+      <c r="AB48">
+        <v>2.42</v>
+      </c>
+      <c r="AC48">
+        <v>2.29</v>
+      </c>
+      <c r="AD48">
+        <v>1.55</v>
+      </c>
+      <c r="AE48">
+        <v>1.18</v>
+      </c>
+      <c r="AF48">
+        <v>1.55</v>
+      </c>
+      <c r="AG48">
         <v>2.15</v>
       </c>
-      <c r="S48">
-        <v>1.36</v>
-      </c>
-      <c r="T48">
-        <v>2.88</v>
-      </c>
-      <c r="U48">
-        <v>2.77</v>
-      </c>
-      <c r="V48">
-        <v>1.44</v>
-      </c>
-      <c r="W48">
-        <v>1.08</v>
-      </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.25</v>
-      </c>
-      <c r="Z48">
-        <v>3.48</v>
-      </c>
-      <c r="AA48">
-        <v>1.81</v>
-      </c>
-      <c r="AB48">
-        <v>1.86</v>
-      </c>
-      <c r="AC48">
-        <v>3.04</v>
-      </c>
-      <c r="AD48">
-        <v>1.33</v>
-      </c>
-      <c r="AE48">
-        <v>1.1</v>
-      </c>
-      <c r="AF48">
-        <v>1.7</v>
-      </c>
-      <c r="AG48">
-        <v>2.1</v>
-      </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.62</v>
+        <v>1.12</v>
       </c>
       <c r="AK48">
-        <v>1.3</v>
+        <v>2.24</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-16 16:30:00</t>
+          <t>2026-09-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-16 18:00:00</t>
+          <t>2026-09-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="O50">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q50">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U50">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="V50">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="Z50">
-        <v>5</v>
+        <v>3.97</v>
       </c>
       <c r="AA50">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AB50">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="AC50">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="AD50">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AE50">
+        <v>1.09</v>
+      </c>
+      <c r="AF50">
+        <v>1.72</v>
+      </c>
+      <c r="AG50">
+        <v>2</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.18</v>
       </c>
-      <c r="AF50">
-        <v>1.55</v>
-      </c>
-      <c r="AG50">
-        <v>2.15</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.12</v>
-      </c>
       <c r="AK50">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-09-16 19:00:00</t>
+          <t>2026-09-16 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8575,27 +8575,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G51">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-09-16 19:00:00</t>
+          <t>2026-09-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G52">
@@ -8781,68 +8781,68 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-09-16 19:30:00</t>
+          <t>2026-09-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G58">
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10042,27 +10042,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G61">
@@ -10248,68 +10248,68 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N61">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q61">
-        <v>2.95</v>
+        <v>2.24</v>
       </c>
       <c r="R61">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="S61">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U61">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="V61">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="W61">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z61">
-        <v>5.05</v>
+        <v>4.15</v>
       </c>
       <c r="AA61">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AB61">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AC61">
-        <v>2.21</v>
+        <v>2.52</v>
       </c>
       <c r="AD61">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AE61">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AF61">
         <v>1.57</v>
       </c>
       <c r="AG61">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AK61">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-09-16 21:30:00</t>
+          <t>2026-09-16 22:30:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G62">
@@ -10424,55 +10424,55 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10518,332 +10518,6 @@
         <v>0</v>
       </c>
       <c r="AU62" t="inlineStr">
-        <is>
-          <t>2026-09-16 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Denver Summit W</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>2.24</v>
-      </c>
-      <c r="R63">
-        <v>2.3</v>
-      </c>
-      <c r="S63">
-        <v>1.24</v>
-      </c>
-      <c r="T63">
-        <v>3.6</v>
-      </c>
-      <c r="U63">
-        <v>2.38</v>
-      </c>
-      <c r="V63">
-        <v>1.54</v>
-      </c>
-      <c r="W63">
-        <v>1.11</v>
-      </c>
-      <c r="X63">
-        <v>1.03</v>
-      </c>
-      <c r="Y63">
-        <v>1.16</v>
-      </c>
-      <c r="Z63">
-        <v>4.15</v>
-      </c>
-      <c r="AA63">
-        <v>1.6</v>
-      </c>
-      <c r="AB63">
-        <v>2.17</v>
-      </c>
-      <c r="AC63">
-        <v>2.52</v>
-      </c>
-      <c r="AD63">
-        <v>1.48</v>
-      </c>
-      <c r="AE63">
-        <v>1.15</v>
-      </c>
-      <c r="AF63">
-        <v>1.57</v>
-      </c>
-      <c r="AG63">
-        <v>2.2</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.19</v>
-      </c>
-      <c r="AK63">
-        <v>1.89</v>
-      </c>
-      <c r="AL63">
-        <v>0</v>
-      </c>
-      <c r="AM63">
-        <v>-1</v>
-      </c>
-      <c r="AN63">
-        <v>-1</v>
-      </c>
-      <c r="AO63">
-        <v>-1</v>
-      </c>
-      <c r="AP63">
-        <v>-1</v>
-      </c>
-      <c r="AQ63">
-        <v>0</v>
-      </c>
-      <c r="AR63">
-        <v>0</v>
-      </c>
-      <c r="AS63">
-        <v>0</v>
-      </c>
-      <c r="AT63">
-        <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>2026-09-16 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>2.32</v>
-      </c>
-      <c r="R64">
-        <v>2.25</v>
-      </c>
-      <c r="S64">
-        <v>1.29</v>
-      </c>
-      <c r="T64">
-        <v>3.3</v>
-      </c>
-      <c r="U64">
-        <v>2.36</v>
-      </c>
-      <c r="V64">
-        <v>1.5</v>
-      </c>
-      <c r="W64">
-        <v>1.11</v>
-      </c>
-      <c r="X64">
-        <v>1.01</v>
-      </c>
-      <c r="Y64">
-        <v>1.16</v>
-      </c>
-      <c r="Z64">
-        <v>4.1</v>
-      </c>
-      <c r="AA64">
-        <v>1.66</v>
-      </c>
-      <c r="AB64">
-        <v>2.1</v>
-      </c>
-      <c r="AC64">
-        <v>2.72</v>
-      </c>
-      <c r="AD64">
-        <v>1.4</v>
-      </c>
-      <c r="AE64">
-        <v>1.12</v>
-      </c>
-      <c r="AF64">
-        <v>1.57</v>
-      </c>
-      <c r="AG64">
-        <v>2.16</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.21</v>
-      </c>
-      <c r="AK64">
-        <v>1.83</v>
-      </c>
-      <c r="AL64">
-        <v>0</v>
-      </c>
-      <c r="AM64">
-        <v>-1</v>
-      </c>
-      <c r="AN64">
-        <v>-1</v>
-      </c>
-      <c r="AO64">
-        <v>-1</v>
-      </c>
-      <c r="AP64">
-        <v>-1</v>
-      </c>
-      <c r="AQ64">
-        <v>0</v>
-      </c>
-      <c r="AR64">
-        <v>0</v>
-      </c>
-      <c r="AS64">
-        <v>0</v>
-      </c>
-      <c r="AT64">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
         <is>
           <t>2026-09-16 23:00:00</t>
         </is>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="O2">
         <v>3.55</v>
       </c>
       <c r="P2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q2">
         <v>2.39</v>
@@ -650,10 +650,10 @@
         <v>2.17</v>
       </c>
       <c r="S2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T2">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U2">
         <v>2.44</v>
@@ -665,19 +665,19 @@
         <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
         <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="AA2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB2">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC2">
         <v>2.59</v>
@@ -708,7 +708,7 @@
         <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="Q3">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="R3">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="S3">
         <v>1.47</v>
@@ -822,7 +822,7 @@
         <v>3.26</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK3">
         <v>1.59</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.36</v>
+        <v>2.95</v>
       </c>
       <c r="O9">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>8.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q9">
-        <v>1.78</v>
+        <v>3.67</v>
       </c>
       <c r="R9">
-        <v>2.65</v>
+        <v>2.16</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="U9">
-        <v>2.51</v>
+        <v>3.14</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="Z9">
-        <v>3.96</v>
+        <v>3.21</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AB9">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AC9">
-        <v>2.76</v>
+        <v>3.78</v>
       </c>
       <c r="AD9">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AE9">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AG9">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AK9">
-        <v>3.28</v>
+        <v>1.42</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="P10">
-        <v>2.41</v>
+        <v>7.6</v>
       </c>
       <c r="Q10">
-        <v>3.73</v>
+        <v>1.78</v>
       </c>
       <c r="R10">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="S10">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>3.08</v>
+        <v>2.51</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.21</v>
+        <v>3.96</v>
       </c>
       <c r="AA10">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="AB10">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>3.77</v>
+        <v>2.76</v>
       </c>
       <c r="AD10">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>1.4</v>
+        <v>3.28</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="O13">
         <v>4</v>
@@ -2437,55 +2437,55 @@
         <v>4.5</v>
       </c>
       <c r="Q13">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R13">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V13">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z13">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA13">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AB13">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC13">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD13">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE13">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG13">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2618,7 +2618,7 @@
         <v>1.66</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2627,13 +2627,13 @@
         <v>1.08</v>
       </c>
       <c r="Z14">
-        <v>5.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA14">
         <v>1.39</v>
       </c>
       <c r="AB14">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AC14">
         <v>2.04</v>
@@ -2648,7 +2648,7 @@
         <v>1.59</v>
       </c>
       <c r="AG14">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="O15">
         <v>3.83</v>
@@ -2781,7 +2781,7 @@
         <v>1.54</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
         <v>1.03</v>
@@ -2805,7 +2805,7 @@
         <v>1.46</v>
       </c>
       <c r="AE15">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF15">
         <v>1.74</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O19">
         <v>2.9</v>
       </c>
       <c r="P19">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
       </c>
       <c r="R19">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="S19">
         <v>1.48</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="Q22">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R22">
         <v>2.1</v>
@@ -3952,7 +3952,7 @@
         <v>1.74</v>
       </c>
       <c r="AG22">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P23">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="Q26">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="R26">
         <v>2.45</v>
@@ -4565,7 +4565,7 @@
         <v>1.2</v>
       </c>
       <c r="T26">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U26">
         <v>2.04</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
         <v>1.8</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -4767,7 +4767,7 @@
         <v>1.36</v>
       </c>
       <c r="AG27">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O28">
         <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="S28">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T28">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="U28">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="V28">
         <v>1.6</v>
@@ -4909,22 +4909,22 @@
         <v>1.11</v>
       </c>
       <c r="Z28">
-        <v>4.95</v>
+        <v>3.4</v>
       </c>
       <c r="AA28">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB28">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AC28">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AD28">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE28">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF28">
         <v>1.42</v>
@@ -5036,34 +5036,34 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P29">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q29">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="R29">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="S29">
         <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U29">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="V29">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W29">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
         <v>1.02</v>
@@ -5072,28 +5072,28 @@
         <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="AA29">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB29">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC29">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD29">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE29">
         <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG29">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK29">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O31">
         <v>4.2</v>
       </c>
       <c r="P31">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="Q31">
         <v>1.91</v>
       </c>
       <c r="R31">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S31">
         <v>1.14</v>
       </c>
       <c r="T31">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U31">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V31">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="W31">
         <v>1.2</v>
@@ -5398,16 +5398,16 @@
         <v>1.05</v>
       </c>
       <c r="Z31">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="AA31">
         <v>1.31</v>
       </c>
       <c r="AB31">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="AC31">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AD31">
         <v>1.83</v>
@@ -5416,7 +5416,7 @@
         <v>1.31</v>
       </c>
       <c r="AF31">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG31">
         <v>2.62</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK31">
         <v>2.31</v>
@@ -5525,22 +5525,22 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="O32">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q32">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R32">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T32">
         <v>3.9</v>
@@ -5558,16 +5558,16 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z32">
-        <v>5.44</v>
+        <v>5.15</v>
       </c>
       <c r="AA32">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AB32">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="AC32">
         <v>2.09</v>
@@ -5576,7 +5576,7 @@
         <v>1.66</v>
       </c>
       <c r="AE32">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
         <v>1.42</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
         <v>1.83</v>
@@ -5706,7 +5706,7 @@
         <v>1.42</v>
       </c>
       <c r="T33">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="U33">
         <v>2.88</v>
@@ -5724,7 +5724,7 @@
         <v>1.38</v>
       </c>
       <c r="Z33">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AA33">
         <v>2.28</v>
@@ -5733,7 +5733,7 @@
         <v>1.6</v>
       </c>
       <c r="AC33">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="AD33">
         <v>1.21</v>
@@ -5745,7 +5745,7 @@
         <v>1.9</v>
       </c>
       <c r="AG33">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5851,28 +5851,28 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="O34">
-        <v>4.46</v>
+        <v>4.7</v>
       </c>
       <c r="P34">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="Q34">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="R34">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T34">
         <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="V34">
         <v>1.53</v>
@@ -5884,7 +5884,7 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
         <v>4</v>
@@ -5899,13 +5899,13 @@
         <v>2.8</v>
       </c>
       <c r="AD34">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE34">
         <v>1.15</v>
       </c>
       <c r="AF34">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG34">
         <v>1.95</v>
@@ -5924,7 +5924,7 @@
         <v>1.17</v>
       </c>
       <c r="AK34">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="O35">
         <v>3.54</v>
@@ -6032,7 +6032,7 @@
         <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U35">
         <v>2.48</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="O36">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
         <v>1.84</v>
@@ -6250,7 +6250,7 @@
         <v>1.34</v>
       </c>
       <c r="AK36">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="P37">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O43">
         <v>3.6</v>
@@ -7327,16 +7327,16 @@
         <v>4.33</v>
       </c>
       <c r="Q43">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R43">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U43">
         <v>2.64</v>
@@ -7345,7 +7345,7 @@
         <v>1.39</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
         <v>1</v>
@@ -7357,10 +7357,10 @@
         <v>3.2</v>
       </c>
       <c r="AA43">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB43">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC43">
         <v>3.14</v>
@@ -7375,7 +7375,7 @@
         <v>1.83</v>
       </c>
       <c r="AG43">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7647,7 +7647,7 @@
         <v>1.09</v>
       </c>
       <c r="O45">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P45">
         <v>25</v>
@@ -7656,7 +7656,7 @@
         <v>1.22</v>
       </c>
       <c r="R45">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="S45">
         <v>1.09</v>
@@ -7665,43 +7665,43 @@
         <v>6</v>
       </c>
       <c r="U45">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V45">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="W45">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X45">
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z45">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA45">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AB45">
         <v>6</v>
       </c>
       <c r="AC45">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AD45">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="AE45">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AF45">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AG45">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK45">
-        <v>9.9</v>
+        <v>7</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O46">
         <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q46">
         <v>3.91</v>
@@ -7846,13 +7846,13 @@
         <v>3.48</v>
       </c>
       <c r="AA46">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB46">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC46">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="AD46">
         <v>1.33</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -638,61 +638,61 @@
         <v>1.86</v>
       </c>
       <c r="O2">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>3.55</v>
+        <v>2.91</v>
       </c>
       <c r="Q2">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="S2">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T2">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="U2">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V2">
         <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z2">
         <v>4.33</v>
       </c>
       <c r="AA2">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB2">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC2">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE2">
         <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG2">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK2">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="O3">
         <v>3.15</v>
@@ -807,16 +807,16 @@
         <v>2.89</v>
       </c>
       <c r="Q3">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="R3">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="S3">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T3">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
         <v>3.26</v>
@@ -831,7 +831,7 @@
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z3">
         <v>2.94</v>
@@ -843,19 +843,19 @@
         <v>1.64</v>
       </c>
       <c r="AC3">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="AD3">
         <v>1.18</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK3">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,37 +964,37 @@
         <v>3</v>
       </c>
       <c r="O4">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="P4">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
       </c>
       <c r="R4">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="S4">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U4">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="V4">
         <v>1.29</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z4">
         <v>2.43</v>
@@ -1003,7 +1003,7 @@
         <v>2.44</v>
       </c>
       <c r="AB4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -1012,13 +1012,13 @@
         <v>1.13</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
         <v>2.05</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.5</v>
       </c>
       <c r="AK4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1779,22 +1779,22 @@
         <v>2.95</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="P9">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="Q9">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="R9">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="T9">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
         <v>3.14</v>
@@ -1806,19 +1806,19 @@
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
         <v>3.21</v>
       </c>
       <c r="AA9">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AB9">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
         <v>3.78</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q10">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="R10">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="S10">
         <v>1.33</v>
@@ -1975,7 +1975,7 @@
         <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.96</v>
+        <v>4.17</v>
       </c>
       <c r="AA10">
         <v>1.7</v>
@@ -1987,7 +1987,7 @@
         <v>2.76</v>
       </c>
       <c r="AD10">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK10">
         <v>3.28</v>
@@ -2750,11 +2750,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N15">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="O15">
         <v>3.83</v>
@@ -2763,31 +2763,31 @@
         <v>1.45</v>
       </c>
       <c r="Q15">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T15">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V15">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W15">
         <v>1.13</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
         <v>4.47</v>
@@ -2802,7 +2802,7 @@
         <v>2.95</v>
       </c>
       <c r="AD15">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE15">
         <v>1.16</v>
@@ -2811,7 +2811,7 @@
         <v>1.74</v>
       </c>
       <c r="AG15">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>2.9</v>
       </c>
       <c r="P19">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -3424,10 +3424,10 @@
         <v>1.48</v>
       </c>
       <c r="T19">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U19">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V19">
         <v>1.25</v>
@@ -3445,10 +3445,10 @@
         <v>2.52</v>
       </c>
       <c r="AA19">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AB19">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AC19">
         <v>4.4</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,19 +3904,19 @@
         <v>1.88</v>
       </c>
       <c r="Q22">
-        <v>4.1</v>
+        <v>4.28</v>
       </c>
       <c r="R22">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S22">
         <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="U22">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="V22">
         <v>1.36</v>
@@ -3928,31 +3928,31 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z22">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA22">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB22">
         <v>1.79</v>
       </c>
       <c r="AC22">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD22">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG22">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4070,16 +4070,16 @@
         <v>3.1</v>
       </c>
       <c r="R23">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
         <v>2.88</v>
       </c>
       <c r="U23">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V23">
         <v>1.35</v>
@@ -4100,7 +4100,7 @@
         <v>1.98</v>
       </c>
       <c r="AB23">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC23">
         <v>3.5</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="R24">
         <v>2.01</v>
@@ -4239,13 +4239,13 @@
         <v>1.37</v>
       </c>
       <c r="T24">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -4263,7 +4263,7 @@
         <v>2.1</v>
       </c>
       <c r="AB24">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC24">
         <v>3.5</v>
@@ -4275,10 +4275,10 @@
         <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG24">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.44</v>
       </c>
       <c r="AK24">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="O25">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="P25">
         <v>1.67</v>
       </c>
       <c r="Q25">
-        <v>6.16</v>
+        <v>5.8</v>
       </c>
       <c r="R25">
         <v>1.96</v>
@@ -4402,37 +4402,37 @@
         <v>1.48</v>
       </c>
       <c r="T25">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="U25">
         <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W25">
+        <v>1.03</v>
+      </c>
+      <c r="X25">
         <v>1.04</v>
-      </c>
-      <c r="X25">
-        <v>1.05</v>
       </c>
       <c r="Y25">
         <v>1.4</v>
       </c>
       <c r="Z25">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA25">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AB25">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC25">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AD25">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE25">
         <v>1.03</v>
@@ -4441,7 +4441,7 @@
         <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="P26">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="Q26">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R26">
         <v>2.45</v>
       </c>
       <c r="S26">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T26">
         <v>4.1</v>
       </c>
       <c r="U26">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V26">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W26">
         <v>1.17</v>
@@ -4586,22 +4586,22 @@
         <v>5.65</v>
       </c>
       <c r="AA26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB26">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AC26">
         <v>2.08</v>
       </c>
       <c r="AD26">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE26">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AF26">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG26">
         <v>2.81</v>
@@ -4620,7 +4620,7 @@
         <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
         <v>3.7</v>
       </c>
       <c r="P27">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -4725,16 +4725,16 @@
         <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T27">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="V27">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W27">
         <v>1.17</v>
@@ -4746,7 +4746,7 @@
         <v>1.09</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AA27">
         <v>1.4</v>
@@ -4755,16 +4755,16 @@
         <v>2.88</v>
       </c>
       <c r="AC27">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AD27">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE27">
         <v>1.25</v>
       </c>
       <c r="AF27">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG27">
         <v>2.8</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,22 +4882,22 @@
         <v>2.04</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="R28">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U28">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V28">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W28">
         <v>1.1</v>
@@ -4909,25 +4909,25 @@
         <v>1.11</v>
       </c>
       <c r="Z28">
-        <v>3.4</v>
+        <v>4.93</v>
       </c>
       <c r="AA28">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB28">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AC28">
-        <v>2.29</v>
+        <v>1.94</v>
       </c>
       <c r="AD28">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AE28">
         <v>1.2</v>
       </c>
       <c r="AF28">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG28">
         <v>2.5</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,58 +5036,58 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
         <v>3.45</v>
       </c>
       <c r="P29">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q29">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="R29">
         <v>2.19</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T29">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="V29">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z29">
-        <v>4.35</v>
+        <v>3.2</v>
       </c>
       <c r="AA29">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB29">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC29">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AD29">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF29">
         <v>1.48</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AK29">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>2.82</v>
+        <v>2.34</v>
       </c>
       <c r="U30">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="V30">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="AA30">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AB30">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AC30">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="AD30">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE30">
+        <v>1.07</v>
+      </c>
+      <c r="AF30">
+        <v>1.47</v>
+      </c>
+      <c r="AG30">
+        <v>1.93</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.1</v>
       </c>
-      <c r="AF30">
-        <v>1.62</v>
-      </c>
-      <c r="AG30">
-        <v>2.14</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.25</v>
-      </c>
       <c r="AK30">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="O31">
         <v>4.2</v>
@@ -5371,25 +5371,25 @@
         <v>4.4</v>
       </c>
       <c r="Q31">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="R31">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S31">
         <v>1.14</v>
       </c>
       <c r="T31">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="V31">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="W31">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5398,28 +5398,28 @@
         <v>1.05</v>
       </c>
       <c r="Z31">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA31">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AB31">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC31">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AD31">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AE31">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AF31">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AG31">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK31">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P32">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q32">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="R32">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T32">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="U32">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="V32">
         <v>1.67</v>
       </c>
       <c r="W32">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z32">
-        <v>5.15</v>
+        <v>3.6</v>
       </c>
       <c r="AA32">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB32">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC32">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AD32">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AE32">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF32">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AG32">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK32">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5706,7 +5706,7 @@
         <v>1.42</v>
       </c>
       <c r="T33">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="U33">
         <v>2.88</v>
@@ -5718,10 +5718,10 @@
         <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y33">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z33">
         <v>2.76</v>
@@ -5733,7 +5733,7 @@
         <v>1.6</v>
       </c>
       <c r="AC33">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD33">
         <v>1.21</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK33">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,25 +5854,25 @@
         <v>1.33</v>
       </c>
       <c r="O34">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P34">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>1.88</v>
       </c>
       <c r="R34">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="S34">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="V34">
         <v>1.53</v>
@@ -5890,7 +5890,7 @@
         <v>4</v>
       </c>
       <c r="AA34">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
         <v>2.1</v>
@@ -5899,17 +5899,17 @@
         <v>2.8</v>
       </c>
       <c r="AD34">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AE34">
         <v>1.15</v>
       </c>
       <c r="AF34">
+        <v>1.91</v>
+      </c>
+      <c r="AG34">
         <v>1.85</v>
       </c>
-      <c r="AG34">
-        <v>1.95</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK34">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
         <v>3.54</v>
@@ -6026,16 +6026,16 @@
         <v>2.7</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S35">
         <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="U35">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V35">
         <v>1.46</v>
@@ -6053,10 +6053,10 @@
         <v>3.95</v>
       </c>
       <c r="AA35">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB35">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC35">
         <v>2.75</v>
@@ -6065,7 +6065,7 @@
         <v>1.36</v>
       </c>
       <c r="AE35">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
         <v>1.57</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,28 +6177,28 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q36">
-        <v>5.2</v>
+        <v>4.95</v>
       </c>
       <c r="R36">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="S36">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T36">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="U36">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="V36">
         <v>1.31</v>
@@ -6207,7 +6207,7 @@
         <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
         <v>1.39</v>
@@ -6216,13 +6216,13 @@
         <v>2.69</v>
       </c>
       <c r="AA36">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AB36">
         <v>1.68</v>
       </c>
       <c r="AC36">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD36">
         <v>1.18</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.34</v>
+        <v>1.96</v>
       </c>
       <c r="AK36">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,25 +6340,25 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="O37">
-        <v>3.76</v>
+        <v>3.53</v>
       </c>
       <c r="P37">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
       </c>
       <c r="R37">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
         <v>2.6</v>
@@ -6376,13 +6376,13 @@
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="AA37">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AB37">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AC37">
         <v>2.81</v>
@@ -6394,10 +6394,10 @@
         <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AG37">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK37">
         <v>2</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O40">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P40">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7173,10 +7173,10 @@
         <v>1.31</v>
       </c>
       <c r="T42">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U42">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V42">
         <v>1.4</v>
@@ -7194,10 +7194,10 @@
         <v>3.42</v>
       </c>
       <c r="AA42">
+        <v>1.83</v>
+      </c>
+      <c r="AB42">
         <v>1.84</v>
-      </c>
-      <c r="AB42">
-        <v>1.85</v>
       </c>
       <c r="AC42">
         <v>3.08</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7339,7 +7339,7 @@
         <v>3</v>
       </c>
       <c r="U43">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="V43">
         <v>1.39</v>
@@ -7357,10 +7357,10 @@
         <v>3.2</v>
       </c>
       <c r="AA43">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB43">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC43">
         <v>3.14</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK43">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="O45">
         <v>14</v>
@@ -7653,25 +7653,25 @@
         <v>25</v>
       </c>
       <c r="Q45">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="R45">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="S45">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="T45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U45">
+        <v>1.5</v>
+      </c>
+      <c r="V45">
+        <v>2.53</v>
+      </c>
+      <c r="W45">
         <v>1.51</v>
-      </c>
-      <c r="V45">
-        <v>2.55</v>
-      </c>
-      <c r="W45">
-        <v>1.47</v>
       </c>
       <c r="X45">
         <v>1</v>
@@ -7698,10 +7698,10 @@
         <v>2</v>
       </c>
       <c r="AF45">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.05</v>
       </c>
       <c r="AK45">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,7 +7816,7 @@
         <v>2.02</v>
       </c>
       <c r="Q46">
-        <v>3.91</v>
+        <v>3.32</v>
       </c>
       <c r="R46">
         <v>2.15</v>
@@ -7825,13 +7825,13 @@
         <v>1.36</v>
       </c>
       <c r="T46">
-        <v>2.88</v>
+        <v>3.19</v>
       </c>
       <c r="U46">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W46">
         <v>1.08</v>
@@ -7858,13 +7858,13 @@
         <v>1.33</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF46">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG46">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G5">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-16 11:00:00</t>
+          <t>2026-09-16 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G7">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-16 12:00:00</t>
+          <t>2026-09-16 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
-        <v>3.23</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>2.31</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q9">
-        <v>3.25</v>
+        <v>1.82</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="S9">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="U9">
-        <v>3.14</v>
+        <v>2.51</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.21</v>
+        <v>4.17</v>
       </c>
       <c r="AA9">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
+        <v>2.15</v>
+      </c>
+      <c r="AC9">
+        <v>2.76</v>
+      </c>
+      <c r="AD9">
+        <v>1.41</v>
+      </c>
+      <c r="AE9">
+        <v>1.13</v>
+      </c>
+      <c r="AF9">
+        <v>2.02</v>
+      </c>
+      <c r="AG9">
         <v>1.72</v>
       </c>
-      <c r="AC9">
-        <v>3.78</v>
-      </c>
-      <c r="AD9">
-        <v>1.26</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
-      <c r="AF9">
-        <v>1.81</v>
-      </c>
-      <c r="AG9">
-        <v>1.91</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK9">
-        <v>1.35</v>
+        <v>3.28</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="P10">
-        <v>8.199999999999999</v>
+        <v>2.25</v>
       </c>
       <c r="Q10">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-16 12:30:00</t>
+          <t>2026-09-16 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G11">
@@ -2098,68 +2098,68 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N11">
-        <v>2.88</v>
+        <v>5.45</v>
       </c>
       <c r="O11">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P11">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-16 12:45:00</t>
+          <t>2026-09-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2223,22 +2223,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G12">
@@ -2261,68 +2261,68 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N12">
+        <v>1.43</v>
+      </c>
+      <c r="O12">
+        <v>4.4</v>
+      </c>
+      <c r="P12">
+        <v>5.25</v>
+      </c>
+      <c r="Q12">
+        <v>1.83</v>
+      </c>
+      <c r="R12">
+        <v>2.62</v>
+      </c>
+      <c r="S12">
+        <v>1.2</v>
+      </c>
+      <c r="T12">
+        <v>3.7</v>
+      </c>
+      <c r="U12">
+        <v>2.07</v>
+      </c>
+      <c r="V12">
+        <v>1.71</v>
+      </c>
+      <c r="W12">
+        <v>1.14</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
+        <v>1.08</v>
+      </c>
+      <c r="Z12">
         <v>5.45</v>
       </c>
-      <c r="O12">
-        <v>3.55</v>
-      </c>
-      <c r="P12">
-        <v>1.94</v>
-      </c>
-      <c r="Q12">
-        <v>5.8</v>
-      </c>
-      <c r="R12">
-        <v>2.05</v>
-      </c>
-      <c r="S12">
-        <v>1.46</v>
-      </c>
-      <c r="T12">
-        <v>2.44</v>
-      </c>
-      <c r="U12">
-        <v>3.12</v>
-      </c>
-      <c r="V12">
+      <c r="AA12">
+        <v>1.44</v>
+      </c>
+      <c r="AB12">
+        <v>2.62</v>
+      </c>
+      <c r="AC12">
+        <v>2.07</v>
+      </c>
+      <c r="AD12">
+        <v>1.73</v>
+      </c>
+      <c r="AE12">
         <v>1.29</v>
       </c>
-      <c r="W12">
-        <v>1.05</v>
-      </c>
-      <c r="X12">
-        <v>1.07</v>
-      </c>
-      <c r="Y12">
-        <v>1.39</v>
-      </c>
-      <c r="Z12">
-        <v>2.87</v>
-      </c>
-      <c r="AA12">
-        <v>2.05</v>
-      </c>
-      <c r="AB12">
+      <c r="AF12">
         <v>1.57</v>
       </c>
-      <c r="AC12">
-        <v>3.84</v>
-      </c>
-      <c r="AD12">
-        <v>1.18</v>
-      </c>
-      <c r="AE12">
-        <v>1.03</v>
-      </c>
-      <c r="AF12">
-        <v>2.05</v>
-      </c>
       <c r="AG12">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>1.07</v>
+        <v>2.5</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,68 +2424,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="P13">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="R13">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S13">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="U13">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="V13">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
-        <v>4.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA13">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AC13">
-        <v>2.27</v>
+        <v>2.03</v>
       </c>
       <c r="AD13">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AE13">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AF13">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AG13">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AK13">
-        <v>2.14</v>
+        <v>2.71</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2549,22 +2549,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G14">
@@ -2587,68 +2587,68 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.24</v>
+        <v>4.8</v>
       </c>
       <c r="O14">
-        <v>4.8</v>
+        <v>3.83</v>
       </c>
       <c r="P14">
-        <v>5.75</v>
+        <v>1.45</v>
       </c>
       <c r="Q14">
-        <v>1.62</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="S14">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U14">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="V14">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="W14">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z14">
-        <v>5.45</v>
+        <v>4.47</v>
       </c>
       <c r="AA14">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="AC14">
-        <v>2.04</v>
+        <v>2.95</v>
       </c>
       <c r="AD14">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AE14">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF14">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AG14">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AK14">
-        <v>2.77</v>
+        <v>1.12</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.8</v>
+        <v>1.84</v>
       </c>
       <c r="O15">
-        <v>3.83</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>1.45</v>
+        <v>3.9</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="O19">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="P19">
-        <v>2.6</v>
+        <v>3.39</v>
       </c>
       <c r="Q19">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="R19">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="S19">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U19">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="V19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
         <v>1.04</v>
@@ -3445,25 +3445,25 @@
         <v>2.52</v>
       </c>
       <c r="AA19">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AB19">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC19">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AD19">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE19">
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG19">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.06</v>
+        <v>3.4</v>
       </c>
       <c r="O20">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>3.39</v>
+        <v>1.88</v>
       </c>
       <c r="Q20">
-        <v>2.7</v>
+        <v>4.28</v>
       </c>
       <c r="R20">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="S20">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
       <c r="U20">
-        <v>3.24</v>
+        <v>2.72</v>
       </c>
       <c r="V20">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
         <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="Z20">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="AA20">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="AB20">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AC20">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD20">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AE20">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
+        <v>1.23</v>
+      </c>
+      <c r="AK20">
         <v>1.22</v>
-      </c>
-      <c r="AK20">
-        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q21">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="T21">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="U21">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="V21">
+        <v>1.35</v>
+      </c>
+      <c r="W21">
+        <v>1.07</v>
+      </c>
+      <c r="X21">
+        <v>1.02</v>
+      </c>
+      <c r="Y21">
+        <v>1.28</v>
+      </c>
+      <c r="Z21">
+        <v>3.08</v>
+      </c>
+      <c r="AA21">
+        <v>1.98</v>
+      </c>
+      <c r="AB21">
+        <v>1.71</v>
+      </c>
+      <c r="AC21">
+        <v>3.5</v>
+      </c>
+      <c r="AD21">
+        <v>1.22</v>
+      </c>
+      <c r="AE21">
+        <v>1.03</v>
+      </c>
+      <c r="AF21">
+        <v>1.75</v>
+      </c>
+      <c r="AG21">
+        <v>1.9</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.25</v>
       </c>
-      <c r="W21">
-        <v>1.02</v>
-      </c>
-      <c r="X21">
-        <v>1.03</v>
-      </c>
-      <c r="Y21">
-        <v>1.39</v>
-      </c>
-      <c r="Z21">
-        <v>2.62</v>
-      </c>
-      <c r="AA21">
-        <v>2.29</v>
-      </c>
-      <c r="AB21">
-        <v>1.53</v>
-      </c>
-      <c r="AC21">
-        <v>4.4</v>
-      </c>
-      <c r="AD21">
-        <v>1.14</v>
-      </c>
-      <c r="AE21">
-        <v>1</v>
-      </c>
-      <c r="AF21">
-        <v>1.92</v>
-      </c>
-      <c r="AG21">
-        <v>1.73</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.33</v>
-      </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>4.28</v>
+        <v>3.24</v>
       </c>
       <c r="R22">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T22">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="U22">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
+        <v>1.06</v>
+      </c>
+      <c r="X22">
+        <v>1.02</v>
+      </c>
+      <c r="Y22">
+        <v>1.31</v>
+      </c>
+      <c r="Z22">
+        <v>2.92</v>
+      </c>
+      <c r="AA22">
+        <v>2.1</v>
+      </c>
+      <c r="AB22">
+        <v>1.68</v>
+      </c>
+      <c r="AC22">
+        <v>3.5</v>
+      </c>
+      <c r="AD22">
+        <v>1.22</v>
+      </c>
+      <c r="AE22">
         <v>1.05</v>
       </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
-      <c r="Y22">
-        <v>1.26</v>
-      </c>
-      <c r="Z22">
-        <v>3.2</v>
-      </c>
-      <c r="AA22">
-        <v>1.88</v>
-      </c>
-      <c r="AB22">
-        <v>1.79</v>
-      </c>
-      <c r="AC22">
-        <v>3.14</v>
-      </c>
-      <c r="AD22">
-        <v>1.27</v>
-      </c>
-      <c r="AE22">
-        <v>1.07</v>
-      </c>
       <c r="AF22">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG22">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AK22">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S23">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="T23">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="U23">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="V23">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="Z23">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="AA23">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="AB23">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AC23">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD23">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AG23">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q24">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="R24">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="S24">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="T24">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="U24">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="V24">
+        <v>1.25</v>
+      </c>
+      <c r="W24">
+        <v>1.01</v>
+      </c>
+      <c r="X24">
+        <v>1.04</v>
+      </c>
+      <c r="Y24">
+        <v>1.41</v>
+      </c>
+      <c r="Z24">
+        <v>2.52</v>
+      </c>
+      <c r="AA24">
+        <v>2.33</v>
+      </c>
+      <c r="AB24">
+        <v>1.51</v>
+      </c>
+      <c r="AC24">
+        <v>4.4</v>
+      </c>
+      <c r="AD24">
+        <v>1.14</v>
+      </c>
+      <c r="AE24">
+        <v>1.01</v>
+      </c>
+      <c r="AF24">
+        <v>1.95</v>
+      </c>
+      <c r="AG24">
+        <v>1.74</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.29</v>
+      </c>
+      <c r="AK24">
         <v>1.35</v>
-      </c>
-      <c r="W24">
-        <v>1.06</v>
-      </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
-      <c r="Y24">
-        <v>1.31</v>
-      </c>
-      <c r="Z24">
-        <v>2.92</v>
-      </c>
-      <c r="AA24">
-        <v>2.1</v>
-      </c>
-      <c r="AB24">
-        <v>1.68</v>
-      </c>
-      <c r="AC24">
-        <v>3.5</v>
-      </c>
-      <c r="AD24">
-        <v>1.22</v>
-      </c>
-      <c r="AE24">
-        <v>1.05</v>
-      </c>
-      <c r="AF24">
-        <v>1.78</v>
-      </c>
-      <c r="AG24">
-        <v>1.89</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.44</v>
-      </c>
-      <c r="AK24">
-        <v>1.39</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>2.1</v>
       </c>
       <c r="O35">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="Q35">
         <v>2.7</v>
@@ -6032,13 +6032,13 @@
         <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
         <v>2.4</v>
       </c>
       <c r="V35">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6047,22 +6047,22 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA35">
         <v>1.7</v>
       </c>
       <c r="AB35">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC35">
         <v>2.75</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE35">
         <v>1.1</v>
@@ -6071,7 +6071,7 @@
         <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O38">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="P38">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="Q38">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="R38">
         <v>1.81</v>
       </c>
       <c r="S38">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="T38">
         <v>2.2</v>
       </c>
       <c r="U38">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="V38">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W38">
         <v>1.03</v>
@@ -6539,16 +6539,16 @@
         <v>1.6</v>
       </c>
       <c r="Z38">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AA38">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="AB38">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC38">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="AD38">
         <v>1.07</v>
@@ -6560,7 +6560,7 @@
         <v>2.45</v>
       </c>
       <c r="AG38">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O39">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,52 +6829,52 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>2.25</v>
+      </c>
+      <c r="R40">
+        <v>1.97</v>
+      </c>
+      <c r="S40">
+        <v>1.41</v>
+      </c>
+      <c r="T40">
+        <v>2.55</v>
+      </c>
+      <c r="U40">
         <v>3</v>
       </c>
-      <c r="P40">
-        <v>2.45</v>
-      </c>
-      <c r="Q40">
-        <v>3.44</v>
-      </c>
-      <c r="R40">
-        <v>1.9</v>
-      </c>
-      <c r="S40">
-        <v>1.46</v>
-      </c>
-      <c r="T40">
-        <v>2.39</v>
-      </c>
-      <c r="U40">
-        <v>3.18</v>
-      </c>
       <c r="V40">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z40">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AA40">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AB40">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AC40">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AD40">
         <v>1.16</v>
@@ -6883,10 +6883,10 @@
         <v>1.01</v>
       </c>
       <c r="AF40">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AG40">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.36</v>
+        <v>2.07</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G41">
@@ -7001,55 +7001,55 @@
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.25</v>
+        <v>4.23</v>
       </c>
       <c r="R41">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="T41">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="V41">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>2.74</v>
+        <v>3.42</v>
       </c>
       <c r="AA41">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="AB41">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="AC41">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD41">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE41">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="AG41">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK41">
-        <v>2.07</v>
+        <v>1.21</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q42">
-        <v>4.23</v>
+        <v>2.2</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
         <v>3</v>
       </c>
       <c r="U42">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="V42">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z42">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA42">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB42">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC42">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD42">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE42">
         <v>1.06</v>
       </c>
       <c r="AF42">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG42">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK42">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,65 +7318,65 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.68</v>
+        <v>2.62</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q43">
-        <v>2.2</v>
+        <v>3.44</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="T43">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="U43">
-        <v>2.61</v>
+        <v>3.18</v>
       </c>
       <c r="V43">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="Z43">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AA43">
+        <v>2.22</v>
+      </c>
+      <c r="AB43">
+        <v>1.56</v>
+      </c>
+      <c r="AC43">
+        <v>4.1</v>
+      </c>
+      <c r="AD43">
+        <v>1.16</v>
+      </c>
+      <c r="AE43">
+        <v>1.01</v>
+      </c>
+      <c r="AF43">
         <v>1.88</v>
       </c>
-      <c r="AB43">
+      <c r="AG43">
         <v>1.79</v>
       </c>
-      <c r="AC43">
-        <v>3.14</v>
-      </c>
-      <c r="AD43">
-        <v>1.27</v>
-      </c>
-      <c r="AE43">
-        <v>1.06</v>
-      </c>
-      <c r="AF43">
-        <v>1.83</v>
-      </c>
-      <c r="AG43">
-        <v>1.81</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>9</v>
+        <v>1.45</v>
       </c>
       <c r="O47">
         <v>4.2</v>
       </c>
       <c r="P47">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="Q47">
         <v>2.02</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10267,7 +10267,7 @@
         <v>2.3</v>
       </c>
       <c r="S61">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
         <v>3.6</v>
@@ -10276,7 +10276,7 @@
         <v>2.38</v>
       </c>
       <c r="V61">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W61">
         <v>1.11</v>
@@ -10291,16 +10291,16 @@
         <v>4.15</v>
       </c>
       <c r="AA61">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB61">
         <v>2.17</v>
       </c>
       <c r="AC61">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AD61">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE61">
         <v>1.15</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK61">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,46 +10424,46 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R62">
         <v>2.25</v>
       </c>
       <c r="S62">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T62">
         <v>3.3</v>
       </c>
       <c r="U62">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V62">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W62">
         <v>1.11</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
         <v>1.16</v>
       </c>
       <c r="Z62">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA62">
         <v>1.66</v>
       </c>
       <c r="AB62">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC62">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE62">
         <v>1.12</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N11">
@@ -4543,26 +4543,26 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="Q26">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R26">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S26">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
         <v>4.1</v>
@@ -4580,22 +4580,22 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z26">
         <v>5.65</v>
       </c>
       <c r="AA26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB26">
         <v>2.7</v>
       </c>
       <c r="AC26">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD26">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE26">
         <v>1.32</v>
@@ -4620,7 +4620,7 @@
         <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4706,47 +4706,47 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27">
         <v>2.6</v>
       </c>
       <c r="O27">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
         <v>2.3</v>
       </c>
       <c r="Q27">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="S27">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U27">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="V27">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W27">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA27">
         <v>1.4</v>
@@ -4755,13 +4755,13 @@
         <v>2.88</v>
       </c>
       <c r="AC27">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AD27">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AE27">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF27">
         <v>1.39</v>
@@ -5721,7 +5721,7 @@
         <v>1.07</v>
       </c>
       <c r="Y33">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z33">
         <v>2.76</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
         <v>1.48</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="O34">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P34">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="Q34">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R34">
-        <v>2.64</v>
+        <v>2.41</v>
       </c>
       <c r="S34">
         <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="U34">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
         <v>1.11</v>
@@ -5884,13 +5884,13 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
         <v>4</v>
       </c>
       <c r="AA34">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB34">
         <v>2.1</v>
@@ -5899,16 +5899,16 @@
         <v>2.8</v>
       </c>
       <c r="AD34">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF34">
         <v>1.91</v>
       </c>
       <c r="AG34">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK34">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="O44">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P44">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R44">
         <v>2.35</v>
@@ -7535,10 +7535,10 @@
         <v>1.23</v>
       </c>
       <c r="AF44">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK44">
         <v>2.25</v>
@@ -7650,25 +7650,25 @@
         <v>14</v>
       </c>
       <c r="P45">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q45">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R45">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="S45">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T45">
         <v>7</v>
       </c>
       <c r="U45">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V45">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="W45">
         <v>1.51</v>
@@ -7677,10 +7677,10 @@
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z45">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA45">
         <v>1.12</v>
@@ -7689,13 +7689,13 @@
         <v>6</v>
       </c>
       <c r="AC45">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD45">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="AE45">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF45">
         <v>1.78</v>
@@ -7813,31 +7813,31 @@
         <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="Q46">
-        <v>3.32</v>
+        <v>3.92</v>
       </c>
       <c r="R46">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S46">
         <v>1.36</v>
       </c>
       <c r="T46">
-        <v>3.19</v>
+        <v>2.78</v>
       </c>
       <c r="U46">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="V46">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W46">
         <v>1.08</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y46">
         <v>1.25</v>
@@ -7846,25 +7846,25 @@
         <v>3.48</v>
       </c>
       <c r="AA46">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB46">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AC46">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="AD46">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE46">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF46">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG46">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.62</v>
       </c>
       <c r="AK46">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8139,58 +8139,58 @@
         <v>4.3</v>
       </c>
       <c r="P48">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="Q48">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="R48">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U48">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V48">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z48">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="AA48">
+        <v>1.53</v>
+      </c>
+      <c r="AB48">
+        <v>2.37</v>
+      </c>
+      <c r="AC48">
+        <v>2.34</v>
+      </c>
+      <c r="AD48">
         <v>1.54</v>
-      </c>
-      <c r="AB48">
-        <v>2.42</v>
-      </c>
-      <c r="AC48">
-        <v>2.29</v>
-      </c>
-      <c r="AD48">
-        <v>1.55</v>
       </c>
       <c r="AE48">
         <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG48">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK48">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,25 +8305,25 @@
         <v>2.15</v>
       </c>
       <c r="Q49">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
         <v>1.25</v>
       </c>
       <c r="T49">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U49">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V49">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8335,10 +8335,10 @@
         <v>4.65</v>
       </c>
       <c r="AA49">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB49">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC49">
         <v>2.33</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AK49">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,49 +8459,49 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P50">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="Q50">
         <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U50">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V50">
         <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.19</v>
       </c>
       <c r="Z50">
-        <v>3.97</v>
+        <v>3.74</v>
       </c>
       <c r="AA50">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC50">
         <v>2.9</v>
@@ -8513,7 +8513,7 @@
         <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG50">
         <v>2</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK50">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="O59">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P59">
         <v>2.85</v>
       </c>
       <c r="Q59">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R59">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="S59">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T59">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="U59">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V59">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W59">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X59">
         <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z59">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="AA59">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AB59">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="AC59">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AD59">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE59">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF59">
         <v>1.57</v>
       </c>
       <c r="AG59">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="AK59">
         <v>1.44</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>2.91</v>
+        <v>3.6</v>
       </c>
       <c r="Q2">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="R2">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U2">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
         <v>4.33</v>
       </c>
       <c r="AA2">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB2">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC2">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AK2">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,61 +801,61 @@
         <v>2.25</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P3">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="Q3">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="R3">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="S3">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T3">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U3">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z3">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AA3">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AB3">
         <v>1.64</v>
       </c>
       <c r="AC3">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AD3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK3">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O4">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="P4">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -976,13 +976,13 @@
         <v>1.87</v>
       </c>
       <c r="S4">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T4">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U4">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="V4">
         <v>1.29</v>
@@ -1006,7 +1006,7 @@
         <v>1.5</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AD4">
         <v>1.13</v>
@@ -1015,10 +1015,10 @@
         <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.5</v>
       </c>
       <c r="AK4">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1616,25 +1616,25 @@
         <v>2.95</v>
       </c>
       <c r="O8">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="Q8">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="R8">
         <v>2</v>
       </c>
       <c r="S8">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T8">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="U8">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="V8">
         <v>1.34</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK8">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="P9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Q9">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R9">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="S9">
         <v>1.33</v>
@@ -1809,7 +1809,7 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
         <v>4.17</v>
@@ -1830,10 +1830,10 @@
         <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK9">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
+        <v>2.75</v>
+      </c>
+      <c r="O10">
+        <v>3.3</v>
+      </c>
+      <c r="P10">
+        <v>2.2</v>
+      </c>
+      <c r="Q10">
+        <v>3.3</v>
+      </c>
+      <c r="R10">
+        <v>2.2</v>
+      </c>
+      <c r="S10">
+        <v>1.3</v>
+      </c>
+      <c r="T10">
+        <v>3.2</v>
+      </c>
+      <c r="U10">
+        <v>2.63</v>
+      </c>
+      <c r="V10">
+        <v>1.44</v>
+      </c>
+      <c r="W10">
+        <v>1.11</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.22</v>
+      </c>
+      <c r="Z10">
+        <v>4.2</v>
+      </c>
+      <c r="AA10">
+        <v>1.75</v>
+      </c>
+      <c r="AB10">
+        <v>2.05</v>
+      </c>
+      <c r="AC10">
         <v>2.88</v>
       </c>
-      <c r="O10">
-        <v>3.35</v>
-      </c>
-      <c r="P10">
+      <c r="AD10">
+        <v>1.4</v>
+      </c>
+      <c r="AE10">
+        <v>1.14</v>
+      </c>
+      <c r="AF10">
+        <v>1.57</v>
+      </c>
+      <c r="AG10">
         <v>2.25</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>1.94</v>
       </c>
       <c r="Q11">
-        <v>6.36</v>
+        <v>7.9</v>
       </c>
       <c r="R11">
         <v>2.05</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="U11">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="V11">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z11">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AA11">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AB11">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AC11">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE11">
         <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG11">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="AK11">
         <v>1.07</v>
@@ -2268,16 +2268,16 @@
         <v>1.43</v>
       </c>
       <c r="O12">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P12">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q12">
         <v>1.83</v>
       </c>
       <c r="R12">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S12">
         <v>1.2</v>
@@ -2289,13 +2289,13 @@
         <v>2.07</v>
       </c>
       <c r="V12">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W12">
         <v>1.14</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.08</v>
@@ -2307,13 +2307,13 @@
         <v>1.44</v>
       </c>
       <c r="AB12">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="AC12">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AD12">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE12">
         <v>1.29</v>
@@ -2322,7 +2322,7 @@
         <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK12">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>5.75</v>
       </c>
       <c r="Q13">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R13">
         <v>2.54</v>
@@ -2452,10 +2452,10 @@
         <v>2.06</v>
       </c>
       <c r="V13">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2467,10 +2467,10 @@
         <v>5.45</v>
       </c>
       <c r="AA13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB13">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AC13">
         <v>2.03</v>
@@ -2479,7 +2479,7 @@
         <v>1.67</v>
       </c>
       <c r="AE13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
         <v>1.59</v>
@@ -2600,22 +2600,22 @@
         <v>1.45</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="R14">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="S14">
         <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="U14">
         <v>2.3</v>
       </c>
       <c r="V14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
         <v>1.13</v>
@@ -2636,10 +2636,10 @@
         <v>2.28</v>
       </c>
       <c r="AC14">
-        <v>2.95</v>
+        <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AE14">
         <v>1.16</v>
@@ -2648,7 +2648,7 @@
         <v>1.74</v>
       </c>
       <c r="AG14">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P15">
         <v>3.9</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="O19">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>3.39</v>
+        <v>2.8</v>
       </c>
       <c r="Q19">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R19">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="S19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="U19">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="V19">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="Z19">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AA19">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="AB19">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC19">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="AD19">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,65 +3569,65 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P20">
-        <v>1.88</v>
+        <v>4.1</v>
       </c>
       <c r="Q20">
-        <v>4.28</v>
+        <v>2.58</v>
       </c>
       <c r="R20">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T20">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="U20">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y20">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="Z20">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AA20">
-        <v>1.88</v>
+        <v>2.37</v>
       </c>
       <c r="AB20">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="AC20">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="AD20">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF20">
+        <v>2</v>
+      </c>
+      <c r="AG20">
         <v>1.73</v>
       </c>
-      <c r="AG20">
-        <v>1.92</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P21">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="R21">
         <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U21">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
         <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA21">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB21">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AC21">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD21">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG21">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
+        <v>1.7</v>
+      </c>
+      <c r="AK21">
         <v>1.25</v>
-      </c>
-      <c r="AK21">
-        <v>1.43</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
         <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V22">
         <v>1.35</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB22">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC22">
         <v>3.5</v>
       </c>
       <c r="AD22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
         <v>1.78</v>
       </c>
       <c r="AG22">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4067,71 +4067,71 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="R23">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="S23">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T23">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="U23">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V23">
+        <v>1.22</v>
+      </c>
+      <c r="W23">
+        <v>1.05</v>
+      </c>
+      <c r="X23">
+        <v>1.06</v>
+      </c>
+      <c r="Y23">
+        <v>1.43</v>
+      </c>
+      <c r="Z23">
+        <v>2.46</v>
+      </c>
+      <c r="AA23">
+        <v>2.35</v>
+      </c>
+      <c r="AB23">
+        <v>1.49</v>
+      </c>
+      <c r="AC23">
+        <v>5</v>
+      </c>
+      <c r="AD23">
+        <v>1.13</v>
+      </c>
+      <c r="AE23">
+        <v>1.02</v>
+      </c>
+      <c r="AF23">
+        <v>2</v>
+      </c>
+      <c r="AG23">
+        <v>1.68</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.25</v>
       </c>
-      <c r="W23">
-        <v>1.02</v>
-      </c>
-      <c r="X23">
-        <v>1.03</v>
-      </c>
-      <c r="Y23">
-        <v>1.39</v>
-      </c>
-      <c r="Z23">
-        <v>2.62</v>
-      </c>
-      <c r="AA23">
-        <v>2.29</v>
-      </c>
-      <c r="AB23">
+      <c r="AK23">
         <v>1.53</v>
-      </c>
-      <c r="AC23">
-        <v>4.4</v>
-      </c>
-      <c r="AD23">
-        <v>1.14</v>
-      </c>
-      <c r="AE23">
-        <v>1</v>
-      </c>
-      <c r="AF23">
-        <v>1.92</v>
-      </c>
-      <c r="AG23">
-        <v>1.73</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.33</v>
-      </c>
-      <c r="AK23">
-        <v>1.44</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4227,58 +4227,58 @@
         <v>2.9</v>
       </c>
       <c r="P24">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R24">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U24">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z24">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AA24">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="AB24">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AC24">
         <v>4.4</v>
       </c>
       <c r="AD24">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG24">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AK24">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,37 +4384,37 @@
         </is>
       </c>
       <c r="N25">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="O25">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
         <v>1.67</v>
       </c>
       <c r="Q25">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
         <v>1.48</v>
       </c>
       <c r="T25">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="V25">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W25">
         <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y25">
         <v>1.4</v>
@@ -4423,25 +4423,25 @@
         <v>2.88</v>
       </c>
       <c r="AA25">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AB25">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC25">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD25">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.96</v>
       </c>
       <c r="AK25">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O26">
         <v>3.7</v>
@@ -4559,22 +4559,22 @@
         <v>2.38</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S26">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T26">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U26">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V26">
         <v>1.72</v>
       </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -4583,10 +4583,10 @@
         <v>1.1</v>
       </c>
       <c r="Z26">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="AA26">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB26">
         <v>2.7</v>
@@ -4595,10 +4595,10 @@
         <v>2.05</v>
       </c>
       <c r="AD26">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE26">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF26">
         <v>1.38</v>
@@ -4620,7 +4620,7 @@
         <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q27">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="R27">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="S27">
         <v>1.22</v>
@@ -4731,13 +4731,13 @@
         <v>3.9</v>
       </c>
       <c r="U27">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
         <v>1.67</v>
       </c>
       <c r="W27">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X27">
         <v>1.02</v>
@@ -4764,10 +4764,10 @@
         <v>1.3</v>
       </c>
       <c r="AF27">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG27">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK27">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="Q28">
-        <v>3.56</v>
+        <v>3.24</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U28">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="V28">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
         <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>4.93</v>
+        <v>3.8</v>
       </c>
       <c r="AA28">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AB28">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AC28">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="AD28">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="O29">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P29">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="Q29">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="S29">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="U29">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V29">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z29">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA29">
+        <v>1.47</v>
+      </c>
+      <c r="AB29">
+        <v>2.35</v>
+      </c>
+      <c r="AC29">
+        <v>2.3</v>
+      </c>
+      <c r="AD29">
         <v>1.6</v>
       </c>
-      <c r="AB29">
-        <v>2.3</v>
-      </c>
-      <c r="AC29">
-        <v>2.06</v>
-      </c>
-      <c r="AD29">
-        <v>1.4</v>
-      </c>
       <c r="AE29">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG29">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.08</v>
+        <v>1.55</v>
       </c>
       <c r="AK29">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P30">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q30">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="AA30">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB30">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="AC30">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AD30">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AG30">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,34 +5362,34 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="O31">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P31">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q31">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="R31">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T31">
-        <v>3.1</v>
+        <v>4.35</v>
       </c>
       <c r="U31">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="V31">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="W31">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5398,28 +5398,28 @@
         <v>1.05</v>
       </c>
       <c r="Z31">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AA31">
         <v>1.25</v>
       </c>
       <c r="AB31">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC31">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AD31">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AE31">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AF31">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK31">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,65 +5525,65 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O32">
         <v>3.65</v>
       </c>
       <c r="P32">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q32">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S32">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
         <v>2.9</v>
       </c>
       <c r="U32">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="V32">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z32">
-        <v>3.6</v>
+        <v>5.15</v>
       </c>
       <c r="AA32">
         <v>1.47</v>
       </c>
       <c r="AB32">
+        <v>2.2</v>
+      </c>
+      <c r="AC32">
+        <v>2.2</v>
+      </c>
+      <c r="AD32">
+        <v>1.66</v>
+      </c>
+      <c r="AE32">
+        <v>1.29</v>
+      </c>
+      <c r="AF32">
+        <v>1.41</v>
+      </c>
+      <c r="AG32">
         <v>2.6</v>
       </c>
-      <c r="AC32">
-        <v>1.84</v>
-      </c>
-      <c r="AD32">
-        <v>1.53</v>
-      </c>
-      <c r="AE32">
-        <v>1.2</v>
-      </c>
-      <c r="AF32">
-        <v>1.3</v>
-      </c>
-      <c r="AG32">
-        <v>2.3</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5709,22 +5709,22 @@
         <v>2.56</v>
       </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.07</v>
       </c>
       <c r="Y33">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z33">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AA33">
         <v>2.28</v>
@@ -5733,10 +5733,10 @@
         <v>1.6</v>
       </c>
       <c r="AC33">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD33">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE33">
         <v>1.06</v>
@@ -5745,7 +5745,7 @@
         <v>1.9</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5854,22 +5854,22 @@
         <v>1.4</v>
       </c>
       <c r="O34">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="Q34">
         <v>1.89</v>
       </c>
       <c r="R34">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S34">
         <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
         <v>2.5</v>
@@ -5887,19 +5887,19 @@
         <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AA34">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB34">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC34">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AD34">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE34">
         <v>1.14</v>
@@ -5908,7 +5908,7 @@
         <v>1.91</v>
       </c>
       <c r="AG34">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6023,22 +6023,22 @@
         <v>2.72</v>
       </c>
       <c r="Q35">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R35">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
         <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U35">
         <v>2.4</v>
       </c>
       <c r="V35">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6053,19 +6053,19 @@
         <v>4.1</v>
       </c>
       <c r="AA35">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB35">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC35">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD35">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
         <v>1.57</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,19 +6186,19 @@
         <v>1.88</v>
       </c>
       <c r="Q36">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="R36">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="S36">
         <v>1.48</v>
       </c>
       <c r="T36">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="U36">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="V36">
         <v>1.31</v>
@@ -6216,25 +6216,25 @@
         <v>2.69</v>
       </c>
       <c r="AA36">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AB36">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC36">
         <v>4.15</v>
       </c>
       <c r="AD36">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE36">
         <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AG36">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.96</v>
+        <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,22 +6343,22 @@
         <v>1.84</v>
       </c>
       <c r="O37">
-        <v>3.53</v>
+        <v>3.88</v>
       </c>
       <c r="P37">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="Q37">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="R37">
         <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T37">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U37">
         <v>2.6</v>
@@ -6373,13 +6373,13 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z37">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="AA37">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AB37">
         <v>2.13</v>
@@ -6394,7 +6394,7 @@
         <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
         <v>2.11</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,13 +6506,13 @@
         <v>1.85</v>
       </c>
       <c r="O38">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="P38">
-        <v>4.05</v>
+        <v>4.51</v>
       </c>
       <c r="Q38">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R38">
         <v>1.81</v>
@@ -6521,7 +6521,7 @@
         <v>1.57</v>
       </c>
       <c r="T38">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="U38">
         <v>3.72</v>
@@ -6542,13 +6542,13 @@
         <v>2.15</v>
       </c>
       <c r="AA38">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="AB38">
         <v>1.33</v>
       </c>
       <c r="AC38">
-        <v>5.85</v>
+        <v>6.27</v>
       </c>
       <c r="AD38">
         <v>1.07</v>
@@ -6560,7 +6560,7 @@
         <v>2.45</v>
       </c>
       <c r="AG38">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK38">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>0</v>
       </c>
       <c r="Q40">
+        <v>2.42</v>
+      </c>
+      <c r="R40">
+        <v>2.1</v>
+      </c>
+      <c r="S40">
+        <v>1.36</v>
+      </c>
+      <c r="T40">
+        <v>2.75</v>
+      </c>
+      <c r="U40">
+        <v>2.88</v>
+      </c>
+      <c r="V40">
+        <v>1.36</v>
+      </c>
+      <c r="W40">
+        <v>1.04</v>
+      </c>
+      <c r="X40">
+        <v>1.06</v>
+      </c>
+      <c r="Y40">
+        <v>1.36</v>
+      </c>
+      <c r="Z40">
+        <v>3.1</v>
+      </c>
+      <c r="AA40">
         <v>2.25</v>
       </c>
-      <c r="R40">
-        <v>1.97</v>
-      </c>
-      <c r="S40">
-        <v>1.41</v>
-      </c>
-      <c r="T40">
-        <v>2.55</v>
-      </c>
-      <c r="U40">
-        <v>3</v>
-      </c>
-      <c r="V40">
-        <v>1.3</v>
-      </c>
-      <c r="W40">
+      <c r="AB40">
+        <v>1.67</v>
+      </c>
+      <c r="AC40">
+        <v>4.2</v>
+      </c>
+      <c r="AD40">
+        <v>1.2</v>
+      </c>
+      <c r="AE40">
         <v>1.03</v>
       </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.35</v>
-      </c>
-      <c r="Z40">
-        <v>2.74</v>
-      </c>
-      <c r="AA40">
-        <v>2.18</v>
-      </c>
-      <c r="AB40">
-        <v>1.58</v>
-      </c>
-      <c r="AC40">
-        <v>4.05</v>
-      </c>
-      <c r="AD40">
-        <v>1.16</v>
-      </c>
-      <c r="AE40">
-        <v>1.01</v>
-      </c>
       <c r="AF40">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG40">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK40">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>4.23</v>
+        <v>4.75</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U41">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="V41">
+        <v>1.44</v>
+      </c>
+      <c r="W41">
+        <v>1.11</v>
+      </c>
+      <c r="X41">
+        <v>1.04</v>
+      </c>
+      <c r="Y41">
+        <v>1.18</v>
+      </c>
+      <c r="Z41">
+        <v>4.33</v>
+      </c>
+      <c r="AA41">
+        <v>1.65</v>
+      </c>
+      <c r="AB41">
+        <v>2.07</v>
+      </c>
+      <c r="AC41">
+        <v>2.81</v>
+      </c>
+      <c r="AD41">
         <v>1.4</v>
       </c>
-      <c r="W41">
-        <v>1.06</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.23</v>
-      </c>
-      <c r="Z41">
-        <v>3.42</v>
-      </c>
-      <c r="AA41">
-        <v>1.83</v>
-      </c>
-      <c r="AB41">
-        <v>1.84</v>
-      </c>
-      <c r="AC41">
-        <v>3.08</v>
-      </c>
-      <c r="AD41">
-        <v>1.28</v>
-      </c>
       <c r="AE41">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="Q42">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S42">
         <v>1.33</v>
       </c>
       <c r="T42">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U42">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V42">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA42">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AD42">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE42">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AG42">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="O43">
         <v>3</v>
       </c>
       <c r="P43">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="Q43">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="R43">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S43">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T43">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U43">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="V43">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="Z43">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="AA43">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="AB43">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AC43">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="AD43">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AG43">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
+        <v>1.3</v>
+      </c>
+      <c r="AK43">
         <v>1.28</v>
-      </c>
-      <c r="AK43">
-        <v>1.36</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7484,40 +7484,40 @@
         <v>1.54</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P44">
         <v>4.5</v>
       </c>
       <c r="Q44">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R44">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="S44">
         <v>1.22</v>
       </c>
       <c r="T44">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U44">
         <v>2.06</v>
       </c>
       <c r="V44">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W44">
         <v>1.14</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
         <v>1.11</v>
       </c>
       <c r="Z44">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA44">
         <v>1.44</v>
@@ -7538,7 +7538,7 @@
         <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="O45">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P45">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Q45">
         <v>1.28</v>
       </c>
       <c r="R45">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="S45">
         <v>1.1</v>
@@ -7665,43 +7665,43 @@
         <v>7</v>
       </c>
       <c r="U45">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V45">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="W45">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X45">
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z45">
         <v>17</v>
       </c>
       <c r="AA45">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AB45">
         <v>6</v>
       </c>
       <c r="AC45">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AD45">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AE45">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AF45">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG45">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK45">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,31 +7807,31 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q46">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="R46">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S46">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T46">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="U46">
         <v>2.53</v>
       </c>
       <c r="V46">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
         <v>1.08</v>
@@ -7840,16 +7840,16 @@
         <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z46">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="AA46">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB46">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC46">
         <v>2.93</v>
@@ -7861,10 +7861,10 @@
         <v>1.09</v>
       </c>
       <c r="AF46">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>4.2</v>
       </c>
       <c r="P47">
-        <v>5.1</v>
+        <v>1.49</v>
       </c>
       <c r="Q47">
         <v>2.02</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="O48">
         <v>4.3</v>
       </c>
       <c r="P48">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="Q48">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="R48">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S48">
         <v>1.22</v>
@@ -8154,31 +8154,31 @@
         <v>3.5</v>
       </c>
       <c r="U48">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V48">
         <v>1.58</v>
       </c>
       <c r="W48">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>4.76</v>
+        <v>4.9</v>
       </c>
       <c r="AA48">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB48">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC48">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AD48">
         <v>1.54</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK48">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,37 +8296,37 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="O49">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q49">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
         <v>1.25</v>
       </c>
       <c r="T49">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
         <v>2.25</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
         <v>1.12</v>
@@ -8335,10 +8335,10 @@
         <v>4.65</v>
       </c>
       <c r="AA49">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB49">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC49">
         <v>2.33</v>
@@ -8350,10 +8350,10 @@
         <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG49">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AK49">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,13 +8462,13 @@
         <v>1.68</v>
       </c>
       <c r="O50">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R50">
         <v>2.25</v>
@@ -8480,31 +8480,31 @@
         <v>2.96</v>
       </c>
       <c r="U50">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="V50">
         <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Z50">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA50">
         <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AC50">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD50">
         <v>1.33</v>
@@ -8513,10 +8513,10 @@
         <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O59">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P59">
         <v>2.85</v>
@@ -9950,7 +9950,7 @@
         <v>2.2</v>
       </c>
       <c r="V59">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W59">
         <v>1.14</v>
@@ -9968,10 +9968,10 @@
         <v>1.46</v>
       </c>
       <c r="AB59">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AC59">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AD59">
         <v>1.6</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AK59">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O60">
         <v>4.5</v>
@@ -10098,7 +10098,7 @@
         <v>5.4</v>
       </c>
       <c r="Q60">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R60">
         <v>2.42</v>
@@ -10110,7 +10110,7 @@
         <v>3.9</v>
       </c>
       <c r="U60">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V60">
         <v>1.65</v>
@@ -10125,28 +10125,28 @@
         <v>1.11</v>
       </c>
       <c r="Z60">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA60">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB60">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AC60">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AD60">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE60">
         <v>1.23</v>
       </c>
       <c r="AF60">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG60">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.14</v>
       </c>
       <c r="AK60">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,31 +10252,31 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q61">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R61">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S61">
         <v>1.25</v>
       </c>
       <c r="T61">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U61">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V61">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W61">
         <v>1.11</v>
@@ -10288,28 +10288,28 @@
         <v>1.16</v>
       </c>
       <c r="Z61">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA61">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AB61">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC61">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AD61">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE61">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF61">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG61">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK61">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,16 +10415,16 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q62">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="R62">
         <v>2.25</v>
@@ -10436,10 +10436,10 @@
         <v>3.3</v>
       </c>
       <c r="U62">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V62">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W62">
         <v>1.11</v>
@@ -10448,22 +10448,22 @@
         <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z62">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA62">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB62">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AC62">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="AD62">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE62">
         <v>1.12</v>
@@ -10472,7 +10472,7 @@
         <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK62">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="O4">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P4">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
       </c>
       <c r="R4">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="S4">
         <v>1.53</v>
@@ -985,7 +985,7 @@
         <v>3.42</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="W4">
         <v>1.02</v>
@@ -997,13 +997,13 @@
         <v>1.47</v>
       </c>
       <c r="Z4">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AA4">
         <v>2.44</v>
       </c>
       <c r="AB4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC4">
         <v>4.55</v>
@@ -1012,13 +1012,13 @@
         <v>1.13</v>
       </c>
       <c r="AE4">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF4">
         <v>2.01</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
         <v>1.4</v>
@@ -4393,10 +4393,10 @@
         <v>1.67</v>
       </c>
       <c r="Q25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S25">
         <v>1.48</v>
@@ -4405,7 +4405,7 @@
         <v>2.38</v>
       </c>
       <c r="U25">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="V25">
         <v>1.29</v>
@@ -4423,10 +4423,10 @@
         <v>2.88</v>
       </c>
       <c r="AA25">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AB25">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC25">
         <v>3.82</v>
@@ -4435,13 +4435,13 @@
         <v>1.2</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.87</v>
+        <v>1.53</v>
       </c>
       <c r="O29">
-        <v>3.55</v>
+        <v>4.05</v>
       </c>
       <c r="P29">
-        <v>2.16</v>
+        <v>4.8</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="R29">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="T29">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="U29">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="V29">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W29">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z29">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA29">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AB29">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC29">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD29">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AF29">
         <v>1.44</v>
       </c>
       <c r="AG29">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="AK29">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.53</v>
+        <v>2.87</v>
       </c>
       <c r="O31">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="P31">
-        <v>4.8</v>
+        <v>2.16</v>
       </c>
       <c r="Q31">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="S31">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="U31">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="V31">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="W31">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="Z31">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA31">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AB31">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC31">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AD31">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AE31">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
         <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AK31">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="Q33">
-        <v>3.18</v>
+        <v>1.89</v>
       </c>
       <c r="R33">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="S33">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
+        <v>3.3</v>
+      </c>
+      <c r="U33">
+        <v>2.5</v>
+      </c>
+      <c r="V33">
+        <v>1.5</v>
+      </c>
+      <c r="W33">
+        <v>1.11</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.2</v>
+      </c>
+      <c r="Z33">
+        <v>4.15</v>
+      </c>
+      <c r="AA33">
+        <v>1.71</v>
+      </c>
+      <c r="AB33">
+        <v>2.16</v>
+      </c>
+      <c r="AC33">
         <v>2.56</v>
       </c>
-      <c r="U33">
-        <v>3</v>
-      </c>
-      <c r="V33">
-        <v>1.34</v>
-      </c>
-      <c r="W33">
-        <v>1.06</v>
-      </c>
-      <c r="X33">
-        <v>1.07</v>
-      </c>
-      <c r="Y33">
-        <v>1.4</v>
-      </c>
-      <c r="Z33">
-        <v>2.88</v>
-      </c>
-      <c r="AA33">
-        <v>2.28</v>
-      </c>
-      <c r="AB33">
-        <v>1.6</v>
-      </c>
-      <c r="AC33">
-        <v>4.5</v>
-      </c>
       <c r="AD33">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG33">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK33">
-        <v>1.48</v>
+        <v>2.56</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>3.18</v>
+      </c>
+      <c r="R34">
+        <v>1.95</v>
+      </c>
+      <c r="S34">
+        <v>1.42</v>
+      </c>
+      <c r="T34">
+        <v>2.56</v>
+      </c>
+      <c r="U34">
+        <v>3</v>
+      </c>
+      <c r="V34">
+        <v>1.34</v>
+      </c>
+      <c r="W34">
+        <v>1.06</v>
+      </c>
+      <c r="X34">
+        <v>1.07</v>
+      </c>
+      <c r="Y34">
         <v>1.4</v>
       </c>
-      <c r="O34">
-        <v>5</v>
-      </c>
-      <c r="P34">
-        <v>6.7</v>
-      </c>
-      <c r="Q34">
-        <v>1.89</v>
-      </c>
-      <c r="R34">
-        <v>2.4</v>
-      </c>
-      <c r="S34">
+      <c r="Z34">
+        <v>2.88</v>
+      </c>
+      <c r="AA34">
+        <v>2.28</v>
+      </c>
+      <c r="AB34">
+        <v>1.6</v>
+      </c>
+      <c r="AC34">
+        <v>4.5</v>
+      </c>
+      <c r="AD34">
+        <v>1.2</v>
+      </c>
+      <c r="AE34">
+        <v>1.06</v>
+      </c>
+      <c r="AF34">
+        <v>1.9</v>
+      </c>
+      <c r="AG34">
+        <v>1.8</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
         <v>1.3</v>
       </c>
-      <c r="T34">
-        <v>3.3</v>
-      </c>
-      <c r="U34">
-        <v>2.5</v>
-      </c>
-      <c r="V34">
-        <v>1.5</v>
-      </c>
-      <c r="W34">
-        <v>1.11</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.2</v>
-      </c>
-      <c r="Z34">
-        <v>4.15</v>
-      </c>
-      <c r="AA34">
-        <v>1.71</v>
-      </c>
-      <c r="AB34">
-        <v>2.16</v>
-      </c>
-      <c r="AC34">
-        <v>2.56</v>
-      </c>
-      <c r="AD34">
-        <v>1.43</v>
-      </c>
-      <c r="AE34">
-        <v>1.14</v>
-      </c>
-      <c r="AF34">
-        <v>1.91</v>
-      </c>
-      <c r="AG34">
-        <v>1.82</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.11</v>
-      </c>
       <c r="AK34">
-        <v>2.56</v>
+        <v>1.48</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>3.6</v>
+        <v>2.91</v>
       </c>
       <c r="Q2">
-        <v>2.41</v>
+        <v>2.69</v>
       </c>
       <c r="R2">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
         <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="U2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>4.33</v>
+        <v>4.11</v>
       </c>
       <c r="AA2">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB2">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC2">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="AD2">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG2">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK2">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,10 +807,10 @@
         <v>3.01</v>
       </c>
       <c r="Q3">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="R3">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S3">
         <v>1.47</v>
@@ -819,10 +819,10 @@
         <v>2.45</v>
       </c>
       <c r="U3">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
         <v>1.01</v>
@@ -834,16 +834,16 @@
         <v>1.36</v>
       </c>
       <c r="Z3">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA3">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AC3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD3">
         <v>1.17</v>
@@ -852,10 +852,10 @@
         <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.35</v>
       </c>
       <c r="AK3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,22 +961,22 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="O4">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P4">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>3.5</v>
+        <v>4.02</v>
       </c>
       <c r="R4">
         <v>1.8</v>
       </c>
       <c r="S4">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T4">
         <v>2.2</v>
@@ -988,22 +988,22 @@
         <v>1.23</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z4">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AA4">
         <v>2.44</v>
       </c>
       <c r="AB4">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AC4">
         <v>4.55</v>
@@ -1018,7 +1018,7 @@
         <v>2.01</v>
       </c>
       <c r="AG4">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.33</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="P8">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="Q8">
         <v>3.7</v>
@@ -1628,13 +1628,13 @@
         <v>2</v>
       </c>
       <c r="S8">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="T8">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="V8">
         <v>1.34</v>
@@ -1649,19 +1649,19 @@
         <v>1.32</v>
       </c>
       <c r="Z8">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="AA8">
         <v>2.19</v>
       </c>
       <c r="AB8">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AC8">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="AD8">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
         <v>1.03</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AK8">
         <v>1.42</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="O9">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R9">
         <v>2.31</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AB9">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AC9">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="AD9">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE9">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG9">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q10">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U10">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="V10">
         <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
         <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG10">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
+        <v>1.22</v>
+      </c>
+      <c r="AK10">
         <v>1.25</v>
-      </c>
-      <c r="AK10">
-        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>5.75</v>
       </c>
       <c r="Q13">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="R13">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="S13">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T13">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="U13">
         <v>2.06</v>
@@ -2455,7 +2455,7 @@
         <v>1.67</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2473,7 +2473,7 @@
         <v>2.59</v>
       </c>
       <c r="AC13">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AD13">
         <v>1.67</v>
@@ -2501,7 +2501,7 @@
         <v>1.03</v>
       </c>
       <c r="AK13">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="O14">
         <v>3.83</v>
@@ -2600,55 +2600,55 @@
         <v>1.45</v>
       </c>
       <c r="Q14">
-        <v>4.65</v>
+        <v>5.21</v>
       </c>
       <c r="R14">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T14">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="U14">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V14">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="AA14">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB14">
+        <v>2.31</v>
+      </c>
+      <c r="AC14">
         <v>2.28</v>
       </c>
-      <c r="AC14">
-        <v>2.38</v>
-      </c>
       <c r="AD14">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF14">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="P15">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,58 +3409,58 @@
         <v>2.4</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P19">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q19">
-        <v>2.9</v>
+        <v>3.26</v>
       </c>
       <c r="R19">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T19">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="U19">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>1.34</v>
+      </c>
+      <c r="Z19">
+        <v>2.78</v>
+      </c>
+      <c r="AA19">
+        <v>2.15</v>
+      </c>
+      <c r="AB19">
+        <v>1.6</v>
+      </c>
+      <c r="AC19">
+        <v>3.86</v>
+      </c>
+      <c r="AD19">
+        <v>1.2</v>
+      </c>
+      <c r="AE19">
         <v>1.02</v>
       </c>
-      <c r="Y19">
-        <v>1.32</v>
-      </c>
-      <c r="Z19">
-        <v>2.88</v>
-      </c>
-      <c r="AA19">
-        <v>2.05</v>
-      </c>
-      <c r="AB19">
-        <v>1.66</v>
-      </c>
-      <c r="AC19">
-        <v>3.9</v>
-      </c>
-      <c r="AD19">
-        <v>1.22</v>
-      </c>
-      <c r="AE19">
-        <v>1.03</v>
-      </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG19">
         <v>1.85</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK19">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
+        <v>2</v>
+      </c>
+      <c r="O20">
+        <v>3.1</v>
+      </c>
+      <c r="P20">
+        <v>3.4</v>
+      </c>
+      <c r="Q20">
+        <v>2.65</v>
+      </c>
+      <c r="R20">
         <v>1.95</v>
       </c>
-      <c r="O20">
-        <v>3</v>
-      </c>
-      <c r="P20">
-        <v>4.1</v>
-      </c>
-      <c r="Q20">
-        <v>2.58</v>
-      </c>
-      <c r="R20">
-        <v>1.92</v>
-      </c>
       <c r="S20">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U20">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="V20">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W20">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z20">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AA20">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AB20">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC20">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD20">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG20">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK20">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="O21">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P21">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="Q21">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T21">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U21">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
+        <v>1.36</v>
+      </c>
+      <c r="Z21">
+        <v>2.69</v>
+      </c>
+      <c r="AA21">
+        <v>2.2</v>
+      </c>
+      <c r="AB21">
+        <v>1.61</v>
+      </c>
+      <c r="AC21">
+        <v>4.4</v>
+      </c>
+      <c r="AD21">
+        <v>1.17</v>
+      </c>
+      <c r="AE21">
+        <v>1.02</v>
+      </c>
+      <c r="AF21">
+        <v>1.86</v>
+      </c>
+      <c r="AG21">
+        <v>1.81</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.3</v>
       </c>
-      <c r="Z21">
-        <v>3.25</v>
-      </c>
-      <c r="AA21">
-        <v>1.94</v>
-      </c>
-      <c r="AB21">
-        <v>1.76</v>
-      </c>
-      <c r="AC21">
-        <v>3.28</v>
-      </c>
-      <c r="AD21">
-        <v>1.25</v>
-      </c>
-      <c r="AE21">
-        <v>1.06</v>
-      </c>
-      <c r="AF21">
-        <v>1.8</v>
-      </c>
-      <c r="AG21">
-        <v>1.85</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.7</v>
-      </c>
       <c r="AK21">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22">
-        <v>3.2</v>
+        <v>4.39</v>
       </c>
       <c r="R22">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="S22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="U22">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA22">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AB22">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC22">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD22">
         <v>1.25</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF22">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK22">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q23">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="R23">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="S23">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="U23">
-        <v>3.6</v>
+        <v>2.73</v>
       </c>
       <c r="V23">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
+        <v>1.06</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.3</v>
+      </c>
+      <c r="Z23">
+        <v>2.97</v>
+      </c>
+      <c r="AA23">
+        <v>2.02</v>
+      </c>
+      <c r="AB23">
+        <v>1.71</v>
+      </c>
+      <c r="AC23">
+        <v>3.42</v>
+      </c>
+      <c r="AD23">
+        <v>1.23</v>
+      </c>
+      <c r="AE23">
         <v>1.05</v>
       </c>
-      <c r="X23">
-        <v>1.06</v>
-      </c>
-      <c r="Y23">
-        <v>1.43</v>
-      </c>
-      <c r="Z23">
-        <v>2.46</v>
-      </c>
-      <c r="AA23">
-        <v>2.35</v>
-      </c>
-      <c r="AB23">
-        <v>1.49</v>
-      </c>
-      <c r="AC23">
-        <v>5</v>
-      </c>
-      <c r="AD23">
-        <v>1.13</v>
-      </c>
-      <c r="AE23">
-        <v>1.02</v>
-      </c>
       <c r="AF23">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG23">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="O24">
+        <v>2.8</v>
+      </c>
+      <c r="P24">
         <v>2.9</v>
       </c>
-      <c r="P24">
-        <v>2.5</v>
-      </c>
       <c r="Q24">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="S24">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="T24">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="U24">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W24">
+        <v>1.01</v>
+      </c>
+      <c r="X24">
+        <v>1.06</v>
+      </c>
+      <c r="Y24">
+        <v>1.43</v>
+      </c>
+      <c r="Z24">
+        <v>2.46</v>
+      </c>
+      <c r="AA24">
+        <v>2.44</v>
+      </c>
+      <c r="AB24">
+        <v>1.46</v>
+      </c>
+      <c r="AC24">
+        <v>4.65</v>
+      </c>
+      <c r="AD24">
+        <v>1.12</v>
+      </c>
+      <c r="AE24">
         <v>1.05</v>
       </c>
-      <c r="X24">
-        <v>1.04</v>
-      </c>
-      <c r="Y24">
-        <v>1.4</v>
-      </c>
-      <c r="Z24">
-        <v>2.75</v>
-      </c>
-      <c r="AA24">
-        <v>2.26</v>
-      </c>
-      <c r="AB24">
-        <v>1.61</v>
-      </c>
-      <c r="AC24">
-        <v>4.4</v>
-      </c>
-      <c r="AD24">
-        <v>1.18</v>
-      </c>
-      <c r="AE24">
-        <v>1.04</v>
-      </c>
       <c r="AF24">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AG24">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
+        <v>1.35</v>
+      </c>
+      <c r="AK24">
         <v>1.39</v>
-      </c>
-      <c r="AK24">
-        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,49 +4393,49 @@
         <v>1.67</v>
       </c>
       <c r="Q25">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="R25">
         <v>1.96</v>
       </c>
       <c r="S25">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T25">
         <v>2.38</v>
       </c>
       <c r="U25">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="V25">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
         <v>1.4</v>
       </c>
       <c r="Z25">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA25">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB25">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC25">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="AD25">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
         <v>2.05</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
         <v>1.1</v>
@@ -4547,25 +4547,25 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P26">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="Q26">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="R26">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="S26">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U26">
         <v>2.02</v>
@@ -4574,53 +4574,53 @@
         <v>1.72</v>
       </c>
       <c r="W26">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z26">
         <v>5.7</v>
       </c>
       <c r="AA26">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB26">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC26">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AD26">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE26">
+        <v>1.27</v>
+      </c>
+      <c r="AF26">
+        <v>1.36</v>
+      </c>
+      <c r="AG26">
+        <v>2.88</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.29</v>
       </c>
-      <c r="AF26">
-        <v>1.38</v>
-      </c>
-      <c r="AG26">
-        <v>2.81</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.17</v>
-      </c>
       <c r="AK26">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="O27">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P27">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q27">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="R27">
         <v>2.32</v>
@@ -4728,62 +4728,62 @@
         <v>1.22</v>
       </c>
       <c r="T27">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="U27">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V27">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W27">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z27">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA27">
+        <v>1.42</v>
+      </c>
+      <c r="AB27">
+        <v>2.49</v>
+      </c>
+      <c r="AC27">
+        <v>2.13</v>
+      </c>
+      <c r="AD27">
+        <v>1.67</v>
+      </c>
+      <c r="AE27">
+        <v>1.23</v>
+      </c>
+      <c r="AF27">
+        <v>1.39</v>
+      </c>
+      <c r="AG27">
+        <v>2.77</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.26</v>
+      </c>
+      <c r="AK27">
         <v>1.4</v>
-      </c>
-      <c r="AB27">
-        <v>2.88</v>
-      </c>
-      <c r="AC27">
-        <v>2.1</v>
-      </c>
-      <c r="AD27">
-        <v>1.73</v>
-      </c>
-      <c r="AE27">
-        <v>1.3</v>
-      </c>
-      <c r="AF27">
-        <v>1.4</v>
-      </c>
-      <c r="AG27">
-        <v>2.75</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.23</v>
-      </c>
-      <c r="AK27">
-        <v>1.38</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O28">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q28">
+        <v>3.4</v>
+      </c>
+      <c r="R28">
+        <v>2.19</v>
+      </c>
+      <c r="S28">
+        <v>1.26</v>
+      </c>
+      <c r="T28">
         <v>3.24</v>
       </c>
-      <c r="R28">
-        <v>2.1</v>
-      </c>
-      <c r="S28">
-        <v>1.33</v>
-      </c>
-      <c r="T28">
-        <v>3</v>
-      </c>
       <c r="U28">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z28">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="AA28">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AB28">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AC28">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="AD28">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AK28">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,31 +5039,31 @@
         <v>1.53</v>
       </c>
       <c r="O29">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P29">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q29">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="R29">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="S29">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T29">
         <v>4.35</v>
       </c>
       <c r="U29">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="V29">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W29">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5078,7 +5078,7 @@
         <v>1.25</v>
       </c>
       <c r="AB29">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="AC29">
         <v>1.85</v>
@@ -5090,10 +5090,10 @@
         <v>1.32</v>
       </c>
       <c r="AF29">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG29">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK29">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
+        <v>2.5</v>
+      </c>
+      <c r="O30">
+        <v>3.2</v>
+      </c>
+      <c r="P30">
+        <v>2.45</v>
+      </c>
+      <c r="Q30">
+        <v>3.28</v>
+      </c>
+      <c r="R30">
+        <v>2.09</v>
+      </c>
+      <c r="S30">
+        <v>1.35</v>
+      </c>
+      <c r="T30">
+        <v>2.76</v>
+      </c>
+      <c r="U30">
         <v>2.74</v>
       </c>
-      <c r="O30">
-        <v>3.45</v>
-      </c>
-      <c r="P30">
-        <v>2.3</v>
-      </c>
-      <c r="Q30">
-        <v>2.78</v>
-      </c>
-      <c r="R30">
-        <v>2.26</v>
-      </c>
-      <c r="S30">
-        <v>1.25</v>
-      </c>
-      <c r="T30">
-        <v>3.3</v>
-      </c>
-      <c r="U30">
-        <v>1.96</v>
-      </c>
       <c r="V30">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W30">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z30">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA30">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AB30">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="AC30">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="AD30">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AE30">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AG30">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,40 +5365,40 @@
         <v>2.87</v>
       </c>
       <c r="O31">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="R31">
         <v>2.28</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T31">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="U31">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="V31">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z31">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA31">
         <v>1.47</v>
@@ -5407,19 +5407,19 @@
         <v>2.35</v>
       </c>
       <c r="AC31">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AD31">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF31">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG31">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,55 +5525,55 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="O32">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q32">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="R32">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T32">
-        <v>2.9</v>
+        <v>3.74</v>
       </c>
       <c r="U32">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="V32">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W32">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
         <v>1.1</v>
       </c>
       <c r="Z32">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="AA32">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="AC32">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AD32">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE32">
         <v>1.29</v>
@@ -5582,7 +5582,7 @@
         <v>1.41</v>
       </c>
       <c r="AG32">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="O33">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P33">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q33">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R33">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33">
         <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="AA33">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AB33">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC33">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="AD33">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG33">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q34">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R34">
         <v>1.95</v>
       </c>
       <c r="S34">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="T34">
         <v>2.56</v>
       </c>
       <c r="U34">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="V34">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W34">
         <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z34">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AA34">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AB34">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC34">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="AD34">
         <v>1.2</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG34">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,22 +6014,22 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
         <v>2.72</v>
       </c>
       <c r="Q35">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T35">
         <v>3.26</v>
@@ -6038,10 +6038,10 @@
         <v>2.4</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X35">
         <v>1.02</v>
@@ -6050,22 +6050,22 @@
         <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA35">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB35">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC35">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD35">
         <v>1.37</v>
       </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
         <v>1.57</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="P36">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="Q36">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="R36">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="S36">
         <v>1.48</v>
       </c>
       <c r="T36">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="U36">
         <v>3.32</v>
@@ -6210,19 +6210,19 @@
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z36">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="AA36">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="AB36">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC36">
-        <v>4.15</v>
+        <v>4.48</v>
       </c>
       <c r="AD36">
         <v>1.21</v>
@@ -6231,10 +6231,10 @@
         <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AG36">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,61 +6343,61 @@
         <v>1.84</v>
       </c>
       <c r="O37">
-        <v>3.88</v>
+        <v>3.53</v>
       </c>
       <c r="P37">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="Q37">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="R37">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="U37">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V37">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="AA37">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AB37">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC37">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AD37">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE37">
         <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG37">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
         <v>1.96</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P39">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q40">
+        <v>3.88</v>
+      </c>
+      <c r="R40">
+        <v>1.88</v>
+      </c>
+      <c r="S40">
+        <v>1.45</v>
+      </c>
+      <c r="T40">
         <v>2.42</v>
       </c>
-      <c r="R40">
-        <v>2.1</v>
-      </c>
-      <c r="S40">
-        <v>1.36</v>
-      </c>
-      <c r="T40">
-        <v>2.75</v>
-      </c>
       <c r="U40">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W40">
+        <v>1.03</v>
+      </c>
+      <c r="X40">
+        <v>1.03</v>
+      </c>
+      <c r="Y40">
+        <v>1.31</v>
+      </c>
+      <c r="Z40">
+        <v>2.92</v>
+      </c>
+      <c r="AA40">
+        <v>2.02</v>
+      </c>
+      <c r="AB40">
+        <v>1.72</v>
+      </c>
+      <c r="AC40">
+        <v>3.42</v>
+      </c>
+      <c r="AD40">
+        <v>1.23</v>
+      </c>
+      <c r="AE40">
         <v>1.04</v>
       </c>
-      <c r="X40">
-        <v>1.06</v>
-      </c>
-      <c r="Y40">
-        <v>1.36</v>
-      </c>
-      <c r="Z40">
-        <v>3.1</v>
-      </c>
-      <c r="AA40">
-        <v>2.25</v>
-      </c>
-      <c r="AB40">
-        <v>1.67</v>
-      </c>
-      <c r="AC40">
-        <v>4.2</v>
-      </c>
-      <c r="AD40">
-        <v>1.2</v>
-      </c>
-      <c r="AE40">
-        <v>1.03</v>
-      </c>
       <c r="AF40">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q41">
-        <v>4.75</v>
+        <v>2.46</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="T41">
-        <v>3.18</v>
+        <v>2.48</v>
       </c>
       <c r="U41">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z41">
-        <v>4.33</v>
+        <v>2.83</v>
       </c>
       <c r="AA41">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="AB41">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AC41">
-        <v>2.81</v>
+        <v>3.8</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AG41">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK41">
-        <v>1.18</v>
+        <v>1.84</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,34 +7155,34 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.53</v>
+        <v>3.8</v>
       </c>
       <c r="O42">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q42">
-        <v>2</v>
+        <v>4.43</v>
       </c>
       <c r="R42">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
         <v>3.08</v>
       </c>
       <c r="U42">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
         <v>1.03</v>
@@ -7191,28 +7191,28 @@
         <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AC42">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD42">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AG42">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="O43">
+        <v>3.75</v>
+      </c>
+      <c r="P43">
+        <v>4.8</v>
+      </c>
+      <c r="Q43">
+        <v>2.11</v>
+      </c>
+      <c r="R43">
+        <v>2.22</v>
+      </c>
+      <c r="S43">
+        <v>1.38</v>
+      </c>
+      <c r="T43">
         <v>3</v>
       </c>
-      <c r="P43">
-        <v>2.33</v>
-      </c>
-      <c r="Q43">
-        <v>3.6</v>
-      </c>
-      <c r="R43">
-        <v>1.89</v>
-      </c>
-      <c r="S43">
-        <v>1.44</v>
-      </c>
-      <c r="T43">
-        <v>2.75</v>
-      </c>
       <c r="U43">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W43">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA43">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AB43">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AC43">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="AD43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE43">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF43">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG43">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK43">
-        <v>1.28</v>
+        <v>2.16</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="O45">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P45">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q45">
         <v>1.28</v>
       </c>
       <c r="R45">
-        <v>4.5</v>
+        <v>4.13</v>
       </c>
       <c r="S45">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="T45">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="U45">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="V45">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="W45">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X45">
         <v>1</v>
@@ -7680,28 +7680,28 @@
         <v>1.02</v>
       </c>
       <c r="Z45">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA45">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AB45">
         <v>6</v>
       </c>
       <c r="AC45">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AD45">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AE45">
         <v>2.14</v>
       </c>
       <c r="AF45">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK45">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,28 +7807,28 @@
         </is>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P46">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q46">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="R46">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S46">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T46">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U46">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="V46">
         <v>1.44</v>
@@ -7837,7 +7837,7 @@
         <v>1.08</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
         <v>1.24</v>
@@ -7846,10 +7846,10 @@
         <v>3.56</v>
       </c>
       <c r="AA46">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB46">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AC46">
         <v>2.93</v>
@@ -7858,13 +7858,13 @@
         <v>1.34</v>
       </c>
       <c r="AE46">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG46">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AK46">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL46">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -964,28 +964,28 @@
         <v>2.75</v>
       </c>
       <c r="O4">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q4">
-        <v>4.02</v>
+        <v>3.6</v>
       </c>
       <c r="R4">
         <v>1.8</v>
       </c>
       <c r="S4">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="U4">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="V4">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W4">
         <v>1.03</v>
@@ -1000,7 +1000,7 @@
         <v>2.43</v>
       </c>
       <c r="AA4">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="AB4">
         <v>1.47</v>
@@ -1287,43 +1287,43 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O6">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="P6">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="R6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U6">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="V6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W6">
         <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y6">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z6">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AA6">
         <v>2.83</v>
@@ -1332,7 +1332,7 @@
         <v>1.33</v>
       </c>
       <c r="AC6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AD6">
         <v>1.08</v>
@@ -1341,10 +1341,10 @@
         <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AG6">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,28 +1450,28 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P7">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>5.07</v>
+        <v>5.12</v>
       </c>
       <c r="R7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S7">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="T7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U7">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="V7">
         <v>1.17</v>
@@ -1480,22 +1480,22 @@
         <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y7">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AA7">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AB7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC7">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="AD7">
         <v>1.07</v>
@@ -1504,10 +1504,10 @@
         <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AG7">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
         <v>1.18</v>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
+        <v>3.1</v>
+      </c>
+      <c r="O10">
+        <v>3.45</v>
+      </c>
+      <c r="P10">
+        <v>2.06</v>
+      </c>
+      <c r="Q10">
+        <v>3.74</v>
+      </c>
+      <c r="R10">
+        <v>2.13</v>
+      </c>
+      <c r="S10">
+        <v>1.3</v>
+      </c>
+      <c r="T10">
         <v>3</v>
-      </c>
-      <c r="O10">
-        <v>3.3</v>
-      </c>
-      <c r="P10">
-        <v>2.05</v>
-      </c>
-      <c r="Q10">
-        <v>3.78</v>
-      </c>
-      <c r="R10">
-        <v>2.25</v>
-      </c>
-      <c r="S10">
-        <v>1.28</v>
-      </c>
-      <c r="T10">
-        <v>3.08</v>
       </c>
       <c r="U10">
         <v>2.44</v>
@@ -1972,16 +1972,16 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
         <v>2.88</v>
@@ -1990,13 +1990,13 @@
         <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>5.45</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P11">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="Q11">
-        <v>7.9</v>
+        <v>5.75</v>
       </c>
       <c r="R11">
         <v>2.05</v>
       </c>
       <c r="S11">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="V11">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z11">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AA11">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AB11">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AC11">
-        <v>4.25</v>
+        <v>3.86</v>
       </c>
       <c r="AD11">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE11">
         <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AG11">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.34</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O12">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="P12">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q12">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="R12">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="S12">
         <v>1.2</v>
@@ -2289,13 +2289,13 @@
         <v>2.07</v>
       </c>
       <c r="V12">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W12">
         <v>1.14</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.08</v>
@@ -2304,25 +2304,25 @@
         <v>5.45</v>
       </c>
       <c r="AA12">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB12">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="AC12">
         <v>2.02</v>
       </c>
       <c r="AD12">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE12">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2431,61 +2431,61 @@
         <v>1.24</v>
       </c>
       <c r="O13">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q13">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="R13">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S13">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T13">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="U13">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="V13">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z13">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="AA13">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AB13">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AC13">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AD13">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF13">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AG13">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AK13">
         <v>2.75</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="O15">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="Q15">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="S15">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="U15">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="V15">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="Z15">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="AA15">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AB15">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AC15">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AE15">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AG15">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AK15">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
+        <v>1.67</v>
+      </c>
+      <c r="O16">
+        <v>3.65</v>
+      </c>
+      <c r="P16">
+        <v>4.4</v>
+      </c>
+      <c r="Q16">
+        <v>2.32</v>
+      </c>
+      <c r="R16">
+        <v>2.23</v>
+      </c>
+      <c r="S16">
+        <v>1.35</v>
+      </c>
+      <c r="T16">
+        <v>2.9</v>
+      </c>
+      <c r="U16">
+        <v>2.7</v>
+      </c>
+      <c r="V16">
+        <v>1.41</v>
+      </c>
+      <c r="W16">
+        <v>1.06</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>1.28</v>
+      </c>
+      <c r="Z16">
+        <v>3.2</v>
+      </c>
+      <c r="AA16">
         <v>1.9</v>
       </c>
-      <c r="O16">
-        <v>3.1</v>
-      </c>
-      <c r="P16">
-        <v>3.95</v>
-      </c>
-      <c r="Q16">
-        <v>2.62</v>
-      </c>
-      <c r="R16">
-        <v>2.03</v>
-      </c>
-      <c r="S16">
-        <v>1.45</v>
-      </c>
-      <c r="T16">
-        <v>2.55</v>
-      </c>
-      <c r="U16">
-        <v>3.2</v>
-      </c>
-      <c r="V16">
-        <v>1.29</v>
-      </c>
-      <c r="W16">
-        <v>1.03</v>
-      </c>
-      <c r="X16">
-        <v>1.05</v>
-      </c>
-      <c r="Y16">
-        <v>1.42</v>
-      </c>
-      <c r="Z16">
-        <v>2.65</v>
-      </c>
-      <c r="AA16">
-        <v>2.3</v>
-      </c>
       <c r="AB16">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AD16">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P28">
-        <v>2.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q28">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="R28">
-        <v>2.19</v>
+        <v>2.52</v>
       </c>
       <c r="S28">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="T28">
-        <v>3.24</v>
+        <v>4.35</v>
       </c>
       <c r="U28">
-        <v>2.43</v>
+        <v>1.89</v>
       </c>
       <c r="V28">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z28">
-        <v>3.13</v>
+        <v>4</v>
       </c>
       <c r="AA28">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AB28">
-        <v>2.18</v>
+        <v>2.92</v>
       </c>
       <c r="AC28">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="AE28">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AF28">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AG28">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AK28">
-        <v>1.4</v>
+        <v>2.28</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P29">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q29">
-        <v>1.97</v>
+        <v>3.28</v>
       </c>
       <c r="R29">
-        <v>2.52</v>
+        <v>2.09</v>
       </c>
       <c r="S29">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="T29">
-        <v>4.35</v>
+        <v>2.76</v>
       </c>
       <c r="U29">
-        <v>1.89</v>
+        <v>2.74</v>
       </c>
       <c r="V29">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="Z29">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="AA29">
+        <v>1.79</v>
+      </c>
+      <c r="AB29">
+        <v>1.88</v>
+      </c>
+      <c r="AC29">
+        <v>2.88</v>
+      </c>
+      <c r="AD29">
+        <v>1.32</v>
+      </c>
+      <c r="AE29">
+        <v>1.09</v>
+      </c>
+      <c r="AF29">
+        <v>1.63</v>
+      </c>
+      <c r="AG29">
+        <v>2.12</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.25</v>
       </c>
-      <c r="AB29">
-        <v>2.92</v>
-      </c>
-      <c r="AC29">
-        <v>1.85</v>
-      </c>
-      <c r="AD29">
-        <v>1.82</v>
-      </c>
-      <c r="AE29">
-        <v>1.32</v>
-      </c>
-      <c r="AF29">
-        <v>1.41</v>
-      </c>
-      <c r="AG29">
-        <v>2.66</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.1</v>
-      </c>
       <c r="AK29">
-        <v>2.28</v>
+        <v>1.38</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q30">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="R30">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="T30">
-        <v>2.76</v>
+        <v>3.24</v>
       </c>
       <c r="U30">
-        <v>2.74</v>
+        <v>2.43</v>
       </c>
       <c r="V30">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>3.42</v>
+        <v>3.13</v>
       </c>
       <c r="AA30">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="AB30">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AC30">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="AD30">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AG30">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK30">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5688,65 +5688,65 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="O33">
         <v>4.8</v>
       </c>
       <c r="P33">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q33">
         <v>1.87</v>
       </c>
       <c r="R33">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
         <v>1.32</v>
       </c>
       <c r="T33">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA33">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB33">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="AD33">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF33">
+        <v>1.85</v>
+      </c>
+      <c r="AG33">
         <v>1.95</v>
       </c>
-      <c r="AG33">
-        <v>1.78</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK33">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>2.65</v>
       </c>
       <c r="Q34">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="T34">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="U34">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V34">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
+        <v>1.07</v>
+      </c>
+      <c r="X34">
+        <v>1.08</v>
+      </c>
+      <c r="Y34">
+        <v>1.4</v>
+      </c>
+      <c r="Z34">
+        <v>2.88</v>
+      </c>
+      <c r="AA34">
+        <v>2.28</v>
+      </c>
+      <c r="AB34">
+        <v>1.6</v>
+      </c>
+      <c r="AC34">
+        <v>4.33</v>
+      </c>
+      <c r="AD34">
+        <v>1.22</v>
+      </c>
+      <c r="AE34">
         <v>1.06</v>
       </c>
-      <c r="X34">
-        <v>1.04</v>
-      </c>
-      <c r="Y34">
-        <v>1.38</v>
-      </c>
-      <c r="Z34">
-        <v>2.76</v>
-      </c>
-      <c r="AA34">
-        <v>2.34</v>
-      </c>
-      <c r="AB34">
-        <v>1.7</v>
-      </c>
-      <c r="AC34">
-        <v>3.94</v>
-      </c>
-      <c r="AD34">
-        <v>1.2</v>
-      </c>
-      <c r="AE34">
-        <v>1.03</v>
-      </c>
       <c r="AF34">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG34">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="Q35">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="R35">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
         <v>1.28</v>
@@ -6035,10 +6035,10 @@
         <v>3.26</v>
       </c>
       <c r="U35">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V35">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
         <v>1.09</v>
@@ -6047,31 +6047,31 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA35">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB35">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AC35">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AD35">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
         <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6503,25 +6503,25 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O38">
         <v>2.9</v>
       </c>
       <c r="P38">
-        <v>4.51</v>
+        <v>4.33</v>
       </c>
       <c r="Q38">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="R38">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="S38">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T38">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="U38">
         <v>3.72</v>
@@ -6533,7 +6533,7 @@
         <v>1.03</v>
       </c>
       <c r="X38">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y38">
         <v>1.6</v>
@@ -6542,25 +6542,25 @@
         <v>2.15</v>
       </c>
       <c r="AA38">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AB38">
         <v>1.33</v>
       </c>
       <c r="AC38">
-        <v>6.27</v>
+        <v>5.85</v>
       </c>
       <c r="AD38">
         <v>1.07</v>
       </c>
       <c r="AE38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF38">
         <v>2.45</v>
       </c>
       <c r="AG38">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="O44">
+        <v>4</v>
+      </c>
+      <c r="P44">
+        <v>4.2</v>
+      </c>
+      <c r="Q44">
+        <v>2.22</v>
+      </c>
+      <c r="R44">
+        <v>2.36</v>
+      </c>
+      <c r="S44">
+        <v>1.21</v>
+      </c>
+      <c r="T44">
         <v>3.9</v>
       </c>
-      <c r="P44">
-        <v>4.5</v>
-      </c>
-      <c r="Q44">
+      <c r="U44">
+        <v>2.04</v>
+      </c>
+      <c r="V44">
+        <v>1.67</v>
+      </c>
+      <c r="W44">
+        <v>1.17</v>
+      </c>
+      <c r="X44">
+        <v>1.02</v>
+      </c>
+      <c r="Y44">
+        <v>1.13</v>
+      </c>
+      <c r="Z44">
+        <v>6</v>
+      </c>
+      <c r="AA44">
+        <v>1.4</v>
+      </c>
+      <c r="AB44">
+        <v>2.49</v>
+      </c>
+      <c r="AC44">
         <v>2.08</v>
       </c>
-      <c r="R44">
-        <v>2.5</v>
-      </c>
-      <c r="S44">
+      <c r="AD44">
+        <v>1.64</v>
+      </c>
+      <c r="AE44">
+        <v>1.24</v>
+      </c>
+      <c r="AF44">
+        <v>1.44</v>
+      </c>
+      <c r="AG44">
+        <v>2.55</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.22</v>
       </c>
-      <c r="T44">
-        <v>3.75</v>
-      </c>
-      <c r="U44">
-        <v>2.06</v>
-      </c>
-      <c r="V44">
-        <v>1.62</v>
-      </c>
-      <c r="W44">
-        <v>1.14</v>
-      </c>
-      <c r="X44">
-        <v>1.01</v>
-      </c>
-      <c r="Y44">
-        <v>1.11</v>
-      </c>
-      <c r="Z44">
-        <v>5.5</v>
-      </c>
-      <c r="AA44">
-        <v>1.44</v>
-      </c>
-      <c r="AB44">
-        <v>2.43</v>
-      </c>
-      <c r="AC44">
-        <v>2.12</v>
-      </c>
-      <c r="AD44">
-        <v>1.62</v>
-      </c>
-      <c r="AE44">
-        <v>1.23</v>
-      </c>
-      <c r="AF44">
-        <v>1.5</v>
-      </c>
-      <c r="AG44">
-        <v>2.5</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.17</v>
-      </c>
       <c r="AK44">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O45">
         <v>14</v>
       </c>
       <c r="P45">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q45">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="R45">
-        <v>4.13</v>
+        <v>3.8</v>
       </c>
       <c r="S45">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="T45">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="U45">
         <v>1.49</v>
       </c>
       <c r="V45">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="W45">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="X45">
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z45">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA45">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AB45">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AC45">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AD45">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AE45">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG45">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK45">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.98</v>
+        <v>3.38</v>
       </c>
       <c r="O46">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="P46">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="Q46">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="R46">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T46">
-        <v>2.77</v>
+        <v>3.14</v>
       </c>
       <c r="U46">
         <v>2.7</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W46">
         <v>1.08</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z46">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="AA46">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB46">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC46">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="AD46">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG46">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="AK46">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="O47">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="P47">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Q47">
         <v>2.02</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="O48">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="P48">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q48">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="R48">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T48">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U48">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V48">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z48">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AA48">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AB48">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="AC48">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AD48">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK48">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P49">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q49">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S49">
         <v>1.25</v>
@@ -8320,13 +8320,13 @@
         <v>2.25</v>
       </c>
       <c r="V49">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
         <v>1.12</v>
@@ -8335,16 +8335,16 @@
         <v>4.65</v>
       </c>
       <c r="AA49">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB49">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC49">
         <v>2.33</v>
       </c>
       <c r="AD49">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE49">
         <v>1.16</v>
@@ -8353,7 +8353,7 @@
         <v>1.47</v>
       </c>
       <c r="AG49">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q50">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S50">
         <v>1.33</v>
@@ -8480,10 +8480,10 @@
         <v>2.96</v>
       </c>
       <c r="U50">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W50">
         <v>1.06</v>
@@ -8495,28 +8495,28 @@
         <v>1.33</v>
       </c>
       <c r="Z50">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA50">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB50">
         <v>2.03</v>
       </c>
       <c r="AC50">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AD50">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE50">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG50">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G57">
@@ -9926,55 +9926,55 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="O59">
         <v>3.4</v>
       </c>
       <c r="P59">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="Q59">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="R59">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="S59">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T59">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="U59">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V59">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X59">
         <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="Z59">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA59">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB59">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC59">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AD59">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE59">
         <v>1.22</v>
@@ -9983,7 +9983,7 @@
         <v>1.57</v>
       </c>
       <c r="AG59">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
         <v>1.4</v>
@@ -10092,25 +10092,25 @@
         <v>1.5</v>
       </c>
       <c r="O60">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P60">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q60">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R60">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="S60">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
         <v>3.9</v>
       </c>
       <c r="U60">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V60">
         <v>1.65</v>
@@ -10119,13 +10119,13 @@
         <v>1.17</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
         <v>1.11</v>
       </c>
       <c r="Z60">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA60">
         <v>1.47</v>
@@ -10134,19 +10134,19 @@
         <v>2.63</v>
       </c>
       <c r="AC60">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AD60">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE60">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF60">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG60">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.14</v>
       </c>
       <c r="AK60">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,31 +10252,31 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="O61">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P61">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="Q61">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="R61">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S61">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T61">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="U61">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V61">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W61">
         <v>1.11</v>
@@ -10288,28 +10288,28 @@
         <v>1.16</v>
       </c>
       <c r="Z61">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="AA61">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AB61">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC61">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD61">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE61">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF61">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG61">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,28 +10424,28 @@
         <v>3.6</v>
       </c>
       <c r="Q62">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="R62">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S62">
         <v>1.27</v>
       </c>
       <c r="T62">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U62">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V62">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W62">
         <v>1.11</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
         <v>1.17</v>
@@ -10457,10 +10457,10 @@
         <v>1.68</v>
       </c>
       <c r="AB62">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AC62">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="AD62">
         <v>1.39</v>
@@ -10469,7 +10469,7 @@
         <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG62">
         <v>2.15</v>
@@ -10488,7 +10488,7 @@
         <v>1.19</v>
       </c>
       <c r="AK62">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P20">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="R20">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="S20">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T20">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U20">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="V20">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z20">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AA20">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB20">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC20">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="AD20">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE20">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG20">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.62</v>
+        <v>3.51</v>
       </c>
       <c r="O21">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q21">
-        <v>3.5</v>
+        <v>4.39</v>
       </c>
       <c r="R21">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="S21">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="T21">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="U21">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="V21">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="AA21">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB21">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD21">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AG21">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.51</v>
+        <v>2</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
-        <v>4.39</v>
+        <v>2.65</v>
       </c>
       <c r="R22">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T22">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="U22">
+        <v>2.94</v>
+      </c>
+      <c r="V22">
+        <v>1.31</v>
+      </c>
+      <c r="W22">
+        <v>1.03</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>1.33</v>
+      </c>
+      <c r="Z22">
         <v>2.83</v>
       </c>
-      <c r="V22">
-        <v>1.33</v>
-      </c>
-      <c r="W22">
+      <c r="AA22">
+        <v>2.08</v>
+      </c>
+      <c r="AB22">
+        <v>1.64</v>
+      </c>
+      <c r="AC22">
+        <v>3.58</v>
+      </c>
+      <c r="AD22">
+        <v>1.21</v>
+      </c>
+      <c r="AE22">
         <v>1.04</v>
       </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.28</v>
-      </c>
-      <c r="Z22">
-        <v>3.05</v>
-      </c>
-      <c r="AA22">
-        <v>1.95</v>
-      </c>
-      <c r="AB22">
-        <v>1.73</v>
-      </c>
-      <c r="AC22">
-        <v>3.28</v>
-      </c>
-      <c r="AD22">
-        <v>1.25</v>
-      </c>
-      <c r="AE22">
-        <v>1.06</v>
-      </c>
       <c r="AF22">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.26</v>
       </c>
       <c r="AK22">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="O28">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q28">
-        <v>1.97</v>
+        <v>3.4</v>
       </c>
       <c r="R28">
-        <v>2.52</v>
+        <v>2.19</v>
       </c>
       <c r="S28">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="T28">
-        <v>4.35</v>
+        <v>3.24</v>
       </c>
       <c r="U28">
-        <v>1.89</v>
+        <v>2.43</v>
       </c>
       <c r="V28">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="W28">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z28">
-        <v>4</v>
+        <v>3.13</v>
       </c>
       <c r="AA28">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AB28">
-        <v>2.92</v>
+        <v>2.18</v>
       </c>
       <c r="AC28">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="AD28">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AE28">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AG28">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AK28">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="O29">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P29">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q29">
-        <v>3.28</v>
+        <v>1.97</v>
       </c>
       <c r="R29">
-        <v>2.09</v>
+        <v>2.52</v>
       </c>
       <c r="S29">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="T29">
-        <v>2.76</v>
+        <v>4.35</v>
       </c>
       <c r="U29">
-        <v>2.74</v>
+        <v>1.89</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="Z29">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="AA29">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AB29">
-        <v>1.88</v>
+        <v>2.92</v>
       </c>
       <c r="AC29">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="AD29">
+        <v>1.82</v>
+      </c>
+      <c r="AE29">
         <v>1.32</v>
       </c>
-      <c r="AE29">
-        <v>1.09</v>
-      </c>
       <c r="AF29">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AG29">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK29">
-        <v>1.38</v>
+        <v>2.28</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q30">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="R30">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="S30">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>3.24</v>
+        <v>2.76</v>
       </c>
       <c r="U30">
-        <v>2.43</v>
+        <v>2.74</v>
       </c>
       <c r="V30">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z30">
-        <v>3.13</v>
+        <v>3.42</v>
       </c>
       <c r="AA30">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AB30">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AC30">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="AD30">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AE30">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AG30">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P44">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q44">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="R44">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="S44">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U44">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="V44">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="W44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA44">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AB44">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC44">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="AD44">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AE44">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF44">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.09</v>
+        <v>3.38</v>
       </c>
       <c r="O45">
-        <v>14</v>
+        <v>3.46</v>
       </c>
       <c r="P45">
-        <v>25</v>
+        <v>2.13</v>
       </c>
       <c r="Q45">
+        <v>3.8</v>
+      </c>
+      <c r="R45">
+        <v>2.2</v>
+      </c>
+      <c r="S45">
+        <v>1.36</v>
+      </c>
+      <c r="T45">
+        <v>3.14</v>
+      </c>
+      <c r="U45">
+        <v>2.7</v>
+      </c>
+      <c r="V45">
+        <v>1.41</v>
+      </c>
+      <c r="W45">
+        <v>1.08</v>
+      </c>
+      <c r="X45">
+        <v>1.03</v>
+      </c>
+      <c r="Y45">
+        <v>1.29</v>
+      </c>
+      <c r="Z45">
+        <v>3.6</v>
+      </c>
+      <c r="AA45">
+        <v>1.85</v>
+      </c>
+      <c r="AB45">
+        <v>2</v>
+      </c>
+      <c r="AC45">
+        <v>3.3</v>
+      </c>
+      <c r="AD45">
         <v>1.33</v>
       </c>
-      <c r="R45">
-        <v>3.8</v>
-      </c>
-      <c r="S45">
-        <v>1.09</v>
-      </c>
-      <c r="T45">
-        <v>6</v>
-      </c>
-      <c r="U45">
-        <v>1.49</v>
-      </c>
-      <c r="V45">
-        <v>2.33</v>
-      </c>
-      <c r="W45">
-        <v>1.47</v>
-      </c>
-      <c r="X45">
-        <v>1</v>
-      </c>
-      <c r="Y45">
-        <v>1.03</v>
-      </c>
-      <c r="Z45">
-        <v>11</v>
-      </c>
-      <c r="AA45">
-        <v>1.15</v>
-      </c>
-      <c r="AB45">
-        <v>5.2</v>
-      </c>
-      <c r="AC45">
-        <v>1.4</v>
-      </c>
-      <c r="AD45">
-        <v>2.8</v>
-      </c>
       <c r="AE45">
-        <v>1.85</v>
+        <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.05</v>
+        <v>1.62</v>
       </c>
       <c r="AK45">
-        <v>7</v>
+        <v>1.33</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.38</v>
+        <v>1.09</v>
       </c>
       <c r="O46">
-        <v>3.46</v>
+        <v>14</v>
       </c>
       <c r="P46">
-        <v>2.13</v>
+        <v>25</v>
       </c>
       <c r="Q46">
+        <v>1.33</v>
+      </c>
+      <c r="R46">
         <v>3.8</v>
       </c>
-      <c r="R46">
-        <v>2.2</v>
-      </c>
       <c r="S46">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="T46">
-        <v>3.14</v>
+        <v>6</v>
       </c>
       <c r="U46">
-        <v>2.7</v>
+        <v>1.49</v>
       </c>
       <c r="V46">
-        <v>1.41</v>
+        <v>2.33</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="X46">
+        <v>1</v>
+      </c>
+      <c r="Y46">
         <v>1.03</v>
       </c>
-      <c r="Y46">
-        <v>1.29</v>
-      </c>
       <c r="Z46">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="AA46">
+        <v>1.15</v>
+      </c>
+      <c r="AB46">
+        <v>5.2</v>
+      </c>
+      <c r="AC46">
+        <v>1.4</v>
+      </c>
+      <c r="AD46">
+        <v>2.8</v>
+      </c>
+      <c r="AE46">
         <v>1.85</v>
       </c>
-      <c r="AB46">
-        <v>2</v>
-      </c>
-      <c r="AC46">
-        <v>3.3</v>
-      </c>
-      <c r="AD46">
-        <v>1.33</v>
-      </c>
-      <c r="AE46">
-        <v>1.13</v>
-      </c>
       <c r="AF46">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG46">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.62</v>
+        <v>1.05</v>
       </c>
       <c r="AK46">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8136,16 +8136,16 @@
         <v>1.45</v>
       </c>
       <c r="O48">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="P48">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q48">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R48">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S48">
         <v>1.21</v>
@@ -8172,19 +8172,19 @@
         <v>5.1</v>
       </c>
       <c r="AA48">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AB48">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="AC48">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AD48">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
         <v>1.57</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK48">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,10 +8305,10 @@
         <v>2.08</v>
       </c>
       <c r="Q49">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R49">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
         <v>1.25</v>
@@ -8320,7 +8320,7 @@
         <v>2.25</v>
       </c>
       <c r="V49">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
         <v>1.14</v>
@@ -8329,31 +8329,31 @@
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z49">
         <v>4.65</v>
       </c>
       <c r="AA49">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB49">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC49">
         <v>2.33</v>
       </c>
       <c r="AD49">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE49">
         <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG49">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AK49">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.33</v>
@@ -8507,13 +8507,13 @@
         <v>3.05</v>
       </c>
       <c r="AD50">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE50">
         <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG50">
         <v>2.01</v>
@@ -9938,7 +9938,7 @@
         <v>3.08</v>
       </c>
       <c r="R59">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S59">
         <v>1.34</v>
@@ -9953,7 +9953,7 @@
         <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X59">
         <v>1.02</v>
@@ -9965,7 +9965,7 @@
         <v>3.95</v>
       </c>
       <c r="AA59">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB59">
         <v>2.05</v>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="O60">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P60">
         <v>5.25</v>
@@ -10110,7 +10110,7 @@
         <v>3.9</v>
       </c>
       <c r="U60">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="V60">
         <v>1.65</v>
@@ -10119,13 +10119,13 @@
         <v>1.17</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
         <v>1.11</v>
       </c>
       <c r="Z60">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="AA60">
         <v>1.47</v>
@@ -10140,7 +10140,7 @@
         <v>1.62</v>
       </c>
       <c r="AE60">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF60">
         <v>1.56</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -635,58 +635,58 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P2">
-        <v>2.91</v>
+        <v>2.55</v>
       </c>
       <c r="Q2">
-        <v>2.69</v>
+        <v>2.22</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S2">
         <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="U2">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="AA2">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC2">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AD2">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
         <v>1.55</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
@@ -2434,31 +2434,31 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="Q13">
         <v>1.62</v>
       </c>
       <c r="R13">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S13">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="U13">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V13">
         <v>1.62</v>
       </c>
       <c r="W13">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.11</v>
@@ -2479,7 +2479,7 @@
         <v>1.61</v>
       </c>
       <c r="AE13">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AF13">
         <v>1.72</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="O20">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q20">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="R20">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="S20">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U20">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="V20">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.33</v>
+      </c>
+      <c r="Z20">
+        <v>2.83</v>
+      </c>
+      <c r="AA20">
+        <v>2.08</v>
+      </c>
+      <c r="AB20">
+        <v>1.64</v>
+      </c>
+      <c r="AC20">
+        <v>3.58</v>
+      </c>
+      <c r="AD20">
+        <v>1.21</v>
+      </c>
+      <c r="AE20">
         <v>1.04</v>
       </c>
-      <c r="Y20">
-        <v>1.36</v>
-      </c>
-      <c r="Z20">
-        <v>2.69</v>
-      </c>
-      <c r="AA20">
-        <v>2.2</v>
-      </c>
-      <c r="AB20">
-        <v>1.61</v>
-      </c>
-      <c r="AC20">
-        <v>4.4</v>
-      </c>
-      <c r="AD20">
-        <v>1.17</v>
-      </c>
-      <c r="AE20">
-        <v>1.02</v>
-      </c>
       <c r="AF20">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG20">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK20">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="O22">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q22">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="R22">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="S22">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T22">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U22">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="V22">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AA22">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB22">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC22">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="AD22">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG22">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.53</v>
+        <v>2.87</v>
       </c>
       <c r="O29">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q29">
-        <v>1.97</v>
+        <v>3.47</v>
       </c>
       <c r="R29">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="S29">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T29">
-        <v>4.35</v>
+        <v>3.34</v>
       </c>
       <c r="U29">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="V29">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="W29">
+        <v>1.11</v>
+      </c>
+      <c r="X29">
+        <v>1.02</v>
+      </c>
+      <c r="Y29">
+        <v>1.11</v>
+      </c>
+      <c r="Z29">
+        <v>4.85</v>
+      </c>
+      <c r="AA29">
+        <v>1.47</v>
+      </c>
+      <c r="AB29">
+        <v>2.35</v>
+      </c>
+      <c r="AC29">
+        <v>2.22</v>
+      </c>
+      <c r="AD29">
+        <v>1.56</v>
+      </c>
+      <c r="AE29">
         <v>1.19</v>
       </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>1.05</v>
-      </c>
-      <c r="Z29">
-        <v>4</v>
-      </c>
-      <c r="AA29">
-        <v>1.25</v>
-      </c>
-      <c r="AB29">
-        <v>2.92</v>
-      </c>
-      <c r="AC29">
-        <v>1.85</v>
-      </c>
-      <c r="AD29">
-        <v>1.82</v>
-      </c>
-      <c r="AE29">
+      <c r="AF29">
+        <v>1.33</v>
+      </c>
+      <c r="AG29">
+        <v>2.2</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.2</v>
+      </c>
+      <c r="AK29">
         <v>1.32</v>
-      </c>
-      <c r="AF29">
-        <v>1.41</v>
-      </c>
-      <c r="AG29">
-        <v>2.66</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.1</v>
-      </c>
-      <c r="AK29">
-        <v>2.28</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P30">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q30">
-        <v>3.28</v>
+        <v>1.97</v>
       </c>
       <c r="R30">
-        <v>2.09</v>
+        <v>2.52</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="T30">
-        <v>2.76</v>
+        <v>4.35</v>
       </c>
       <c r="U30">
-        <v>2.74</v>
+        <v>1.89</v>
       </c>
       <c r="V30">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="Z30">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="AA30">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AB30">
-        <v>1.88</v>
+        <v>2.92</v>
       </c>
       <c r="AC30">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="AD30">
+        <v>1.82</v>
+      </c>
+      <c r="AE30">
         <v>1.32</v>
       </c>
-      <c r="AE30">
-        <v>1.09</v>
-      </c>
       <c r="AF30">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AG30">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK30">
-        <v>1.38</v>
+        <v>2.28</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P31">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>3.47</v>
+        <v>3.28</v>
       </c>
       <c r="R31">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="S31">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
-        <v>3.34</v>
+        <v>2.76</v>
       </c>
       <c r="U31">
-        <v>2.2</v>
+        <v>2.74</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>4.85</v>
+        <v>3.42</v>
       </c>
       <c r="AA31">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AB31">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AC31">
-        <v>2.22</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AG31">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AL31">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="O3">
+        <v>3.15</v>
+      </c>
+      <c r="P3">
         <v>3</v>
       </c>
-      <c r="P3">
-        <v>3.01</v>
-      </c>
       <c r="Q3">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="R3">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="S3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T3">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="U3">
         <v>3.18</v>
@@ -825,28 +825,28 @@
         <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA3">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AB3">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="AD3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE3">
         <v>1.02</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="O4">
         <v>3</v>
       </c>
       <c r="P4">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="Q4">
-        <v>3.6</v>
+        <v>4.08</v>
       </c>
       <c r="R4">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="S4">
         <v>1.54</v>
@@ -982,7 +982,7 @@
         <v>2.45</v>
       </c>
       <c r="U4">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="V4">
         <v>1.25</v>
@@ -991,28 +991,28 @@
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z4">
         <v>2.43</v>
       </c>
       <c r="AA4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AB4">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC4">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AD4">
         <v>1.13</v>
       </c>
       <c r="AE4">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
         <v>2.01</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA5">
         <v>1.72</v>
@@ -1172,7 +1172,7 @@
         <v>2.75</v>
       </c>
       <c r="AD5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
         <v>1.11</v>
@@ -1197,7 +1197,7 @@
         <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="R6">
         <v>1.73</v>
@@ -1332,7 +1332,7 @@
         <v>1.33</v>
       </c>
       <c r="AC6">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="AD6">
         <v>1.08</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK6">
         <v>1.43</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O7">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P7">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q7">
-        <v>5.12</v>
+        <v>4.85</v>
       </c>
       <c r="R7">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="S7">
         <v>1.64</v>
@@ -1486,28 +1486,28 @@
         <v>1.57</v>
       </c>
       <c r="Z7">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AA7">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AB7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AC7">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AD7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE7">
         <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AG7">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
         <v>1.18</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="O8">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="Q8">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S8">
         <v>1.46</v>
       </c>
       <c r="T8">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="U8">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="V8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W8">
         <v>1.03</v>
@@ -1646,22 +1646,22 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z8">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="AA8">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AB8">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC8">
         <v>3.68</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
         <v>1.03</v>
@@ -1686,7 +1686,7 @@
         <v>1.38</v>
       </c>
       <c r="AK8">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P9">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Q9">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R9">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="S9">
         <v>1.33</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U9">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="V9">
         <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.26</v>
+        <v>3.88</v>
       </c>
       <c r="AA9">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB9">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AC9">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AD9">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AG9">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK9">
         <v>3.28</v>
@@ -1939,22 +1939,22 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="O10">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="R10">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
         <v>3</v>
@@ -1969,13 +1969,13 @@
         <v>1.09</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA10">
         <v>1.75</v>
@@ -1984,16 +1984,16 @@
         <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD10">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
         <v>2.08</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK10">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="N11">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="O11">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P11">
         <v>1.36</v>
@@ -2150,7 +2150,7 @@
         <v>3.86</v>
       </c>
       <c r="AD11">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE11">
         <v>1.03</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>4.45</v>
+        <v>5.1</v>
       </c>
       <c r="O14">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Q14">
-        <v>5.21</v>
+        <v>4.7</v>
       </c>
       <c r="R14">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="S14">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="V14">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W14">
         <v>1.14</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z14">
-        <v>4.45</v>
+        <v>3.7</v>
       </c>
       <c r="AA14">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB14">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="AC14">
-        <v>2.28</v>
+        <v>2.95</v>
       </c>
       <c r="AD14">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE14">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF14">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AG14">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="O15">
         <v>3.1</v>
       </c>
       <c r="P15">
-        <v>3.95</v>
+        <v>3.63</v>
       </c>
       <c r="Q15">
         <v>2.62</v>
@@ -2775,7 +2775,7 @@
         <v>2.55</v>
       </c>
       <c r="U15">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V15">
         <v>1.29</v>
@@ -2793,7 +2793,7 @@
         <v>2.65</v>
       </c>
       <c r="AA15">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB15">
         <v>1.55</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O16">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q16">
         <v>2.32</v>
@@ -2932,16 +2932,16 @@
         <v>2.23</v>
       </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
         <v>1.06</v>
@@ -2974,7 +2974,7 @@
         <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
         <v>3.5</v>
       </c>
       <c r="P17">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q17">
         <v>2.72</v>
@@ -3098,16 +3098,16 @@
         <v>1.29</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3131,13 +3131,13 @@
         <v>1.38</v>
       </c>
       <c r="AE17">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
         <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q18">
         <v>3.98</v>
@@ -3297,10 +3297,10 @@
         <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O19">
         <v>2.9</v>
@@ -3421,10 +3421,10 @@
         <v>1.84</v>
       </c>
       <c r="S19">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="U19">
         <v>2.95</v>
@@ -3433,31 +3433,31 @@
         <v>1.31</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
         <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
         <v>2.78</v>
       </c>
       <c r="AA19">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB19">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC19">
-        <v>3.86</v>
+        <v>4.33</v>
       </c>
       <c r="AD19">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE19">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
         <v>1.82</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK19">
         <v>1.4</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
+        <v>2.7</v>
+      </c>
+      <c r="O20">
+        <v>2.9</v>
+      </c>
+      <c r="P20">
+        <v>2.6</v>
+      </c>
+      <c r="Q20">
+        <v>3.5</v>
+      </c>
+      <c r="R20">
         <v>2</v>
       </c>
-      <c r="O20">
-        <v>3.1</v>
-      </c>
-      <c r="P20">
-        <v>3.4</v>
-      </c>
-      <c r="Q20">
-        <v>2.65</v>
-      </c>
-      <c r="R20">
-        <v>1.95</v>
-      </c>
       <c r="S20">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T20">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U20">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="V20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z20">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="AA20">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB20">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC20">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AD20">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE20">
         <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG20">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.51</v>
+        <v>2.37</v>
       </c>
       <c r="O21">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="Q21">
-        <v>4.39</v>
+        <v>3.4</v>
       </c>
       <c r="R21">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="S21">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="T21">
-        <v>2.54</v>
+        <v>2.18</v>
       </c>
       <c r="U21">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="V21">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y21">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="Z21">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AA21">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="AB21">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AC21">
-        <v>3.28</v>
+        <v>4.65</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="O22">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P22">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="Q22">
-        <v>3.5</v>
+        <v>4.93</v>
       </c>
       <c r="R22">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
-        <v>3.18</v>
+        <v>2.73</v>
       </c>
       <c r="V22">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>2.69</v>
+        <v>3.08</v>
       </c>
       <c r="AA22">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB22">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AC22">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD22">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AE22">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF22">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AK22">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="O23">
         <v>3.1</v>
       </c>
       <c r="P23">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q23">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="R23">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T23">
-        <v>2.73</v>
+        <v>2.51</v>
       </c>
       <c r="U23">
-        <v>2.73</v>
+        <v>3.03</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z23">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AA23">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB23">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC23">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE23">
         <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG23">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.37</v>
+        <v>1.73</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="O24">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="P24">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
         <v>3.4</v>
       </c>
       <c r="R24">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="S24">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>2.18</v>
+        <v>2.73</v>
       </c>
       <c r="U24">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V24">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>2.46</v>
+        <v>2.97</v>
       </c>
       <c r="AA24">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="AB24">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AC24">
-        <v>4.65</v>
+        <v>3.42</v>
       </c>
       <c r="AD24">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AE24">
         <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O25">
         <v>3.3</v>
@@ -4393,43 +4393,43 @@
         <v>1.67</v>
       </c>
       <c r="Q25">
-        <v>6.04</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
         <v>1.47</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="U25">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="V25">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W25">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA25">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB25">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC25">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="AD25">
         <v>1.19</v>
@@ -4441,7 +4441,7 @@
         <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.24</v>
       </c>
       <c r="AK25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,28 +4547,28 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="Q26">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="R26">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="S26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T26">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U26">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V26">
         <v>1.72</v>
@@ -4580,31 +4580,31 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z26">
-        <v>5.7</v>
+        <v>6.33</v>
       </c>
       <c r="AA26">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB26">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="AC26">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AD26">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE26">
         <v>1.27</v>
       </c>
       <c r="AF26">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG26">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q27">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="R27">
         <v>2.32</v>
@@ -4731,10 +4731,10 @@
         <v>3.55</v>
       </c>
       <c r="U27">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="V27">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="W27">
         <v>1.14</v>
@@ -4743,47 +4743,47 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AA27">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AC27">
         <v>2.13</v>
       </c>
       <c r="AD27">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE27">
+        <v>1.22</v>
+      </c>
+      <c r="AF27">
+        <v>1.4</v>
+      </c>
+      <c r="AG27">
+        <v>2.6</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.23</v>
       </c>
-      <c r="AF27">
-        <v>1.39</v>
-      </c>
-      <c r="AG27">
-        <v>2.77</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.26</v>
-      </c>
       <c r="AK27">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P28">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="Q28">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R28">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.24</v>
+        <v>2.32</v>
       </c>
       <c r="U28">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="AA28">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AB28">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AC28">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AE28">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AG28">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AK28">
         <v>1.4</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.87</v>
+        <v>1.5</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="P29">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q29">
-        <v>3.47</v>
+        <v>1.95</v>
       </c>
       <c r="R29">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="S29">
         <v>1.18</v>
       </c>
       <c r="T29">
-        <v>3.34</v>
+        <v>4.4</v>
       </c>
       <c r="U29">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="V29">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z29">
-        <v>4.85</v>
+        <v>6.65</v>
       </c>
       <c r="AA29">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AB29">
-        <v>2.35</v>
+        <v>3.13</v>
       </c>
       <c r="AC29">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="AD29">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AE29">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AF29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG29">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK29">
-        <v>1.32</v>
+        <v>2.34</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.53</v>
+        <v>2.85</v>
       </c>
       <c r="O30">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q30">
-        <v>1.97</v>
+        <v>3.24</v>
       </c>
       <c r="R30">
-        <v>2.52</v>
+        <v>2.17</v>
       </c>
       <c r="S30">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="U30">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="V30">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA30">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AB30">
-        <v>2.92</v>
+        <v>1.89</v>
       </c>
       <c r="AC30">
-        <v>1.85</v>
+        <v>2.63</v>
       </c>
       <c r="AD30">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AE30">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AG30">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
+        <v>2.8</v>
+      </c>
+      <c r="O31">
+        <v>3.4</v>
+      </c>
+      <c r="P31">
+        <v>2.1</v>
+      </c>
+      <c r="Q31">
+        <v>3.47</v>
+      </c>
+      <c r="R31">
+        <v>2.28</v>
+      </c>
+      <c r="S31">
+        <v>1.24</v>
+      </c>
+      <c r="T31">
+        <v>2.8</v>
+      </c>
+      <c r="U31">
+        <v>1.89</v>
+      </c>
+      <c r="V31">
+        <v>1.57</v>
+      </c>
+      <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
+        <v>1.11</v>
+      </c>
+      <c r="Z31">
+        <v>4.85</v>
+      </c>
+      <c r="AA31">
+        <v>1.53</v>
+      </c>
+      <c r="AB31">
+        <v>2.35</v>
+      </c>
+      <c r="AC31">
+        <v>2.22</v>
+      </c>
+      <c r="AD31">
+        <v>1.56</v>
+      </c>
+      <c r="AE31">
+        <v>1.19</v>
+      </c>
+      <c r="AF31">
+        <v>1.43</v>
+      </c>
+      <c r="AG31">
         <v>2.5</v>
       </c>
-      <c r="O31">
-        <v>3.2</v>
-      </c>
-      <c r="P31">
-        <v>2.45</v>
-      </c>
-      <c r="Q31">
-        <v>3.28</v>
-      </c>
-      <c r="R31">
-        <v>2.09</v>
-      </c>
-      <c r="S31">
-        <v>1.35</v>
-      </c>
-      <c r="T31">
-        <v>2.76</v>
-      </c>
-      <c r="U31">
-        <v>2.74</v>
-      </c>
-      <c r="V31">
-        <v>1.39</v>
-      </c>
-      <c r="W31">
-        <v>1.06</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
-        <v>1.23</v>
-      </c>
-      <c r="Z31">
-        <v>3.42</v>
-      </c>
-      <c r="AA31">
-        <v>1.79</v>
-      </c>
-      <c r="AB31">
-        <v>1.88</v>
-      </c>
-      <c r="AC31">
-        <v>2.88</v>
-      </c>
-      <c r="AD31">
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.57</v>
+      </c>
+      <c r="AK31">
         <v>1.32</v>
-      </c>
-      <c r="AE31">
-        <v>1.09</v>
-      </c>
-      <c r="AF31">
-        <v>1.63</v>
-      </c>
-      <c r="AG31">
-        <v>2.12</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.25</v>
-      </c>
-      <c r="AK31">
-        <v>1.38</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O32">
         <v>3.6</v>
       </c>
       <c r="P32">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q32">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R32">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S32">
         <v>1.19</v>
@@ -5546,7 +5546,7 @@
         <v>3.74</v>
       </c>
       <c r="U32">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="V32">
         <v>1.69</v>
@@ -5555,7 +5555,7 @@
         <v>1.17</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
         <v>1.1</v>
@@ -5570,19 +5570,19 @@
         <v>2.56</v>
       </c>
       <c r="AC32">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AD32">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE32">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG32">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O33">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>7.5</v>
       </c>
       <c r="Q33">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R33">
         <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T33">
         <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5761,7 +5761,7 @@
         <v>1.15</v>
       </c>
       <c r="AK33">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>1.6</v>
       </c>
       <c r="AC34">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AD34">
         <v>1.22</v>
@@ -5908,7 +5908,7 @@
         <v>1.9</v>
       </c>
       <c r="AG34">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="O36">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>1.61</v>
+        <v>2.03</v>
       </c>
       <c r="Q36">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="R36">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T36">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="U36">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="V36">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W36">
         <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z36">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AA36">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AB36">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC36">
-        <v>4.48</v>
+        <v>4.25</v>
       </c>
       <c r="AD36">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE36">
         <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AG36">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK36">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="O37">
         <v>3.53</v>
@@ -6349,10 +6349,10 @@
         <v>3.33</v>
       </c>
       <c r="Q37">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="S37">
         <v>1.33</v>
@@ -6361,22 +6361,22 @@
         <v>3.18</v>
       </c>
       <c r="U37">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W37">
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z37">
-        <v>3.88</v>
+        <v>4.09</v>
       </c>
       <c r="AA37">
         <v>1.84</v>
@@ -6394,10 +6394,10 @@
         <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="O39">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q39">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
         <v>2.2</v>
@@ -6684,7 +6684,7 @@
         <v>1.38</v>
       </c>
       <c r="T39">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U39">
         <v>2.8</v>
@@ -6699,10 +6699,10 @@
         <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA39">
         <v>2</v>
@@ -6717,7 +6717,7 @@
         <v>1.24</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
         <v>2.12</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O40">
         <v>3</v>
@@ -6841,7 +6841,7 @@
         <v>3.88</v>
       </c>
       <c r="R40">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S40">
         <v>1.45</v>
@@ -6850,7 +6850,7 @@
         <v>2.42</v>
       </c>
       <c r="U40">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="V40">
         <v>1.31</v>
@@ -6865,16 +6865,16 @@
         <v>1.31</v>
       </c>
       <c r="Z40">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA40">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AB40">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC40">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="AD40">
         <v>1.23</v>
@@ -6883,10 +6883,10 @@
         <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG40">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="O41">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q41">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="R41">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="U41">
-        <v>2.95</v>
+        <v>2.51</v>
       </c>
       <c r="V41">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>2.83</v>
+        <v>3.48</v>
       </c>
       <c r="AA41">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="AB41">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC41">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="AD41">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AG41">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,58 +7155,58 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O42">
         <v>3.4</v>
       </c>
       <c r="P42">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Q42">
-        <v>4.43</v>
+        <v>4.28</v>
       </c>
       <c r="R42">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T42">
         <v>3.08</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V42">
         <v>1.46</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AA42">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB42">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD42">
         <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
         <v>1.61</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>1.83</v>
       </c>
       <c r="AK42">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="O43">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P43">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q43">
+        <v>2.41</v>
+      </c>
+      <c r="R43">
+        <v>2.12</v>
+      </c>
+      <c r="S43">
+        <v>1.43</v>
+      </c>
+      <c r="T43">
+        <v>2.48</v>
+      </c>
+      <c r="U43">
+        <v>2.95</v>
+      </c>
+      <c r="V43">
+        <v>1.31</v>
+      </c>
+      <c r="W43">
+        <v>1.03</v>
+      </c>
+      <c r="X43">
+        <v>1.03</v>
+      </c>
+      <c r="Y43">
+        <v>1.36</v>
+      </c>
+      <c r="Z43">
+        <v>2.9</v>
+      </c>
+      <c r="AA43">
         <v>2.11</v>
       </c>
-      <c r="R43">
-        <v>2.22</v>
-      </c>
-      <c r="S43">
-        <v>1.38</v>
-      </c>
-      <c r="T43">
-        <v>3</v>
-      </c>
-      <c r="U43">
-        <v>2.48</v>
-      </c>
-      <c r="V43">
-        <v>1.43</v>
-      </c>
-      <c r="W43">
-        <v>1.08</v>
-      </c>
-      <c r="X43">
-        <v>1</v>
-      </c>
-      <c r="Y43">
-        <v>1.22</v>
-      </c>
-      <c r="Z43">
-        <v>3.5</v>
-      </c>
-      <c r="AA43">
-        <v>1.79</v>
-      </c>
       <c r="AB43">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AC43">
-        <v>2.97</v>
+        <v>3.78</v>
       </c>
       <c r="AD43">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AE43">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF43">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AG43">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK43">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O44">
         <v>3.6</v>
@@ -7490,55 +7490,55 @@
         <v>4.5</v>
       </c>
       <c r="Q44">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R44">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="S44">
         <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U44">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="V44">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W44">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA44">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AB44">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC44">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="AD44">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE44">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG44">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="O45">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="Q45">
         <v>3.8</v>
@@ -7662,13 +7662,13 @@
         <v>1.36</v>
       </c>
       <c r="T45">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="U45">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="V45">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W45">
         <v>1.08</v>
@@ -7677,31 +7677,31 @@
         <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z45">
         <v>3.6</v>
       </c>
       <c r="AA45">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB45">
         <v>2</v>
       </c>
       <c r="AC45">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="AD45">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE45">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG45">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.62</v>
       </c>
       <c r="AK45">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7831,10 +7831,10 @@
         <v>1.49</v>
       </c>
       <c r="V46">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="W46">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X46">
         <v>1</v>
@@ -7846,25 +7846,25 @@
         <v>11</v>
       </c>
       <c r="AA46">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AB46">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AC46">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AD46">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="AE46">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AF46">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG46">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -8305,25 +8305,25 @@
         <v>2.08</v>
       </c>
       <c r="Q49">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
         <v>1.25</v>
       </c>
       <c r="T49">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U49">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8332,7 +8332,7 @@
         <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA49">
         <v>1.53</v>
@@ -8353,7 +8353,7 @@
         <v>1.45</v>
       </c>
       <c r="AG49">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AK49">
         <v>1.4</v>
@@ -10089,34 +10089,34 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O60">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P60">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q60">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R60">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="S60">
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U60">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="V60">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W60">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10125,28 +10125,28 @@
         <v>1.11</v>
       </c>
       <c r="Z60">
-        <v>6</v>
+        <v>4.85</v>
       </c>
       <c r="AA60">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB60">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AC60">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AD60">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE60">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF60">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG60">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.14</v>
       </c>
       <c r="AK60">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AL60">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -612,42 +612,42 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="O2">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="P2">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
         <v>1.3</v>
@@ -656,28 +656,28 @@
         <v>3.25</v>
       </c>
       <c r="U2">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W2">
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
         <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB2">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC2">
         <v>2.62</v>
@@ -689,53 +689,53 @@
         <v>1.17</v>
       </c>
       <c r="AF2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG2">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "90+1", "90+6"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK2">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -2268,28 +2268,28 @@
         <v>1.44</v>
       </c>
       <c r="O12">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P12">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>1.9</v>
       </c>
       <c r="R12">
-        <v>2.51</v>
+        <v>2.73</v>
       </c>
       <c r="S12">
         <v>1.2</v>
       </c>
       <c r="T12">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U12">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V12">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="W12">
         <v>1.14</v>
@@ -2301,13 +2301,13 @@
         <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>5.45</v>
+        <v>3.75</v>
       </c>
       <c r="AA12">
         <v>1.39</v>
       </c>
       <c r="AB12">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AC12">
         <v>2.02</v>
@@ -2316,13 +2316,13 @@
         <v>1.73</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
         <v>1.53</v>
       </c>
       <c r="AG12">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.12</v>
       </c>
       <c r="AK12">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2443,13 +2443,13 @@
         <v>2.59</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U13">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V13">
         <v>1.62</v>
@@ -2479,13 +2479,13 @@
         <v>1.61</v>
       </c>
       <c r="AE13">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
         <v>1.72</v>
       </c>
       <c r="AG13">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.09</v>
       </c>
       <c r="AK13">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.35</v>
+        <v>3.65</v>
       </c>
       <c r="O19">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P19">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="Q19">
-        <v>3.26</v>
+        <v>4.93</v>
       </c>
       <c r="R19">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="V19">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z19">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="AA19">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AB19">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE19">
         <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AK19">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="O20">
+        <v>2.8</v>
+      </c>
+      <c r="P20">
         <v>2.9</v>
       </c>
-      <c r="P20">
-        <v>2.6</v>
-      </c>
       <c r="Q20">
+        <v>3.4</v>
+      </c>
+      <c r="R20">
+        <v>1.91</v>
+      </c>
+      <c r="S20">
+        <v>1.58</v>
+      </c>
+      <c r="T20">
+        <v>2.18</v>
+      </c>
+      <c r="U20">
         <v>3.5</v>
       </c>
-      <c r="R20">
-        <v>2</v>
-      </c>
-      <c r="S20">
-        <v>1.47</v>
-      </c>
-      <c r="T20">
-        <v>2.38</v>
-      </c>
-      <c r="U20">
-        <v>3.2</v>
-      </c>
       <c r="V20">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W20">
         <v>1.01</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y20">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z20">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="AA20">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AB20">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AC20">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="AD20">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE20">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG20">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O21">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P21">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q21">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="R21">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="S21">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="U21">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="V21">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Z21">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="AA21">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="AB21">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="AC21">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="AD21">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AG21">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK21">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="O22">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P22">
-        <v>1.97</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>4.93</v>
+        <v>3.5</v>
       </c>
       <c r="R22">
+        <v>2</v>
+      </c>
+      <c r="S22">
+        <v>1.47</v>
+      </c>
+      <c r="T22">
+        <v>2.38</v>
+      </c>
+      <c r="U22">
+        <v>3.2</v>
+      </c>
+      <c r="V22">
+        <v>1.3</v>
+      </c>
+      <c r="W22">
+        <v>1.01</v>
+      </c>
+      <c r="X22">
+        <v>1.04</v>
+      </c>
+      <c r="Y22">
+        <v>1.4</v>
+      </c>
+      <c r="Z22">
+        <v>2.76</v>
+      </c>
+      <c r="AA22">
         <v>2.2</v>
       </c>
-      <c r="S22">
-        <v>1.36</v>
-      </c>
-      <c r="T22">
-        <v>2.88</v>
-      </c>
-      <c r="U22">
-        <v>2.73</v>
-      </c>
-      <c r="V22">
-        <v>1.38</v>
-      </c>
-      <c r="W22">
-        <v>1.05</v>
-      </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>1.28</v>
-      </c>
-      <c r="Z22">
-        <v>3.08</v>
-      </c>
-      <c r="AA22">
-        <v>1.93</v>
-      </c>
       <c r="AB22">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC22">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="AD22">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AE22">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O30">
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q30">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="R30">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S30">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T30">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="U30">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z30">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="AA30">
+        <v>1.53</v>
+      </c>
+      <c r="AB30">
+        <v>2.35</v>
+      </c>
+      <c r="AC30">
+        <v>2.22</v>
+      </c>
+      <c r="AD30">
+        <v>1.56</v>
+      </c>
+      <c r="AE30">
+        <v>1.19</v>
+      </c>
+      <c r="AF30">
+        <v>1.43</v>
+      </c>
+      <c r="AG30">
+        <v>2.5</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.57</v>
       </c>
-      <c r="AB30">
-        <v>1.89</v>
-      </c>
-      <c r="AC30">
-        <v>2.63</v>
-      </c>
-      <c r="AD30">
-        <v>1.44</v>
-      </c>
-      <c r="AE30">
-        <v>1.14</v>
-      </c>
-      <c r="AF30">
-        <v>1.5</v>
-      </c>
-      <c r="AG30">
-        <v>2.38</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.22</v>
-      </c>
       <c r="AK30">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O31">
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q31">
-        <v>3.47</v>
+        <v>3.24</v>
       </c>
       <c r="R31">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S31">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
+        <v>2.38</v>
+      </c>
+      <c r="V31">
+        <v>1.52</v>
+      </c>
+      <c r="W31">
+        <v>1.08</v>
+      </c>
+      <c r="X31">
+        <v>1.01</v>
+      </c>
+      <c r="Y31">
+        <v>1.15</v>
+      </c>
+      <c r="Z31">
+        <v>4.2</v>
+      </c>
+      <c r="AA31">
+        <v>1.57</v>
+      </c>
+      <c r="AB31">
         <v>1.89</v>
       </c>
-      <c r="V31">
-        <v>1.57</v>
-      </c>
-      <c r="W31">
-        <v>1.1</v>
-      </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>1.11</v>
-      </c>
-      <c r="Z31">
-        <v>4.85</v>
-      </c>
-      <c r="AA31">
-        <v>1.53</v>
-      </c>
-      <c r="AB31">
-        <v>2.35</v>
-      </c>
       <c r="AC31">
-        <v>2.22</v>
+        <v>2.63</v>
       </c>
       <c r="AD31">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE31">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AG31">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6029,10 +6029,10 @@
         <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
         <v>2.48</v>
@@ -6041,7 +6041,7 @@
         <v>1.46</v>
       </c>
       <c r="W35">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
         <v>1.02</v>
@@ -6056,10 +6056,10 @@
         <v>1.71</v>
       </c>
       <c r="AB35">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AC35">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
       <c r="AD35">
         <v>1.36</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="O40">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q40">
-        <v>3.88</v>
+        <v>2.1</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T40">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="U40">
-        <v>2.82</v>
+        <v>2.51</v>
       </c>
       <c r="V40">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="W40">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
+        <v>3.48</v>
+      </c>
+      <c r="AA40">
+        <v>1.8</v>
+      </c>
+      <c r="AB40">
+        <v>1.87</v>
+      </c>
+      <c r="AC40">
         <v>2.97</v>
       </c>
-      <c r="AA40">
-        <v>2.07</v>
-      </c>
-      <c r="AB40">
-        <v>1.68</v>
-      </c>
-      <c r="AC40">
-        <v>3.9</v>
-      </c>
       <c r="AD40">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE40">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AG40">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK40">
-        <v>1.3</v>
+        <v>2.16</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q41">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S41">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T41">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="U41">
-        <v>2.51</v>
+        <v>2.95</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
+        <v>1.03</v>
+      </c>
+      <c r="Y41">
+        <v>1.36</v>
+      </c>
+      <c r="Z41">
+        <v>2.9</v>
+      </c>
+      <c r="AA41">
+        <v>2.11</v>
+      </c>
+      <c r="AB41">
+        <v>1.62</v>
+      </c>
+      <c r="AC41">
+        <v>3.78</v>
+      </c>
+      <c r="AD41">
+        <v>1.19</v>
+      </c>
+      <c r="AE41">
         <v>1.02</v>
       </c>
-      <c r="Y41">
-        <v>1.22</v>
-      </c>
-      <c r="Z41">
-        <v>3.48</v>
-      </c>
-      <c r="AA41">
-        <v>1.8</v>
-      </c>
-      <c r="AB41">
-        <v>1.87</v>
-      </c>
-      <c r="AC41">
-        <v>2.97</v>
-      </c>
-      <c r="AD41">
-        <v>1.3</v>
-      </c>
-      <c r="AE41">
-        <v>1.08</v>
-      </c>
       <c r="AF41">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG41">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK41">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P42">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S42">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="T42">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="U42">
-        <v>2.44</v>
+        <v>2.82</v>
       </c>
       <c r="V42">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z42">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="AA42">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AB42">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AC42">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD42">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AG42">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>3.75</v>
+      </c>
+      <c r="O43">
+        <v>3.4</v>
+      </c>
+      <c r="P43">
+        <v>1.86</v>
+      </c>
+      <c r="Q43">
+        <v>4.28</v>
+      </c>
+      <c r="R43">
+        <v>2.25</v>
+      </c>
+      <c r="S43">
+        <v>1.35</v>
+      </c>
+      <c r="T43">
+        <v>3.08</v>
+      </c>
+      <c r="U43">
+        <v>2.44</v>
+      </c>
+      <c r="V43">
+        <v>1.46</v>
+      </c>
+      <c r="W43">
+        <v>1.11</v>
+      </c>
+      <c r="X43">
+        <v>1.01</v>
+      </c>
+      <c r="Y43">
+        <v>1.22</v>
+      </c>
+      <c r="Z43">
+        <v>4</v>
+      </c>
+      <c r="AA43">
         <v>1.75</v>
       </c>
-      <c r="O43">
-        <v>3.2</v>
-      </c>
-      <c r="P43">
-        <v>4.2</v>
-      </c>
-      <c r="Q43">
-        <v>2.41</v>
-      </c>
-      <c r="R43">
-        <v>2.12</v>
-      </c>
-      <c r="S43">
-        <v>1.43</v>
-      </c>
-      <c r="T43">
-        <v>2.48</v>
-      </c>
-      <c r="U43">
-        <v>2.95</v>
-      </c>
-      <c r="V43">
-        <v>1.31</v>
-      </c>
-      <c r="W43">
-        <v>1.03</v>
-      </c>
-      <c r="X43">
-        <v>1.03</v>
-      </c>
-      <c r="Y43">
+      <c r="AB43">
+        <v>2.05</v>
+      </c>
+      <c r="AC43">
+        <v>2.88</v>
+      </c>
+      <c r="AD43">
         <v>1.36</v>
       </c>
-      <c r="Z43">
-        <v>2.9</v>
-      </c>
-      <c r="AA43">
-        <v>2.11</v>
-      </c>
-      <c r="AB43">
-        <v>1.62</v>
-      </c>
-      <c r="AC43">
-        <v>3.78</v>
-      </c>
-      <c r="AD43">
-        <v>1.19</v>
-      </c>
       <c r="AE43">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AG43">
-        <v>1.74</v>
+        <v>2.13</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.12</v>
+        <v>1.83</v>
       </c>
       <c r="AK43">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="O48">
         <v>4.25</v>
       </c>
       <c r="P48">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q48">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R48">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S48">
         <v>1.21</v>
@@ -8166,16 +8166,16 @@
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z48">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA48">
         <v>1.52</v>
       </c>
       <c r="AB48">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AC48">
         <v>2.2</v>
@@ -8184,13 +8184,13 @@
         <v>1.57</v>
       </c>
       <c r="AE48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
         <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK48">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,43 +8459,43 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
       </c>
       <c r="R50">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="S50">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="U50">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V50">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.33</v>
       </c>
       <c r="Z50">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA50">
         <v>1.79</v>
@@ -8507,16 +8507,16 @@
         <v>3.05</v>
       </c>
       <c r="AD50">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF50">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG50">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -9935,10 +9935,10 @@
         <v>2.45</v>
       </c>
       <c r="Q59">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="R59">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="S59">
         <v>1.34</v>
@@ -9953,7 +9953,7 @@
         <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X59">
         <v>1.02</v>
@@ -9977,7 +9977,7 @@
         <v>1.4</v>
       </c>
       <c r="AE59">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF59">
         <v>1.57</v>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="O61">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q61">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R61">
         <v>2.4</v>
@@ -10273,43 +10273,43 @@
         <v>3.38</v>
       </c>
       <c r="U61">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="V61">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
         <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA61">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB61">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="AC61">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AD61">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE61">
         <v>1.15</v>
       </c>
       <c r="AF61">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG61">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,22 +10415,22 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="O62">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P62">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="Q62">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="R62">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="S62">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T62">
         <v>3.25</v>
@@ -10442,31 +10442,31 @@
         <v>1.5</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X62">
         <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z62">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AA62">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB62">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC62">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD62">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE62">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF62">
         <v>1.58</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK62">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="O19">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="P19">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="Q19">
-        <v>4.93</v>
+        <v>3.26</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="S19">
+        <v>1.4</v>
+      </c>
+      <c r="T19">
+        <v>2.62</v>
+      </c>
+      <c r="U19">
+        <v>2.95</v>
+      </c>
+      <c r="V19">
+        <v>1.31</v>
+      </c>
+      <c r="W19">
+        <v>1.06</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
         <v>1.36</v>
       </c>
-      <c r="T19">
-        <v>2.88</v>
-      </c>
-      <c r="U19">
-        <v>2.73</v>
-      </c>
-      <c r="V19">
-        <v>1.38</v>
-      </c>
-      <c r="W19">
-        <v>1.05</v>
-      </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
-        <v>1.28</v>
-      </c>
       <c r="Z19">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="AA19">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AB19">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC19">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD19">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE19">
         <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG19">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="AK19">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.37</v>
+        <v>3.65</v>
       </c>
       <c r="O20">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="P20">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="Q20">
-        <v>3.4</v>
+        <v>4.93</v>
       </c>
       <c r="R20">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="V20">
+        <v>1.38</v>
+      </c>
+      <c r="W20">
+        <v>1.05</v>
+      </c>
+      <c r="X20">
+        <v>1.02</v>
+      </c>
+      <c r="Y20">
+        <v>1.28</v>
+      </c>
+      <c r="Z20">
+        <v>3.08</v>
+      </c>
+      <c r="AA20">
+        <v>1.93</v>
+      </c>
+      <c r="AB20">
+        <v>1.75</v>
+      </c>
+      <c r="AC20">
+        <v>3.2</v>
+      </c>
+      <c r="AD20">
+        <v>1.26</v>
+      </c>
+      <c r="AE20">
+        <v>1.06</v>
+      </c>
+      <c r="AF20">
+        <v>1.8</v>
+      </c>
+      <c r="AG20">
+        <v>1.87</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.77</v>
+      </c>
+      <c r="AK20">
         <v>1.22</v>
-      </c>
-      <c r="W20">
-        <v>1.01</v>
-      </c>
-      <c r="X20">
-        <v>1.07</v>
-      </c>
-      <c r="Y20">
-        <v>1.47</v>
-      </c>
-      <c r="Z20">
-        <v>2.4</v>
-      </c>
-      <c r="AA20">
-        <v>2.44</v>
-      </c>
-      <c r="AB20">
-        <v>1.47</v>
-      </c>
-      <c r="AC20">
-        <v>4.65</v>
-      </c>
-      <c r="AD20">
-        <v>1.12</v>
-      </c>
-      <c r="AE20">
-        <v>1.05</v>
-      </c>
-      <c r="AF20">
-        <v>2.05</v>
-      </c>
-      <c r="AG20">
-        <v>1.67</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.36</v>
-      </c>
-      <c r="AK20">
-        <v>1.39</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="O21">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q21">
-        <v>3.26</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="U21">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="V21">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AA21">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB21">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC21">
-        <v>4.33</v>
+        <v>3.48</v>
       </c>
       <c r="AD21">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG21">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="O22">
+        <v>2.8</v>
+      </c>
+      <c r="P22">
         <v>2.9</v>
       </c>
-      <c r="P22">
-        <v>2.6</v>
-      </c>
       <c r="Q22">
+        <v>3.4</v>
+      </c>
+      <c r="R22">
+        <v>1.91</v>
+      </c>
+      <c r="S22">
+        <v>1.58</v>
+      </c>
+      <c r="T22">
+        <v>2.18</v>
+      </c>
+      <c r="U22">
         <v>3.5</v>
       </c>
-      <c r="R22">
-        <v>2</v>
-      </c>
-      <c r="S22">
-        <v>1.47</v>
-      </c>
-      <c r="T22">
-        <v>2.38</v>
-      </c>
-      <c r="U22">
-        <v>3.2</v>
-      </c>
       <c r="V22">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W22">
         <v>1.01</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z22">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="AA22">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AB22">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AC22">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="AD22">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG22">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK22">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
+        <v>2.7</v>
+      </c>
+      <c r="O23">
+        <v>2.9</v>
+      </c>
+      <c r="P23">
+        <v>2.6</v>
+      </c>
+      <c r="Q23">
+        <v>3.5</v>
+      </c>
+      <c r="R23">
+        <v>2</v>
+      </c>
+      <c r="S23">
+        <v>1.47</v>
+      </c>
+      <c r="T23">
+        <v>2.38</v>
+      </c>
+      <c r="U23">
+        <v>3.2</v>
+      </c>
+      <c r="V23">
+        <v>1.3</v>
+      </c>
+      <c r="W23">
+        <v>1.01</v>
+      </c>
+      <c r="X23">
+        <v>1.04</v>
+      </c>
+      <c r="Y23">
+        <v>1.4</v>
+      </c>
+      <c r="Z23">
+        <v>2.76</v>
+      </c>
+      <c r="AA23">
+        <v>2.2</v>
+      </c>
+      <c r="AB23">
+        <v>1.57</v>
+      </c>
+      <c r="AC23">
+        <v>3.98</v>
+      </c>
+      <c r="AD23">
+        <v>1.17</v>
+      </c>
+      <c r="AE23">
+        <v>1.04</v>
+      </c>
+      <c r="AF23">
         <v>1.91</v>
       </c>
-      <c r="O23">
-        <v>3.1</v>
-      </c>
-      <c r="P23">
-        <v>3.3</v>
-      </c>
-      <c r="Q23">
-        <v>2.6</v>
-      </c>
-      <c r="R23">
-        <v>1.98</v>
-      </c>
-      <c r="S23">
-        <v>1.43</v>
-      </c>
-      <c r="T23">
-        <v>2.51</v>
-      </c>
-      <c r="U23">
-        <v>3.03</v>
-      </c>
-      <c r="V23">
-        <v>1.34</v>
-      </c>
-      <c r="W23">
-        <v>1.03</v>
-      </c>
-      <c r="X23">
-        <v>1.03</v>
-      </c>
-      <c r="Y23">
+      <c r="AG23">
+        <v>1.81</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.33</v>
       </c>
-      <c r="Z23">
-        <v>3.1</v>
-      </c>
-      <c r="AA23">
-        <v>2.1</v>
-      </c>
-      <c r="AB23">
-        <v>1.7</v>
-      </c>
-      <c r="AC23">
-        <v>3.48</v>
-      </c>
-      <c r="AD23">
-        <v>1.22</v>
-      </c>
-      <c r="AE23">
-        <v>1.05</v>
-      </c>
-      <c r="AF23">
-        <v>1.87</v>
-      </c>
-      <c r="AG23">
-        <v>1.83</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.25</v>
-      </c>
       <c r="AK23">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O30">
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q30">
-        <v>3.47</v>
+        <v>3.24</v>
       </c>
       <c r="R30">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S30">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U30">
+        <v>2.38</v>
+      </c>
+      <c r="V30">
+        <v>1.52</v>
+      </c>
+      <c r="W30">
+        <v>1.08</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.15</v>
+      </c>
+      <c r="Z30">
+        <v>4.2</v>
+      </c>
+      <c r="AA30">
+        <v>1.57</v>
+      </c>
+      <c r="AB30">
         <v>1.89</v>
       </c>
-      <c r="V30">
-        <v>1.57</v>
-      </c>
-      <c r="W30">
-        <v>1.1</v>
-      </c>
-      <c r="X30">
-        <v>1.02</v>
-      </c>
-      <c r="Y30">
-        <v>1.11</v>
-      </c>
-      <c r="Z30">
-        <v>4.85</v>
-      </c>
-      <c r="AA30">
-        <v>1.53</v>
-      </c>
-      <c r="AB30">
-        <v>2.35</v>
-      </c>
       <c r="AC30">
-        <v>2.22</v>
+        <v>2.63</v>
       </c>
       <c r="AD30">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE30">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AG30">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O31">
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q31">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="R31">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S31">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T31">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="U31">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="V31">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z31">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="AA31">
+        <v>1.53</v>
+      </c>
+      <c r="AB31">
+        <v>2.35</v>
+      </c>
+      <c r="AC31">
+        <v>2.22</v>
+      </c>
+      <c r="AD31">
+        <v>1.56</v>
+      </c>
+      <c r="AE31">
+        <v>1.19</v>
+      </c>
+      <c r="AF31">
+        <v>1.43</v>
+      </c>
+      <c r="AG31">
+        <v>2.5</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.57</v>
       </c>
-      <c r="AB31">
-        <v>1.89</v>
-      </c>
-      <c r="AC31">
-        <v>2.63</v>
-      </c>
-      <c r="AD31">
-        <v>1.44</v>
-      </c>
-      <c r="AE31">
-        <v>1.14</v>
-      </c>
-      <c r="AF31">
-        <v>1.5</v>
-      </c>
-      <c r="AG31">
-        <v>2.38</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.22</v>
-      </c>
       <c r="AK31">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P40">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q40">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S40">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T40">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="U40">
-        <v>2.51</v>
+        <v>2.95</v>
       </c>
       <c r="V40">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X40">
+        <v>1.03</v>
+      </c>
+      <c r="Y40">
+        <v>1.36</v>
+      </c>
+      <c r="Z40">
+        <v>2.9</v>
+      </c>
+      <c r="AA40">
+        <v>2.11</v>
+      </c>
+      <c r="AB40">
+        <v>1.62</v>
+      </c>
+      <c r="AC40">
+        <v>3.78</v>
+      </c>
+      <c r="AD40">
+        <v>1.19</v>
+      </c>
+      <c r="AE40">
         <v>1.02</v>
       </c>
-      <c r="Y40">
-        <v>1.22</v>
-      </c>
-      <c r="Z40">
-        <v>3.48</v>
-      </c>
-      <c r="AA40">
-        <v>1.8</v>
-      </c>
-      <c r="AB40">
-        <v>1.87</v>
-      </c>
-      <c r="AC40">
-        <v>2.97</v>
-      </c>
-      <c r="AD40">
-        <v>1.3</v>
-      </c>
-      <c r="AE40">
-        <v>1.08</v>
-      </c>
       <c r="AF40">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK40">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="O41">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q41">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="R41">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="U41">
-        <v>2.95</v>
+        <v>2.51</v>
       </c>
       <c r="V41">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="AA41">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AB41">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC41">
-        <v>3.78</v>
+        <v>2.97</v>
       </c>
       <c r="AD41">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AG41">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -804,46 +804,46 @@
         <v>3.15</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="R3">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="S3">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="U3">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
         <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA3">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AB3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC3">
-        <v>3.92</v>
+        <v>4.01</v>
       </c>
       <c r="AD3">
         <v>1.18</v>
@@ -859,34 +859,34 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "68", "78"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK3">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>2.29</v>
       </c>
       <c r="Q4">
-        <v>4.08</v>
+        <v>3.75</v>
       </c>
       <c r="R4">
         <v>1.78</v>
@@ -979,46 +979,46 @@
         <v>1.54</v>
       </c>
       <c r="T4">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="U4">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="V4">
         <v>1.25</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
         <v>1.07</v>
       </c>
       <c r="Y4">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z4">
         <v>2.43</v>
       </c>
       <c r="AA4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AB4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC4">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF4">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1116,115 +1116,115 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="Q5">
+        <v>3.1</v>
+      </c>
+      <c r="R5">
+        <v>1.99</v>
+      </c>
+      <c r="S5">
+        <v>1.33</v>
+      </c>
+      <c r="T5">
         <v>3</v>
       </c>
-      <c r="R5">
-        <v>2.27</v>
-      </c>
-      <c r="S5">
-        <v>1.3</v>
-      </c>
-      <c r="T5">
-        <v>3.2</v>
-      </c>
       <c r="U5">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA5">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC5">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "24"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK5">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1296,55 +1296,55 @@
         <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="R6">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="S6">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="T6">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="U6">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="V6">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
         <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y6">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z6">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AA6">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AB6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC6">
         <v>6.5</v>
       </c>
       <c r="AD6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AG6">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1427,81 +1427,81 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
         <v>2.8</v>
       </c>
       <c r="P7">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="Q7">
-        <v>4.85</v>
+        <v>4.47</v>
       </c>
       <c r="R7">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="S7">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="T7">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U7">
         <v>3.8</v>
       </c>
       <c r="V7">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
         <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z7">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="AA7">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AB7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC7">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="AD7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
         <v>2.3</v>
@@ -1511,46 +1511,46 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="O15">
         <v>3.1</v>
       </c>
       <c r="P15">
-        <v>3.63</v>
+        <v>3.95</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="R15">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T15">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="U15">
         <v>3.3</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W15">
         <v>1.03</v>
@@ -2787,31 +2787,31 @@
         <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="Z15">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AA15">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AB15">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC15">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AD15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AG15">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P16">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q16">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="R16">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U16">
         <v>2.88</v>
@@ -2947,34 +2947,34 @@
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AD16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE16">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
         <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
         <v>2.1</v>
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
+        <v>2.36</v>
+      </c>
+      <c r="O17">
+        <v>3.3</v>
+      </c>
+      <c r="P17">
+        <v>2.7</v>
+      </c>
+      <c r="Q17">
+        <v>2.99</v>
+      </c>
+      <c r="R17">
         <v>2.1</v>
-      </c>
-      <c r="O17">
-        <v>3.5</v>
-      </c>
-      <c r="P17">
-        <v>2.95</v>
-      </c>
-      <c r="Q17">
-        <v>2.72</v>
-      </c>
-      <c r="R17">
-        <v>2.32</v>
       </c>
       <c r="S17">
         <v>1.29</v>
       </c>
       <c r="T17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
         <v>1.08</v>
@@ -3116,25 +3116,25 @@
         <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AA17">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB17">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC17">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD17">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE17">
         <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG17">
         <v>2.25</v>
@@ -3153,7 +3153,7 @@
         <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,31 +3243,31 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="Q18">
-        <v>3.98</v>
+        <v>5.5</v>
       </c>
       <c r="R18">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S18">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V18">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
         <v>1.06</v>
@@ -3276,32 +3276,32 @@
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z18">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA18">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC18">
         <v>3.3</v>
       </c>
       <c r="AD18">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE18">
         <v>1.07</v>
       </c>
       <c r="AF18">
+        <v>1.95</v>
+      </c>
+      <c r="AG18">
         <v>1.75</v>
       </c>
-      <c r="AG18">
-        <v>1.95</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="AK18">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.35</v>
+        <v>3.65</v>
       </c>
       <c r="O19">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P19">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="Q19">
-        <v>3.26</v>
+        <v>4.93</v>
       </c>
       <c r="R19">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="V19">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z19">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="AA19">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AB19">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE19">
         <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AK19">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.65</v>
+        <v>1.91</v>
       </c>
       <c r="O20">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>1.97</v>
+        <v>3.3</v>
       </c>
       <c r="Q20">
-        <v>4.93</v>
+        <v>2.6</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="U20">
-        <v>2.73</v>
+        <v>3.03</v>
       </c>
       <c r="V20">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.33</v>
+      </c>
+      <c r="Z20">
+        <v>3.1</v>
+      </c>
+      <c r="AA20">
+        <v>2.1</v>
+      </c>
+      <c r="AB20">
+        <v>1.7</v>
+      </c>
+      <c r="AC20">
+        <v>3.48</v>
+      </c>
+      <c r="AD20">
+        <v>1.22</v>
+      </c>
+      <c r="AE20">
         <v>1.05</v>
       </c>
-      <c r="X20">
-        <v>1.02</v>
-      </c>
-      <c r="Y20">
-        <v>1.28</v>
-      </c>
-      <c r="Z20">
-        <v>3.08</v>
-      </c>
-      <c r="AA20">
-        <v>1.93</v>
-      </c>
-      <c r="AB20">
-        <v>1.75</v>
-      </c>
-      <c r="AC20">
-        <v>3.2</v>
-      </c>
-      <c r="AD20">
-        <v>1.26</v>
-      </c>
-      <c r="AE20">
-        <v>1.06</v>
-      </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG20">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
+        <v>2.37</v>
+      </c>
+      <c r="O21">
+        <v>2.8</v>
+      </c>
+      <c r="P21">
+        <v>2.9</v>
+      </c>
+      <c r="Q21">
+        <v>3.4</v>
+      </c>
+      <c r="R21">
         <v>1.91</v>
       </c>
-      <c r="O21">
-        <v>3.1</v>
-      </c>
-      <c r="P21">
-        <v>3.3</v>
-      </c>
-      <c r="Q21">
-        <v>2.6</v>
-      </c>
-      <c r="R21">
-        <v>1.98</v>
-      </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="T21">
-        <v>2.51</v>
+        <v>2.18</v>
       </c>
       <c r="U21">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="V21">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y21">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="Z21">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA21">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AB21">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AC21">
-        <v>3.48</v>
+        <v>4.65</v>
       </c>
       <c r="AD21">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE21">
         <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="O22">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P22">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R22">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="T22">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="U22">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="V22">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W22">
         <v>1.01</v>
       </c>
       <c r="X22">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Z22">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="AA22">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AB22">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AC22">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="AD22">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="O23">
         <v>2.9</v>
       </c>
       <c r="P23">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q23">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="S23">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T23">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="U23">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z23">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AA23">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB23">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC23">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AD23">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE23">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG23">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK23">
         <v>1.4</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
         <v>3.3</v>
@@ -4396,13 +4396,13 @@
         <v>5</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S25">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="T25">
-        <v>2.64</v>
+        <v>2.22</v>
       </c>
       <c r="U25">
         <v>3.35</v>
@@ -4411,37 +4411,37 @@
         <v>1.31</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="Z25">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AA25">
+        <v>2.5</v>
+      </c>
+      <c r="AB25">
+        <v>1.48</v>
+      </c>
+      <c r="AC25">
+        <v>4.55</v>
+      </c>
+      <c r="AD25">
+        <v>1.14</v>
+      </c>
+      <c r="AE25">
+        <v>1.02</v>
+      </c>
+      <c r="AF25">
         <v>2.2</v>
       </c>
-      <c r="AB25">
-        <v>1.61</v>
-      </c>
-      <c r="AC25">
-        <v>3.82</v>
-      </c>
-      <c r="AD25">
-        <v>1.19</v>
-      </c>
-      <c r="AE25">
-        <v>1.03</v>
-      </c>
-      <c r="AF25">
-        <v>2.05</v>
-      </c>
       <c r="AG25">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.5</v>
+        <v>2.85</v>
       </c>
       <c r="O29">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q29">
-        <v>1.95</v>
+        <v>3.24</v>
       </c>
       <c r="R29">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="S29">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T29">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="U29">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>6.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA29">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AB29">
-        <v>3.13</v>
+        <v>1.89</v>
       </c>
       <c r="AC29">
-        <v>1.93</v>
+        <v>2.63</v>
       </c>
       <c r="AD29">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AE29">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG29">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>2.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.85</v>
+        <v>1.5</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="P30">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q30">
-        <v>3.24</v>
+        <v>1.95</v>
       </c>
       <c r="R30">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="S30">
+        <v>1.18</v>
+      </c>
+      <c r="T30">
+        <v>4.4</v>
+      </c>
+      <c r="U30">
+        <v>1.95</v>
+      </c>
+      <c r="V30">
+        <v>1.83</v>
+      </c>
+      <c r="W30">
         <v>1.22</v>
-      </c>
-      <c r="T30">
-        <v>3.5</v>
-      </c>
-      <c r="U30">
-        <v>2.38</v>
-      </c>
-      <c r="V30">
-        <v>1.52</v>
-      </c>
-      <c r="W30">
-        <v>1.08</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="Z30">
-        <v>4.2</v>
+        <v>6.65</v>
       </c>
       <c r="AA30">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AB30">
-        <v>1.89</v>
+        <v>3.13</v>
       </c>
       <c r="AC30">
-        <v>2.63</v>
+        <v>1.93</v>
       </c>
       <c r="AD30">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AF30">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG30">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK30">
-        <v>1.36</v>
+        <v>2.34</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>5.8</v>
+        <v>5.05</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T39">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U39">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V39">
+        <v>1.3</v>
+      </c>
+      <c r="W39">
+        <v>1.03</v>
+      </c>
+      <c r="X39">
+        <v>1.07</v>
+      </c>
+      <c r="Y39">
         <v>1.36</v>
       </c>
-      <c r="W39">
-        <v>1.05</v>
-      </c>
-      <c r="X39">
-        <v>1.03</v>
-      </c>
-      <c r="Y39">
-        <v>1.3</v>
-      </c>
       <c r="Z39">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA39">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB39">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC39">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD39">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE39">
         <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG39">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK39">
-        <v>2.47</v>
+        <v>1.89</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
+        <v>3.75</v>
+      </c>
+      <c r="O40">
+        <v>3.4</v>
+      </c>
+      <c r="P40">
+        <v>1.86</v>
+      </c>
+      <c r="Q40">
+        <v>4.28</v>
+      </c>
+      <c r="R40">
+        <v>2.25</v>
+      </c>
+      <c r="S40">
+        <v>1.35</v>
+      </c>
+      <c r="T40">
+        <v>3.08</v>
+      </c>
+      <c r="U40">
+        <v>2.44</v>
+      </c>
+      <c r="V40">
+        <v>1.46</v>
+      </c>
+      <c r="W40">
+        <v>1.11</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.22</v>
+      </c>
+      <c r="Z40">
+        <v>4</v>
+      </c>
+      <c r="AA40">
         <v>1.75</v>
       </c>
-      <c r="O40">
-        <v>3.2</v>
-      </c>
-      <c r="P40">
-        <v>4.2</v>
-      </c>
-      <c r="Q40">
-        <v>2.41</v>
-      </c>
-      <c r="R40">
-        <v>2.12</v>
-      </c>
-      <c r="S40">
-        <v>1.43</v>
-      </c>
-      <c r="T40">
-        <v>2.48</v>
-      </c>
-      <c r="U40">
-        <v>2.95</v>
-      </c>
-      <c r="V40">
-        <v>1.31</v>
-      </c>
-      <c r="W40">
-        <v>1.03</v>
-      </c>
-      <c r="X40">
-        <v>1.03</v>
-      </c>
-      <c r="Y40">
+      <c r="AB40">
+        <v>2.05</v>
+      </c>
+      <c r="AC40">
+        <v>2.88</v>
+      </c>
+      <c r="AD40">
         <v>1.36</v>
       </c>
-      <c r="Z40">
-        <v>2.9</v>
-      </c>
-      <c r="AA40">
-        <v>2.11</v>
-      </c>
-      <c r="AB40">
-        <v>1.62</v>
-      </c>
-      <c r="AC40">
-        <v>3.78</v>
-      </c>
-      <c r="AD40">
-        <v>1.19</v>
-      </c>
       <c r="AE40">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AG40">
-        <v>1.74</v>
+        <v>2.13</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.12</v>
+        <v>1.83</v>
       </c>
       <c r="AK40">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,28 +7155,28 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="O42">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P42">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q42">
-        <v>3.88</v>
+        <v>2.41</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S42">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T42">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="U42">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="V42">
         <v>1.31</v>
@@ -7188,31 +7188,31 @@
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z42">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AA42">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AB42">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC42">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AD42">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE42">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF42">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG42">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AK42">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="Q43">
-        <v>4.28</v>
+        <v>3.88</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="T43">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="U43">
-        <v>2.44</v>
+        <v>2.82</v>
       </c>
       <c r="V43">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="AA43">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AB43">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AC43">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD43">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AG43">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL43">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "33"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+7"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "47"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1602,21 +1602,21 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="O8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
         <v>2.44</v>
@@ -1628,92 +1628,92 @@
         <v>1.99</v>
       </c>
       <c r="S8">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="U8">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>3.26</v>
+        <v>3.41</v>
       </c>
       <c r="AA8">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AB8">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC8">
-        <v>3.68</v>
+        <v>3.52</v>
       </c>
       <c r="AD8">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG8">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AJ8">
+        <v>1.49</v>
+      </c>
+      <c r="AK8">
         <v>1.38</v>
       </c>
-      <c r="AK8">
-        <v>1.4</v>
-      </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1765,88 +1765,88 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="O9">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="P9">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="Q9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R9">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="AA9">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AB9">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AC9">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>["90+1"]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK9">
         <v>3.28</v>
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,66 +1916,66 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q10">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="R10">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
         <v>1.35</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U10">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
         <v>1.09</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
         <v>1.75</v>
@@ -1990,56 +1990,56 @@
         <v>1.25</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
         <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "43", "51"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "19"]</t>
         </is>
       </c>
       <c r="AJ10">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,16 +2079,16 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -2098,17 +2098,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q11">
         <v>5.75</v>
@@ -2123,74 +2123,74 @@
         <v>2.5</v>
       </c>
       <c r="U11">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="V11">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z11">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA11">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB11">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="AD11">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE11">
         <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG11">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "45+2"]</t>
         </is>
       </c>
       <c r="AJ11">
         <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -2242,130 +2242,130 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="O12">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="P12">
         <v>5</v>
       </c>
       <c r="Q12">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R12">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="S12">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T12">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U12">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="W12">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z12">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA12">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB12">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AC12">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="AD12">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE12">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG12">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>["6", "90+2"]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ12">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2424,38 +2424,38 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
         <v>1.24</v>
       </c>
       <c r="O13">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P13">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q13">
         <v>1.62</v>
       </c>
       <c r="R13">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="S13">
         <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U13">
         <v>2.05</v>
       </c>
       <c r="V13">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.02</v>
@@ -2473,62 +2473,62 @@
         <v>2.75</v>
       </c>
       <c r="AC13">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AD13">
         <v>1.61</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF13">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG13">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>["12"]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ13">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK13">
-        <v>3.06</v>
+        <v>2.75</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2571,33 +2571,33 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>5.1</v>
+        <v>7.45</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P14">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="Q14">
         <v>4.7</v>
@@ -2612,16 +2612,16 @@
         <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V14">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
         <v>1.14</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
         <v>1.15</v>
@@ -2630,25 +2630,25 @@
         <v>3.7</v>
       </c>
       <c r="AA14">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AB14">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="AC14">
         <v>2.95</v>
       </c>
       <c r="AD14">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF14">
         <v>1.74</v>
       </c>
       <c r="AG14">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "84"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2688,10 +2688,10 @@
         <v>0</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2743,14 +2743,14 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "72"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,13 +2894,13 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3048,22 +3048,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3072,115 +3072,115 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>2.36</v>
+        <v>5</v>
       </c>
       <c r="O17">
+        <v>3.7</v>
+      </c>
+      <c r="P17">
+        <v>1.57</v>
+      </c>
+      <c r="Q17">
+        <v>5.5</v>
+      </c>
+      <c r="R17">
+        <v>2.21</v>
+      </c>
+      <c r="S17">
+        <v>1.34</v>
+      </c>
+      <c r="T17">
+        <v>3</v>
+      </c>
+      <c r="U17">
+        <v>2.72</v>
+      </c>
+      <c r="V17">
+        <v>1.36</v>
+      </c>
+      <c r="W17">
+        <v>1.06</v>
+      </c>
+      <c r="X17">
+        <v>1.02</v>
+      </c>
+      <c r="Y17">
+        <v>1.27</v>
+      </c>
+      <c r="Z17">
+        <v>3.14</v>
+      </c>
+      <c r="AA17">
+        <v>1.91</v>
+      </c>
+      <c r="AB17">
+        <v>1.75</v>
+      </c>
+      <c r="AC17">
         <v>3.3</v>
       </c>
-      <c r="P17">
-        <v>2.7</v>
-      </c>
-      <c r="Q17">
-        <v>2.99</v>
-      </c>
-      <c r="R17">
-        <v>2.1</v>
-      </c>
-      <c r="S17">
-        <v>1.29</v>
-      </c>
-      <c r="T17">
-        <v>3.3</v>
-      </c>
-      <c r="U17">
-        <v>2.55</v>
-      </c>
-      <c r="V17">
-        <v>1.47</v>
-      </c>
-      <c r="W17">
-        <v>1.08</v>
-      </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
-        <v>1.2</v>
-      </c>
-      <c r="Z17">
-        <v>3.94</v>
-      </c>
-      <c r="AA17">
-        <v>1.68</v>
-      </c>
-      <c r="AB17">
-        <v>2.07</v>
-      </c>
-      <c r="AC17">
-        <v>2.88</v>
-      </c>
       <c r="AD17">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="AK17">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3211,22 +3211,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3239,111 +3239,111 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
+        <v>2.36</v>
+      </c>
+      <c r="O18">
+        <v>3.3</v>
+      </c>
+      <c r="P18">
+        <v>2.7</v>
+      </c>
+      <c r="Q18">
+        <v>2.99</v>
+      </c>
+      <c r="R18">
+        <v>2.1</v>
+      </c>
+      <c r="S18">
+        <v>1.29</v>
+      </c>
+      <c r="T18">
+        <v>3.3</v>
+      </c>
+      <c r="U18">
+        <v>2.55</v>
+      </c>
+      <c r="V18">
+        <v>1.47</v>
+      </c>
+      <c r="W18">
+        <v>1.08</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.2</v>
+      </c>
+      <c r="Z18">
+        <v>3.94</v>
+      </c>
+      <c r="AA18">
+        <v>1.68</v>
+      </c>
+      <c r="AB18">
+        <v>2.07</v>
+      </c>
+      <c r="AC18">
+        <v>2.88</v>
+      </c>
+      <c r="AD18">
+        <v>1.36</v>
+      </c>
+      <c r="AE18">
+        <v>1.11</v>
+      </c>
+      <c r="AF18">
+        <v>1.57</v>
+      </c>
+      <c r="AG18">
+        <v>2.25</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>["32", "43"]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.24</v>
+      </c>
+      <c r="AK18">
+        <v>1.5</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
         <v>5</v>
       </c>
-      <c r="O18">
-        <v>3.7</v>
-      </c>
-      <c r="P18">
-        <v>1.57</v>
-      </c>
-      <c r="Q18">
-        <v>5.5</v>
-      </c>
-      <c r="R18">
-        <v>2.21</v>
-      </c>
-      <c r="S18">
-        <v>1.34</v>
-      </c>
-      <c r="T18">
+      <c r="AN18">
         <v>3</v>
       </c>
-      <c r="U18">
-        <v>2.72</v>
-      </c>
-      <c r="V18">
-        <v>1.36</v>
-      </c>
-      <c r="W18">
-        <v>1.06</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
-        <v>1.27</v>
-      </c>
-      <c r="Z18">
-        <v>3.14</v>
-      </c>
-      <c r="AA18">
-        <v>1.91</v>
-      </c>
-      <c r="AB18">
-        <v>1.75</v>
-      </c>
-      <c r="AC18">
-        <v>3.3</v>
-      </c>
-      <c r="AD18">
-        <v>1.26</v>
-      </c>
-      <c r="AE18">
+      <c r="AO18">
+        <v>13</v>
+      </c>
+      <c r="AP18">
+        <v>8</v>
+      </c>
+      <c r="AQ18">
+        <v>1.62</v>
+      </c>
+      <c r="AR18">
         <v>1.07</v>
       </c>
-      <c r="AF18">
-        <v>1.95</v>
-      </c>
-      <c r="AG18">
-        <v>1.75</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>2.3</v>
-      </c>
-      <c r="AK18">
-        <v>1.13</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>-1</v>
-      </c>
-      <c r="AN18">
-        <v>-1</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>-1</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
       <c r="AS18">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3386,13 +3386,13 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -3402,68 +3402,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O19">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="Q19">
-        <v>4.93</v>
+        <v>4.33</v>
       </c>
       <c r="R19">
         <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>2.73</v>
+        <v>2.54</v>
       </c>
       <c r="V19">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z19">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA19">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AB19">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC19">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD19">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3472,41 +3472,41 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35"]</t>
         </is>
       </c>
       <c r="AJ19">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AK19">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3537,25 +3537,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -3565,111 +3565,111 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P20">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q20">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="R20">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="S20">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="U20">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z20">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AA20">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC20">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE20">
         <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG20">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK20">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3724,115 +3724,115 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="O21">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P21">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q21">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R21">
         <v>1.91</v>
       </c>
       <c r="S21">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="T21">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="U21">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V21">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Z21">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AA21">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AB21">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC21">
         <v>4.65</v>
       </c>
       <c r="AD21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE21">
         <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG21">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+3"]</t>
         </is>
       </c>
       <c r="AJ21">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK21">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3887,85 +3887,85 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
         <v>2.7</v>
       </c>
       <c r="O22">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q22">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="R22">
         <v>2</v>
       </c>
       <c r="S22">
+        <v>1.44</v>
+      </c>
+      <c r="T22">
+        <v>2.51</v>
+      </c>
+      <c r="U22">
+        <v>3</v>
+      </c>
+      <c r="V22">
+        <v>1.33</v>
+      </c>
+      <c r="W22">
+        <v>1.06</v>
+      </c>
+      <c r="X22">
+        <v>1.02</v>
+      </c>
+      <c r="Y22">
+        <v>1.34</v>
+      </c>
+      <c r="Z22">
+        <v>3.08</v>
+      </c>
+      <c r="AA22">
+        <v>2.07</v>
+      </c>
+      <c r="AB22">
+        <v>1.68</v>
+      </c>
+      <c r="AC22">
+        <v>3.5</v>
+      </c>
+      <c r="AD22">
+        <v>1.22</v>
+      </c>
+      <c r="AE22">
+        <v>1.05</v>
+      </c>
+      <c r="AF22">
+        <v>1.75</v>
+      </c>
+      <c r="AG22">
+        <v>1.91</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>["11", "22"]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>["70", "90+5"]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.47</v>
-      </c>
-      <c r="T22">
-        <v>2.38</v>
-      </c>
-      <c r="U22">
-        <v>3.2</v>
-      </c>
-      <c r="V22">
-        <v>1.3</v>
-      </c>
-      <c r="W22">
-        <v>1.01</v>
-      </c>
-      <c r="X22">
-        <v>1.04</v>
-      </c>
-      <c r="Y22">
-        <v>1.4</v>
-      </c>
-      <c r="Z22">
-        <v>2.76</v>
-      </c>
-      <c r="AA22">
-        <v>2.2</v>
-      </c>
-      <c r="AB22">
-        <v>1.57</v>
-      </c>
-      <c r="AC22">
-        <v>3.98</v>
-      </c>
-      <c r="AD22">
-        <v>1.17</v>
-      </c>
-      <c r="AE22">
-        <v>1.04</v>
-      </c>
-      <c r="AF22">
-        <v>1.91</v>
-      </c>
-      <c r="AG22">
-        <v>1.81</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.33</v>
       </c>
       <c r="AK22">
         <v>1.4</v>
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4026,139 +4026,139 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="O23">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q23">
-        <v>3.26</v>
+        <v>2.3</v>
       </c>
       <c r="R23">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T23">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="U23">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="V23">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
         <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z23">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="AA23">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB23">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC23">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="AD23">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG23">
         <v>1.85</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "83"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3"]</t>
         </is>
       </c>
       <c r="AJ23">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,100 +4198,100 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
         <v>2.65</v>
       </c>
       <c r="O24">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
         <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T24">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U24">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W24">
+        <v>1.07</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>1.28</v>
+      </c>
+      <c r="Z24">
+        <v>3.08</v>
+      </c>
+      <c r="AA24">
+        <v>1.91</v>
+      </c>
+      <c r="AB24">
+        <v>1.81</v>
+      </c>
+      <c r="AC24">
+        <v>3.28</v>
+      </c>
+      <c r="AD24">
+        <v>1.25</v>
+      </c>
+      <c r="AE24">
         <v>1.06</v>
       </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
-      <c r="Y24">
-        <v>1.3</v>
-      </c>
-      <c r="Z24">
-        <v>2.97</v>
-      </c>
-      <c r="AA24">
-        <v>1.98</v>
-      </c>
-      <c r="AB24">
-        <v>1.76</v>
-      </c>
-      <c r="AC24">
-        <v>3.42</v>
-      </c>
-      <c r="AD24">
-        <v>1.23</v>
-      </c>
-      <c r="AE24">
-        <v>1.05</v>
-      </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG24">
         <v>1.91</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "85"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "54", "67"]</t>
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
         <v>1.37</v>
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4376,11 +4376,11 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AJ25">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,13 +4524,13 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4539,66 +4539,66 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
         <v>3.1</v>
       </c>
       <c r="Q26">
+        <v>2.4</v>
+      </c>
+      <c r="R26">
         <v>2.44</v>
       </c>
-      <c r="R26">
-        <v>2.45</v>
-      </c>
       <c r="S26">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T26">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V26">
         <v>1.72</v>
       </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z26">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="AA26">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB26">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AC26">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AD26">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE26">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF26">
         <v>1.38</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "14", "28", "36"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["74"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,45 +4687,45 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q27">
-        <v>3.24</v>
+        <v>2.76</v>
       </c>
       <c r="R27">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T27">
         <v>3.55</v>
@@ -4737,13 +4737,13 @@
         <v>1.61</v>
       </c>
       <c r="W27">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z27">
         <v>5</v>
@@ -4755,7 +4755,7 @@
         <v>2.4</v>
       </c>
       <c r="AC27">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="AD27">
         <v>1.62</v>
@@ -4764,19 +4764,19 @@
         <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG27">
         <v>2.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "54"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "29", "65", "86"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4841,139 +4841,139 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="O28">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="P28">
-        <v>2.47</v>
+        <v>4.6</v>
       </c>
       <c r="Q28">
-        <v>3.32</v>
+        <v>1.8</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T28">
-        <v>2.32</v>
+        <v>4.25</v>
       </c>
       <c r="U28">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="Z28">
-        <v>3.8</v>
+        <v>6.25</v>
       </c>
       <c r="AA28">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AB28">
-        <v>1.88</v>
+        <v>3.05</v>
       </c>
       <c r="AC28">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="AD28">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AF28">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AG28">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "50", "87"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54", "65"]</t>
         </is>
       </c>
       <c r="AJ28">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,45 +5013,45 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q29">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T29">
         <v>3.5</v>
@@ -5063,7 +5063,7 @@
         <v>1.52</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5072,7 +5072,7 @@
         <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA29">
         <v>1.57</v>
@@ -5081,10 +5081,10 @@
         <v>1.89</v>
       </c>
       <c r="AC29">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD29">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE29">
         <v>1.14</v>
@@ -5093,50 +5093,50 @@
         <v>1.5</v>
       </c>
       <c r="AG29">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "57", "62"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "19", "29"]</t>
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK29">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5167,25 +5167,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -5195,68 +5195,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="O30">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="P30">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q30">
-        <v>1.95</v>
+        <v>3.42</v>
       </c>
       <c r="R30">
+        <v>2.06</v>
+      </c>
+      <c r="S30">
+        <v>1.34</v>
+      </c>
+      <c r="T30">
+        <v>3.17</v>
+      </c>
+      <c r="U30">
         <v>2.75</v>
       </c>
-      <c r="S30">
-        <v>1.18</v>
-      </c>
-      <c r="T30">
-        <v>4.4</v>
-      </c>
-      <c r="U30">
-        <v>1.95</v>
-      </c>
       <c r="V30">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
+        <v>1.05</v>
+      </c>
+      <c r="X30">
+        <v>1</v>
+      </c>
+      <c r="Y30">
         <v>1.22</v>
       </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.05</v>
-      </c>
       <c r="Z30">
-        <v>6.65</v>
+        <v>3.42</v>
       </c>
       <c r="AA30">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB30">
-        <v>3.13</v>
+        <v>1.91</v>
       </c>
       <c r="AC30">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="AD30">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="AE30">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AG30">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5265,41 +5265,41 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "44"]</t>
         </is>
       </c>
       <c r="AJ30">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK30">
-        <v>2.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5351,18 +5351,18 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="O31">
         <v>3.4</v>
@@ -5371,22 +5371,22 @@
         <v>2.1</v>
       </c>
       <c r="Q31">
-        <v>3.47</v>
+        <v>2.95</v>
       </c>
       <c r="R31">
         <v>2.28</v>
       </c>
       <c r="S31">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T31">
         <v>2.8</v>
       </c>
       <c r="U31">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W31">
         <v>1.1</v>
@@ -5395,74 +5395,74 @@
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA31">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB31">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC31">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AD31">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AE31">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AF31">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
         <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "72"]</t>
         </is>
       </c>
       <c r="AJ31">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK31">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,130 +5502,130 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
         <v>1.91</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q32">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R32">
         <v>2.5</v>
       </c>
       <c r="S32">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T32">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="V32">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W32">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z32">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="AA32">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AB32">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AC32">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AD32">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE32">
+        <v>1.28</v>
+      </c>
+      <c r="AF32">
+        <v>1.29</v>
+      </c>
+      <c r="AG32">
+        <v>2.88</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>["31"]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>["43", "84"]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.25</v>
       </c>
-      <c r="AF32">
-        <v>1.4</v>
-      </c>
-      <c r="AG32">
-        <v>2.7</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.19</v>
-      </c>
       <c r="AK32">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,54 +5665,54 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="O33">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="P33">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q33">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R33">
         <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
         <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "54", "63", "82"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -5761,34 +5761,34 @@
         <v>1.15</v>
       </c>
       <c r="AK33">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5843,21 +5843,21 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="O34">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P34">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
         <v>2.9</v>
@@ -5884,10 +5884,10 @@
         <v>1.08</v>
       </c>
       <c r="Y34">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z34">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA34">
         <v>2.28</v>
@@ -5896,7 +5896,7 @@
         <v>1.6</v>
       </c>
       <c r="AC34">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AD34">
         <v>1.22</v>
@@ -5908,7 +5908,7 @@
         <v>1.9</v>
       </c>
       <c r="AG34">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5917,41 +5917,41 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AJ34">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,16 +5991,16 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
@@ -6029,10 +6029,10 @@
         <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="U35">
         <v>2.48</v>
@@ -6041,10 +6041,10 @@
         <v>1.46</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.2</v>
@@ -6056,7 +6056,7 @@
         <v>1.71</v>
       </c>
       <c r="AB35">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AC35">
         <v>2.93</v>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6154,54 +6154,54 @@
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P36">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="Q36">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S36">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="T36">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="U36">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="V36">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W36">
         <v>1.03</v>
@@ -6213,19 +6213,19 @@
         <v>1.44</v>
       </c>
       <c r="Z36">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AA36">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AB36">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AC36">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AD36">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
         <v>1.02</v>
@@ -6234,50 +6234,50 @@
         <v>2.03</v>
       </c>
       <c r="AG36">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "81"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "16", "49"]</t>
         </is>
       </c>
       <c r="AJ36">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AL36">
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -6329,14 +6329,14 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
@@ -6349,19 +6349,19 @@
         <v>3.33</v>
       </c>
       <c r="Q37">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="R37">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="S37">
         <v>1.33</v>
       </c>
       <c r="T37">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="U37">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
         <v>1.47</v>
@@ -6370,77 +6370,77 @@
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="AA37">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC37">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="AD37">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE37">
         <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG37">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ37">
         <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6643,13 +6643,13 @@
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -6658,11 +6658,11 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40"]</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71", "90+4"]</t>
         </is>
       </c>
       <c r="AJ39">
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,65 +6829,65 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.75</v>
+        <v>1.7</v>
       </c>
       <c r="O40">
         <v>3.4</v>
       </c>
       <c r="P40">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="Q40">
-        <v>4.28</v>
+        <v>2.3</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="S40">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T40">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="U40">
-        <v>2.44</v>
+        <v>2.81</v>
       </c>
       <c r="V40">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z40">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AA40">
+        <v>2.01</v>
+      </c>
+      <c r="AB40">
+        <v>1.73</v>
+      </c>
+      <c r="AC40">
+        <v>3.75</v>
+      </c>
+      <c r="AD40">
+        <v>1.25</v>
+      </c>
+      <c r="AE40">
+        <v>1.05</v>
+      </c>
+      <c r="AF40">
+        <v>1.95</v>
+      </c>
+      <c r="AG40">
         <v>1.75</v>
       </c>
-      <c r="AB40">
-        <v>2.05</v>
-      </c>
-      <c r="AC40">
-        <v>2.88</v>
-      </c>
-      <c r="AD40">
-        <v>1.36</v>
-      </c>
-      <c r="AE40">
-        <v>1.13</v>
-      </c>
-      <c r="AF40">
-        <v>1.61</v>
-      </c>
-      <c r="AG40">
-        <v>2.13</v>
-      </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="AK40">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="P41">
-        <v>4.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q41">
+        <v>4</v>
+      </c>
+      <c r="R41">
+        <v>2</v>
+      </c>
+      <c r="S41">
+        <v>1.4</v>
+      </c>
+      <c r="T41">
+        <v>2.75</v>
+      </c>
+      <c r="U41">
+        <v>2.97</v>
+      </c>
+      <c r="V41">
+        <v>1.35</v>
+      </c>
+      <c r="W41">
+        <v>1.05</v>
+      </c>
+      <c r="X41">
+        <v>1.06</v>
+      </c>
+      <c r="Y41">
+        <v>1.31</v>
+      </c>
+      <c r="Z41">
+        <v>2.92</v>
+      </c>
+      <c r="AA41">
         <v>2.1</v>
       </c>
-      <c r="R41">
-        <v>2.3</v>
-      </c>
-      <c r="S41">
-        <v>1.38</v>
-      </c>
-      <c r="T41">
-        <v>2.88</v>
-      </c>
-      <c r="U41">
-        <v>2.51</v>
-      </c>
-      <c r="V41">
-        <v>1.42</v>
-      </c>
-      <c r="W41">
-        <v>1.08</v>
-      </c>
-      <c r="X41">
-        <v>1.02</v>
-      </c>
-      <c r="Y41">
+      <c r="AB41">
+        <v>1.67</v>
+      </c>
+      <c r="AC41">
+        <v>3.9</v>
+      </c>
+      <c r="AD41">
         <v>1.22</v>
       </c>
-      <c r="Z41">
-        <v>3.48</v>
-      </c>
-      <c r="AA41">
-        <v>1.8</v>
-      </c>
-      <c r="AB41">
-        <v>1.87</v>
-      </c>
-      <c r="AC41">
-        <v>2.97</v>
-      </c>
-      <c r="AD41">
-        <v>1.3</v>
-      </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AG41">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>2.16</v>
+        <v>1.36</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="O42">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q42">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="R42">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
+        <v>2.88</v>
+      </c>
+      <c r="U42">
         <v>2.48</v>
       </c>
-      <c r="U42">
-        <v>2.95</v>
-      </c>
       <c r="V42">
+        <v>1.4</v>
+      </c>
+      <c r="W42">
+        <v>1.08</v>
+      </c>
+      <c r="X42">
+        <v>1.02</v>
+      </c>
+      <c r="Y42">
+        <v>1.25</v>
+      </c>
+      <c r="Z42">
+        <v>3.5</v>
+      </c>
+      <c r="AA42">
+        <v>1.8</v>
+      </c>
+      <c r="AB42">
+        <v>1.9</v>
+      </c>
+      <c r="AC42">
+        <v>2.92</v>
+      </c>
+      <c r="AD42">
         <v>1.31</v>
       </c>
-      <c r="W42">
-        <v>1.03</v>
-      </c>
-      <c r="X42">
-        <v>1.03</v>
-      </c>
-      <c r="Y42">
-        <v>1.36</v>
-      </c>
-      <c r="Z42">
-        <v>2.9</v>
-      </c>
-      <c r="AA42">
-        <v>2.11</v>
-      </c>
-      <c r="AB42">
-        <v>1.62</v>
-      </c>
-      <c r="AC42">
-        <v>3.78</v>
-      </c>
-      <c r="AD42">
-        <v>1.19</v>
-      </c>
       <c r="AE42">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF42">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK42">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="O43">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="Q43">
-        <v>3.88</v>
+        <v>4.71</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S43">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="U43">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="V43">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>2.97</v>
+        <v>3.9</v>
       </c>
       <c r="AA43">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AB43">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AC43">
-        <v>3.9</v>
+        <v>2.86</v>
       </c>
       <c r="AD43">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE43">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
+        <v>2.05</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.91</v>
       </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.3</v>
-      </c>
       <c r="AK43">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="O44">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
         <v>4.5</v>
       </c>
       <c r="Q44">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="R44">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S44">
         <v>1.25</v>
       </c>
       <c r="T44">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U44">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="V44">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7520,25 +7520,25 @@
         <v>5</v>
       </c>
       <c r="AA44">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB44">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC44">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="AD44">
+        <v>1.47</v>
+      </c>
+      <c r="AE44">
+        <v>1.16</v>
+      </c>
+      <c r="AF44">
         <v>1.5</v>
       </c>
-      <c r="AE44">
-        <v>1.17</v>
-      </c>
-      <c r="AF44">
-        <v>1.53</v>
-      </c>
       <c r="AG44">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7640,20 +7640,20 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O45">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P45">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="Q45">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R45">
         <v>2.2</v>
@@ -7662,13 +7662,13 @@
         <v>1.36</v>
       </c>
       <c r="T45">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="U45">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V45">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W45">
         <v>1.08</v>
@@ -7677,28 +7677,28 @@
         <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z45">
         <v>3.6</v>
       </c>
       <c r="AA45">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB45">
         <v>2</v>
       </c>
       <c r="AC45">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="AD45">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE45">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG45">
         <v>2.15</v>
@@ -7717,7 +7717,7 @@
         <v>1.62</v>
       </c>
       <c r="AK45">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,7 +7810,7 @@
         <v>1.09</v>
       </c>
       <c r="O46">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P46">
         <v>25</v>
@@ -7828,13 +7828,13 @@
         <v>6</v>
       </c>
       <c r="U46">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V46">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="W46">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="X46">
         <v>1</v>
@@ -7846,25 +7846,25 @@
         <v>11</v>
       </c>
       <c r="AA46">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB46">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AC46">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AD46">
         <v>3.16</v>
       </c>
       <c r="AE46">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AF46">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG46">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -8142,16 +8142,16 @@
         <v>4.8</v>
       </c>
       <c r="Q48">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="R48">
         <v>2.55</v>
       </c>
       <c r="S48">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T48">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="U48">
         <v>2.15</v>
@@ -8172,22 +8172,22 @@
         <v>5.4</v>
       </c>
       <c r="AA48">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB48">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AC48">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD48">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
         <v>2.21</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK48">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,10 +8305,10 @@
         <v>2.08</v>
       </c>
       <c r="Q49">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S49">
         <v>1.25</v>
@@ -8317,13 +8317,13 @@
         <v>3.5</v>
       </c>
       <c r="U49">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="V49">
         <v>1.58</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8332,28 +8332,28 @@
         <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA49">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB49">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AC49">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AD49">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AE49">
         <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG49">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AK49">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,28 +8462,28 @@
         <v>1.7</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
       </c>
       <c r="R50">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="S50">
         <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U50">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V50">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
         <v>1.07</v>
@@ -8498,10 +8498,10 @@
         <v>4.1</v>
       </c>
       <c r="AA50">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB50">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="AC50">
         <v>3.05</v>
@@ -8513,10 +8513,10 @@
         <v>1.17</v>
       </c>
       <c r="AF50">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -9935,10 +9935,10 @@
         <v>2.45</v>
       </c>
       <c r="Q59">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="R59">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="S59">
         <v>1.34</v>
@@ -9953,10 +9953,10 @@
         <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
         <v>1.22</v>
@@ -9971,19 +9971,19 @@
         <v>2.05</v>
       </c>
       <c r="AC59">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD59">
         <v>1.4</v>
       </c>
       <c r="AE59">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF59">
         <v>1.57</v>
       </c>
       <c r="AG59">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="O60">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P60">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q60">
         <v>1.99</v>
       </c>
       <c r="R60">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T60">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U60">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="V60">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W60">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z60">
-        <v>4.85</v>
+        <v>6</v>
       </c>
       <c r="AA60">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB60">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AC60">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD60">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE60">
         <v>1.25</v>
       </c>
       <c r="AF60">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG60">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK60">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
+        <v>1.66</v>
+      </c>
+      <c r="O61">
+        <v>3.65</v>
+      </c>
+      <c r="P61">
+        <v>4.2</v>
+      </c>
+      <c r="Q61">
+        <v>1.91</v>
+      </c>
+      <c r="R61">
+        <v>2.5</v>
+      </c>
+      <c r="S61">
+        <v>1.22</v>
+      </c>
+      <c r="T61">
+        <v>3.8</v>
+      </c>
+      <c r="U61">
+        <v>2.1</v>
+      </c>
+      <c r="V61">
+        <v>1.65</v>
+      </c>
+      <c r="W61">
+        <v>1.18</v>
+      </c>
+      <c r="X61">
+        <v>1.02</v>
+      </c>
+      <c r="Y61">
+        <v>1.11</v>
+      </c>
+      <c r="Z61">
+        <v>5.2</v>
+      </c>
+      <c r="AA61">
+        <v>1.41</v>
+      </c>
+      <c r="AB61">
+        <v>2.52</v>
+      </c>
+      <c r="AC61">
+        <v>2.14</v>
+      </c>
+      <c r="AD61">
         <v>1.68</v>
       </c>
-      <c r="O61">
-        <v>3.6</v>
-      </c>
-      <c r="P61">
-        <v>4.1</v>
-      </c>
-      <c r="Q61">
-        <v>2</v>
-      </c>
-      <c r="R61">
-        <v>2.4</v>
-      </c>
-      <c r="S61">
+      <c r="AE61">
         <v>1.24</v>
       </c>
-      <c r="T61">
-        <v>3.38</v>
-      </c>
-      <c r="U61">
-        <v>2.3</v>
-      </c>
-      <c r="V61">
-        <v>1.53</v>
-      </c>
-      <c r="W61">
-        <v>1.12</v>
-      </c>
-      <c r="X61">
-        <v>1.03</v>
-      </c>
-      <c r="Y61">
-        <v>1.15</v>
-      </c>
-      <c r="Z61">
-        <v>4.2</v>
-      </c>
-      <c r="AA61">
-        <v>1.58</v>
-      </c>
-      <c r="AB61">
-        <v>2.24</v>
-      </c>
-      <c r="AC61">
-        <v>2.42</v>
-      </c>
-      <c r="AD61">
-        <v>1.49</v>
-      </c>
-      <c r="AE61">
-        <v>1.15</v>
-      </c>
       <c r="AF61">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AG61">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O62">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P62">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q62">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="R62">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S62">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U62">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V62">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W62">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X62">
         <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z62">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="AA62">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB62">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC62">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD62">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE62">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF62">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG62">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.21</v>
       </c>
       <c r="AK62">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AL62">
         <v>0</v>
